--- a/04. Initram_RFS_BuildRoot/Initram_RFS_BuildRoot.xlsx
+++ b/04. Initram_RFS_BuildRoot/Initram_RFS_BuildRoot.xlsx
@@ -9,13 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Các khái niêm cơ bản " sheetId="4" r:id="rId1"/>
     <sheet name="RFS" sheetId="6" r:id="rId2"/>
     <sheet name="Init RAMFS" sheetId="3" r:id="rId3"/>
-    <sheet name="BuildRoot" sheetId="2" r:id="rId4"/>
+    <sheet name="BuildRoot_menuconfig" sheetId="2" r:id="rId4"/>
+    <sheet name="BuildRoot_BR2_EXTERNAL" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -2288,9 +2289,6 @@
     <t># Sau khi cấu hình xong, save lại</t>
   </si>
   <si>
-    <t>make savedefconfig</t>
-  </si>
-  <si>
     <t># Defconfig sẽ được lưu tại defconfig</t>
   </si>
   <si>
@@ -2903,12 +2901,15 @@
       <t>genimage trong cấu hình:</t>
     </r>
   </si>
+  <si>
+    <t>make savedefconfig BR2_DEFCONFIG=defconfig</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3018,6 +3019,44 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="163"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -3320,7 +3359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3472,31 +3511,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
@@ -3540,6 +3554,55 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4116,12 +4179,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BD134"/>
-  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="16384" width="3.125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:56" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A1" s="32" t="s">
         <v>115</v>
       </c>
@@ -4134,7 +4197,7 @@
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
     </row>
-    <row r="2" spans="1:56" s="50" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:56" s="50" customFormat="1" ht="15">
       <c r="A2" s="42" t="s">
         <v>86</v>
       </c>
@@ -4147,7 +4210,7 @@
       <c r="I2" s="51"/>
       <c r="J2" s="51"/>
     </row>
-    <row r="3" spans="1:56" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:56" ht="15">
       <c r="A3" s="42" t="s">
         <v>87</v>
       </c>
@@ -4158,34 +4221,34 @@
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
-      <c r="T3" s="84" t="s">
+      <c r="T3" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="U3" s="84"/>
-      <c r="V3" s="84"/>
-      <c r="W3" s="84"/>
-      <c r="X3" s="84"/>
-      <c r="Y3" s="84"/>
-      <c r="Z3" s="84" t="s">
+      <c r="U3" s="123"/>
+      <c r="V3" s="123"/>
+      <c r="W3" s="123"/>
+      <c r="X3" s="123"/>
+      <c r="Y3" s="123"/>
+      <c r="Z3" s="123" t="s">
         <v>24</v>
       </c>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="84"/>
-      <c r="AC3" s="84"/>
-      <c r="AD3" s="84"/>
-      <c r="AE3" s="84"/>
-      <c r="AF3" s="84" t="s">
+      <c r="AA3" s="123"/>
+      <c r="AB3" s="123"/>
+      <c r="AC3" s="123"/>
+      <c r="AD3" s="123"/>
+      <c r="AE3" s="123"/>
+      <c r="AF3" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="AG3" s="84"/>
-      <c r="AH3" s="84"/>
-      <c r="AI3" s="84"/>
-      <c r="AJ3" s="84"/>
-      <c r="AK3" s="84"/>
-      <c r="AL3" s="84"/>
-      <c r="AM3" s="84"/>
-    </row>
-    <row r="4" spans="1:56" ht="15" x14ac:dyDescent="0.25">
+      <c r="AG3" s="123"/>
+      <c r="AH3" s="123"/>
+      <c r="AI3" s="123"/>
+      <c r="AJ3" s="123"/>
+      <c r="AK3" s="123"/>
+      <c r="AL3" s="123"/>
+      <c r="AM3" s="123"/>
+    </row>
+    <row r="4" spans="1:56" ht="15">
       <c r="C4" s="43"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -4193,32 +4256,32 @@
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
-      <c r="T4" s="87" t="s">
+      <c r="T4" s="126" t="s">
         <v>26</v>
       </c>
-      <c r="U4" s="87"/>
-      <c r="V4" s="87"/>
-      <c r="W4" s="87"/>
-      <c r="X4" s="87"/>
-      <c r="Y4" s="87"/>
-      <c r="Z4" s="85" t="s">
+      <c r="U4" s="126"/>
+      <c r="V4" s="126"/>
+      <c r="W4" s="126"/>
+      <c r="X4" s="126"/>
+      <c r="Y4" s="126"/>
+      <c r="Z4" s="124" t="s">
         <v>27</v>
       </c>
-      <c r="AA4" s="85"/>
-      <c r="AB4" s="85"/>
-      <c r="AC4" s="85"/>
-      <c r="AD4" s="85"/>
-      <c r="AE4" s="85"/>
-      <c r="AF4" s="85" t="s">
+      <c r="AA4" s="124"/>
+      <c r="AB4" s="124"/>
+      <c r="AC4" s="124"/>
+      <c r="AD4" s="124"/>
+      <c r="AE4" s="124"/>
+      <c r="AF4" s="124" t="s">
         <v>28</v>
       </c>
-      <c r="AG4" s="85"/>
-      <c r="AH4" s="85"/>
-      <c r="AI4" s="85"/>
-      <c r="AJ4" s="85"/>
-      <c r="AK4" s="85"/>
-      <c r="AL4" s="85"/>
-      <c r="AM4" s="85"/>
+      <c r="AG4" s="124"/>
+      <c r="AH4" s="124"/>
+      <c r="AI4" s="124"/>
+      <c r="AJ4" s="124"/>
+      <c r="AK4" s="124"/>
+      <c r="AL4" s="124"/>
+      <c r="AM4" s="124"/>
       <c r="AN4" s="3" t="s">
         <v>32</v>
       </c>
@@ -4239,7 +4302,7 @@
       <c r="BC4" s="3"/>
       <c r="BD4" s="3"/>
     </row>
-    <row r="5" spans="1:56" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:56" ht="15">
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -4249,37 +4312,37 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="T5" s="87" t="s">
+      <c r="T5" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="U5" s="87"/>
-      <c r="V5" s="87"/>
-      <c r="W5" s="87"/>
-      <c r="X5" s="87"/>
-      <c r="Y5" s="87"/>
-      <c r="Z5" s="85" t="s">
+      <c r="U5" s="126"/>
+      <c r="V5" s="126"/>
+      <c r="W5" s="126"/>
+      <c r="X5" s="126"/>
+      <c r="Y5" s="126"/>
+      <c r="Z5" s="124" t="s">
         <v>30</v>
       </c>
-      <c r="AA5" s="85"/>
-      <c r="AB5" s="85"/>
-      <c r="AC5" s="85"/>
-      <c r="AD5" s="85"/>
-      <c r="AE5" s="85"/>
-      <c r="AF5" s="85" t="s">
+      <c r="AA5" s="124"/>
+      <c r="AB5" s="124"/>
+      <c r="AC5" s="124"/>
+      <c r="AD5" s="124"/>
+      <c r="AE5" s="124"/>
+      <c r="AF5" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="AG5" s="85"/>
-      <c r="AH5" s="85"/>
-      <c r="AI5" s="85"/>
-      <c r="AJ5" s="85"/>
-      <c r="AK5" s="85"/>
-      <c r="AL5" s="85"/>
-      <c r="AM5" s="85"/>
+      <c r="AG5" s="124"/>
+      <c r="AH5" s="124"/>
+      <c r="AI5" s="124"/>
+      <c r="AJ5" s="124"/>
+      <c r="AK5" s="124"/>
+      <c r="AL5" s="124"/>
+      <c r="AM5" s="124"/>
       <c r="AN5" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:56" s="52" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:56" s="52" customFormat="1" ht="15.75" thickBot="1">
       <c r="B6" s="53"/>
       <c r="C6" s="53"/>
       <c r="D6" s="53"/>
@@ -4311,7 +4374,7 @@
       <c r="AM6" s="55"/>
       <c r="AN6" s="56"/>
     </row>
-    <row r="7" spans="1:56" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:56" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A7" s="32" t="s">
         <v>116</v>
       </c>
@@ -4324,7 +4387,7 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:56" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:56" ht="15">
       <c r="A8" s="6" t="s">
         <v>88</v>
       </c>
@@ -4336,7 +4399,7 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:56" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:56">
       <c r="B9" s="6" t="s">
         <v>0</v>
       </c>
@@ -4348,7 +4411,7 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:56" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:56">
       <c r="B10" s="9" t="s">
         <v>1</v>
       </c>
@@ -4360,7 +4423,7 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:56" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:56">
       <c r="B11" s="9" t="s">
         <v>2</v>
       </c>
@@ -4372,7 +4435,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:56" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:56">
       <c r="B12" s="9" t="s">
         <v>3</v>
       </c>
@@ -4384,7 +4447,7 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:56" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:56">
       <c r="B13" s="9" t="s">
         <v>4</v>
       </c>
@@ -4396,7 +4459,7 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:56" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:56" ht="15">
       <c r="A14" s="45" t="s">
         <v>117</v>
       </c>
@@ -4408,7 +4471,7 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:56" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:56" ht="15" thickBot="1">
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -4419,7 +4482,7 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:56" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:56" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A16" s="32" t="s">
         <v>118</v>
       </c>
@@ -4432,7 +4495,7 @@
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="44" t="s">
         <v>5</v>
       </c>
@@ -4444,7 +4507,7 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="44" t="s">
         <v>6</v>
       </c>
@@ -4456,7 +4519,7 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="15">
       <c r="A19" s="45" t="s">
         <v>119</v>
       </c>
@@ -4468,7 +4531,7 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="15" thickBot="1">
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -4479,7 +4542,7 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="1:10" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A21" s="32" t="s">
         <v>120</v>
       </c>
@@ -4492,7 +4555,7 @@
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="15">
       <c r="A22" s="44" t="s">
         <v>89</v>
       </c>
@@ -4504,7 +4567,7 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="44" t="s">
         <v>94</v>
       </c>
@@ -4516,7 +4579,7 @@
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="15" thickBot="1">
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -4527,7 +4590,7 @@
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
     </row>
-    <row r="25" spans="1:10" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A25" s="32" t="s">
         <v>121</v>
       </c>
@@ -4540,7 +4603,7 @@
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="15">
       <c r="A26" s="46" t="s">
         <v>90</v>
       </c>
@@ -4553,7 +4616,7 @@
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="46" t="s">
         <v>95</v>
       </c>
@@ -4565,7 +4628,7 @@
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="15" thickBot="1">
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
@@ -4576,7 +4639,7 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" spans="1:10" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A29" s="32" t="s">
         <v>122</v>
       </c>
@@ -4589,7 +4652,7 @@
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="46" t="s">
         <v>96</v>
       </c>
@@ -4601,7 +4664,7 @@
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
     </row>
-    <row r="31" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="15">
       <c r="A31" s="46" t="s">
         <v>97</v>
       </c>
@@ -4613,7 +4676,7 @@
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
     </row>
-    <row r="32" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="15">
       <c r="A32" s="48" t="s">
         <v>123</v>
       </c>
@@ -4625,7 +4688,7 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" ht="15" thickBot="1">
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
@@ -4636,7 +4699,7 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:24" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A34" s="32" t="s">
         <v>124</v>
       </c>
@@ -4649,7 +4712,7 @@
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" spans="1:24" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24" ht="15">
       <c r="A35" s="46" t="s">
         <v>91</v>
       </c>
@@ -4661,7 +4724,7 @@
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24">
       <c r="A36" s="46" t="s">
         <v>98</v>
       </c>
@@ -4673,7 +4736,7 @@
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
     </row>
-    <row r="37" spans="1:24" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="3" customFormat="1" ht="15">
       <c r="A37" s="48" t="s">
         <v>125</v>
       </c>
@@ -4685,7 +4748,7 @@
       <c r="I37" s="45"/>
       <c r="J37" s="45"/>
     </row>
-    <row r="38" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" ht="15" thickBot="1">
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
@@ -4696,7 +4759,7 @@
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
     </row>
-    <row r="39" spans="1:24" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A39" s="32" t="s">
         <v>126</v>
       </c>
@@ -4709,7 +4772,7 @@
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24">
       <c r="A40" s="46" t="s">
         <v>7</v>
       </c>
@@ -4722,7 +4785,7 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24">
       <c r="A41" s="46" t="s">
         <v>8</v>
       </c>
@@ -4735,7 +4798,7 @@
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
     </row>
-    <row r="42" spans="1:24" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" ht="15">
       <c r="A42" s="48" t="s">
         <v>127</v>
       </c>
@@ -4748,7 +4811,7 @@
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
     </row>
-    <row r="43" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" ht="15" thickBot="1">
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
@@ -4759,7 +4822,7 @@
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
     </row>
-    <row r="44" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" ht="15.75" thickBot="1">
       <c r="B44" s="33" t="s">
         <v>128</v>
       </c>
@@ -4782,7 +4845,7 @@
       <c r="S44" s="11"/>
       <c r="T44" s="12"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24">
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
@@ -4793,203 +4856,203 @@
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
     </row>
-    <row r="46" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C46" s="86" t="s">
+    <row r="46" spans="1:24" ht="14.25" customHeight="1">
+      <c r="C46" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="D46" s="86"/>
-      <c r="E46" s="86"/>
-      <c r="F46" s="86"/>
-      <c r="G46" s="86"/>
-      <c r="H46" s="86"/>
-      <c r="I46" s="86" t="s">
+      <c r="D46" s="125"/>
+      <c r="E46" s="125"/>
+      <c r="F46" s="125"/>
+      <c r="G46" s="125"/>
+      <c r="H46" s="125"/>
+      <c r="I46" s="125" t="s">
         <v>10</v>
       </c>
-      <c r="J46" s="86"/>
-      <c r="K46" s="86"/>
-      <c r="L46" s="86"/>
-      <c r="M46" s="86"/>
-      <c r="N46" s="86"/>
-      <c r="O46" s="86"/>
-      <c r="P46" s="86"/>
-      <c r="Q46" s="86"/>
-      <c r="R46" s="86"/>
-      <c r="S46" s="86"/>
-      <c r="T46" s="86"/>
-      <c r="U46" s="86"/>
-      <c r="V46" s="86"/>
-      <c r="W46" s="86"/>
-      <c r="X46" s="86"/>
-    </row>
-    <row r="47" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C47" s="83" t="s">
+      <c r="J46" s="125"/>
+      <c r="K46" s="125"/>
+      <c r="L46" s="125"/>
+      <c r="M46" s="125"/>
+      <c r="N46" s="125"/>
+      <c r="O46" s="125"/>
+      <c r="P46" s="125"/>
+      <c r="Q46" s="125"/>
+      <c r="R46" s="125"/>
+      <c r="S46" s="125"/>
+      <c r="T46" s="125"/>
+      <c r="U46" s="125"/>
+      <c r="V46" s="125"/>
+      <c r="W46" s="125"/>
+      <c r="X46" s="125"/>
+    </row>
+    <row r="47" spans="1:24" ht="18.75" customHeight="1">
+      <c r="C47" s="122" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="83"/>
-      <c r="E47" s="83"/>
-      <c r="F47" s="83"/>
-      <c r="G47" s="83"/>
-      <c r="H47" s="83"/>
-      <c r="I47" s="83" t="s">
+      <c r="D47" s="122"/>
+      <c r="E47" s="122"/>
+      <c r="F47" s="122"/>
+      <c r="G47" s="122"/>
+      <c r="H47" s="122"/>
+      <c r="I47" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="J47" s="83"/>
-      <c r="K47" s="83"/>
-      <c r="L47" s="83"/>
-      <c r="M47" s="83"/>
-      <c r="N47" s="83"/>
-      <c r="O47" s="83"/>
-      <c r="P47" s="83"/>
-      <c r="Q47" s="83"/>
-      <c r="R47" s="83"/>
-      <c r="S47" s="83"/>
-      <c r="T47" s="83"/>
-      <c r="U47" s="83"/>
-      <c r="V47" s="83"/>
-      <c r="W47" s="83"/>
-      <c r="X47" s="83"/>
-    </row>
-    <row r="48" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C48" s="83" t="s">
+      <c r="J47" s="122"/>
+      <c r="K47" s="122"/>
+      <c r="L47" s="122"/>
+      <c r="M47" s="122"/>
+      <c r="N47" s="122"/>
+      <c r="O47" s="122"/>
+      <c r="P47" s="122"/>
+      <c r="Q47" s="122"/>
+      <c r="R47" s="122"/>
+      <c r="S47" s="122"/>
+      <c r="T47" s="122"/>
+      <c r="U47" s="122"/>
+      <c r="V47" s="122"/>
+      <c r="W47" s="122"/>
+      <c r="X47" s="122"/>
+    </row>
+    <row r="48" spans="1:24" ht="17.25" customHeight="1">
+      <c r="C48" s="122" t="s">
         <v>13</v>
       </c>
-      <c r="D48" s="83"/>
-      <c r="E48" s="83"/>
-      <c r="F48" s="83"/>
-      <c r="G48" s="83"/>
-      <c r="H48" s="83"/>
-      <c r="I48" s="83" t="s">
+      <c r="D48" s="122"/>
+      <c r="E48" s="122"/>
+      <c r="F48" s="122"/>
+      <c r="G48" s="122"/>
+      <c r="H48" s="122"/>
+      <c r="I48" s="122" t="s">
         <v>14</v>
       </c>
-      <c r="J48" s="83"/>
-      <c r="K48" s="83"/>
-      <c r="L48" s="83"/>
-      <c r="M48" s="83"/>
-      <c r="N48" s="83"/>
-      <c r="O48" s="83"/>
-      <c r="P48" s="83"/>
-      <c r="Q48" s="83"/>
-      <c r="R48" s="83"/>
-      <c r="S48" s="83"/>
-      <c r="T48" s="83"/>
-      <c r="U48" s="83"/>
-      <c r="V48" s="83"/>
-      <c r="W48" s="83"/>
-      <c r="X48" s="83"/>
-    </row>
-    <row r="49" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C49" s="83" t="s">
+      <c r="J48" s="122"/>
+      <c r="K48" s="122"/>
+      <c r="L48" s="122"/>
+      <c r="M48" s="122"/>
+      <c r="N48" s="122"/>
+      <c r="O48" s="122"/>
+      <c r="P48" s="122"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="122"/>
+      <c r="S48" s="122"/>
+      <c r="T48" s="122"/>
+      <c r="U48" s="122"/>
+      <c r="V48" s="122"/>
+      <c r="W48" s="122"/>
+      <c r="X48" s="122"/>
+    </row>
+    <row r="49" spans="2:24" ht="16.5" customHeight="1">
+      <c r="C49" s="122" t="s">
         <v>15</v>
       </c>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
-      <c r="F49" s="83"/>
-      <c r="G49" s="83"/>
-      <c r="H49" s="83"/>
-      <c r="I49" s="83" t="s">
+      <c r="D49" s="122"/>
+      <c r="E49" s="122"/>
+      <c r="F49" s="122"/>
+      <c r="G49" s="122"/>
+      <c r="H49" s="122"/>
+      <c r="I49" s="122" t="s">
         <v>16</v>
       </c>
-      <c r="J49" s="83"/>
-      <c r="K49" s="83"/>
-      <c r="L49" s="83"/>
-      <c r="M49" s="83"/>
-      <c r="N49" s="83"/>
-      <c r="O49" s="83"/>
-      <c r="P49" s="83"/>
-      <c r="Q49" s="83"/>
-      <c r="R49" s="83"/>
-      <c r="S49" s="83"/>
-      <c r="T49" s="83"/>
-      <c r="U49" s="83"/>
-      <c r="V49" s="83"/>
-      <c r="W49" s="83"/>
-      <c r="X49" s="83"/>
-    </row>
-    <row r="50" spans="2:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C50" s="83" t="s">
+      <c r="J49" s="122"/>
+      <c r="K49" s="122"/>
+      <c r="L49" s="122"/>
+      <c r="M49" s="122"/>
+      <c r="N49" s="122"/>
+      <c r="O49" s="122"/>
+      <c r="P49" s="122"/>
+      <c r="Q49" s="122"/>
+      <c r="R49" s="122"/>
+      <c r="S49" s="122"/>
+      <c r="T49" s="122"/>
+      <c r="U49" s="122"/>
+      <c r="V49" s="122"/>
+      <c r="W49" s="122"/>
+      <c r="X49" s="122"/>
+    </row>
+    <row r="50" spans="2:24" ht="18.75" customHeight="1">
+      <c r="C50" s="122" t="s">
         <v>17</v>
       </c>
-      <c r="D50" s="83"/>
-      <c r="E50" s="83"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="83"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="83" t="s">
+      <c r="D50" s="122"/>
+      <c r="E50" s="122"/>
+      <c r="F50" s="122"/>
+      <c r="G50" s="122"/>
+      <c r="H50" s="122"/>
+      <c r="I50" s="122" t="s">
         <v>18</v>
       </c>
-      <c r="J50" s="83"/>
-      <c r="K50" s="83"/>
-      <c r="L50" s="83"/>
-      <c r="M50" s="83"/>
-      <c r="N50" s="83"/>
-      <c r="O50" s="83"/>
-      <c r="P50" s="83"/>
-      <c r="Q50" s="83"/>
-      <c r="R50" s="83"/>
-      <c r="S50" s="83"/>
-      <c r="T50" s="83"/>
-      <c r="U50" s="83"/>
-      <c r="V50" s="83"/>
-      <c r="W50" s="83"/>
-      <c r="X50" s="83"/>
-    </row>
-    <row r="51" spans="2:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C51" s="83" t="s">
+      <c r="J50" s="122"/>
+      <c r="K50" s="122"/>
+      <c r="L50" s="122"/>
+      <c r="M50" s="122"/>
+      <c r="N50" s="122"/>
+      <c r="O50" s="122"/>
+      <c r="P50" s="122"/>
+      <c r="Q50" s="122"/>
+      <c r="R50" s="122"/>
+      <c r="S50" s="122"/>
+      <c r="T50" s="122"/>
+      <c r="U50" s="122"/>
+      <c r="V50" s="122"/>
+      <c r="W50" s="122"/>
+      <c r="X50" s="122"/>
+    </row>
+    <row r="51" spans="2:24" ht="21" customHeight="1">
+      <c r="C51" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="D51" s="83"/>
-      <c r="E51" s="83"/>
-      <c r="F51" s="83"/>
-      <c r="G51" s="83"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="83" t="s">
+      <c r="D51" s="122"/>
+      <c r="E51" s="122"/>
+      <c r="F51" s="122"/>
+      <c r="G51" s="122"/>
+      <c r="H51" s="122"/>
+      <c r="I51" s="122" t="s">
         <v>20</v>
       </c>
-      <c r="J51" s="83"/>
-      <c r="K51" s="83"/>
-      <c r="L51" s="83"/>
-      <c r="M51" s="83"/>
-      <c r="N51" s="83"/>
-      <c r="O51" s="83"/>
-      <c r="P51" s="83"/>
-      <c r="Q51" s="83"/>
-      <c r="R51" s="83"/>
-      <c r="S51" s="83"/>
-      <c r="T51" s="83"/>
-      <c r="U51" s="83"/>
-      <c r="V51" s="83"/>
-      <c r="W51" s="83"/>
-      <c r="X51" s="83"/>
-    </row>
-    <row r="52" spans="2:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C52" s="83" t="s">
+      <c r="J51" s="122"/>
+      <c r="K51" s="122"/>
+      <c r="L51" s="122"/>
+      <c r="M51" s="122"/>
+      <c r="N51" s="122"/>
+      <c r="O51" s="122"/>
+      <c r="P51" s="122"/>
+      <c r="Q51" s="122"/>
+      <c r="R51" s="122"/>
+      <c r="S51" s="122"/>
+      <c r="T51" s="122"/>
+      <c r="U51" s="122"/>
+      <c r="V51" s="122"/>
+      <c r="W51" s="122"/>
+      <c r="X51" s="122"/>
+    </row>
+    <row r="52" spans="2:24" ht="17.25" customHeight="1">
+      <c r="C52" s="122" t="s">
         <v>21</v>
       </c>
-      <c r="D52" s="83"/>
-      <c r="E52" s="83"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="83" t="s">
+      <c r="D52" s="122"/>
+      <c r="E52" s="122"/>
+      <c r="F52" s="122"/>
+      <c r="G52" s="122"/>
+      <c r="H52" s="122"/>
+      <c r="I52" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="J52" s="83"/>
-      <c r="K52" s="83"/>
-      <c r="L52" s="83"/>
-      <c r="M52" s="83"/>
-      <c r="N52" s="83"/>
-      <c r="O52" s="83"/>
-      <c r="P52" s="83"/>
-      <c r="Q52" s="83"/>
-      <c r="R52" s="83"/>
-      <c r="S52" s="83"/>
-      <c r="T52" s="83"/>
-      <c r="U52" s="83"/>
-      <c r="V52" s="83"/>
-      <c r="W52" s="83"/>
-      <c r="X52" s="83"/>
-    </row>
-    <row r="53" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="J52" s="122"/>
+      <c r="K52" s="122"/>
+      <c r="L52" s="122"/>
+      <c r="M52" s="122"/>
+      <c r="N52" s="122"/>
+      <c r="O52" s="122"/>
+      <c r="P52" s="122"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="122"/>
+      <c r="S52" s="122"/>
+      <c r="T52" s="122"/>
+      <c r="U52" s="122"/>
+      <c r="V52" s="122"/>
+      <c r="W52" s="122"/>
+      <c r="X52" s="122"/>
+    </row>
+    <row r="53" spans="2:24">
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
@@ -5000,7 +5063,7 @@
       <c r="I53" s="6"/>
       <c r="J53" s="6"/>
     </row>
-    <row r="54" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:24">
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
@@ -5011,59 +5074,59 @@
       <c r="I54" s="6"/>
       <c r="J54" s="6"/>
     </row>
-    <row r="121" spans="37:38" x14ac:dyDescent="0.2">
+    <row r="121" spans="37:38">
       <c r="AK121" s="31"/>
       <c r="AL121" s="31"/>
     </row>
-    <row r="122" spans="37:38" x14ac:dyDescent="0.2">
+    <row r="122" spans="37:38">
       <c r="AK122" s="31"/>
       <c r="AL122" s="31"/>
     </row>
-    <row r="123" spans="37:38" x14ac:dyDescent="0.2">
+    <row r="123" spans="37:38">
       <c r="AK123" s="31"/>
       <c r="AL123" s="31"/>
     </row>
-    <row r="124" spans="37:38" x14ac:dyDescent="0.2">
+    <row r="124" spans="37:38">
       <c r="AK124" s="31"/>
       <c r="AL124" s="31"/>
     </row>
-    <row r="125" spans="37:38" x14ac:dyDescent="0.2">
+    <row r="125" spans="37:38">
       <c r="AK125" s="6"/>
       <c r="AL125" s="6"/>
     </row>
-    <row r="126" spans="37:38" x14ac:dyDescent="0.2">
+    <row r="126" spans="37:38">
       <c r="AK126" s="6"/>
       <c r="AL126" s="6"/>
     </row>
-    <row r="127" spans="37:38" ht="15" x14ac:dyDescent="0.2">
+    <row r="127" spans="37:38" ht="15">
       <c r="AK127" s="42"/>
       <c r="AL127" s="6"/>
     </row>
-    <row r="128" spans="37:38" x14ac:dyDescent="0.2">
+    <row r="128" spans="37:38">
       <c r="AK128" s="9"/>
       <c r="AL128" s="6"/>
     </row>
-    <row r="129" spans="37:38" x14ac:dyDescent="0.2">
+    <row r="129" spans="37:38">
       <c r="AK129" s="9"/>
       <c r="AL129" s="6"/>
     </row>
-    <row r="130" spans="37:38" x14ac:dyDescent="0.2">
+    <row r="130" spans="37:38">
       <c r="AK130" s="9"/>
       <c r="AL130" s="6"/>
     </row>
-    <row r="131" spans="37:38" x14ac:dyDescent="0.2">
+    <row r="131" spans="37:38">
       <c r="AK131" s="6"/>
       <c r="AL131" s="6"/>
     </row>
-    <row r="132" spans="37:38" x14ac:dyDescent="0.2">
+    <row r="132" spans="37:38">
       <c r="AK132" s="6"/>
       <c r="AL132" s="6"/>
     </row>
-    <row r="133" spans="37:38" x14ac:dyDescent="0.2">
+    <row r="133" spans="37:38">
       <c r="AK133" s="6"/>
       <c r="AL133" s="6"/>
     </row>
-    <row r="134" spans="37:38" x14ac:dyDescent="0.2">
+    <row r="134" spans="37:38">
       <c r="AK134" s="6"/>
       <c r="AL134" s="6"/>
     </row>
@@ -5101,12 +5164,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BL62"/>
-  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="16384" width="3.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" s="14" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:64" s="14" customFormat="1" ht="15.75" thickBot="1">
       <c r="A1" s="35" t="s">
         <v>171</v>
       </c>
@@ -5119,7 +5182,7 @@
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
     </row>
-    <row r="2" spans="1:64" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:64" s="5" customFormat="1" ht="15" thickBot="1">
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="6"/>
@@ -5130,7 +5193,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:64" s="5" customFormat="1" ht="15">
       <c r="B3" s="37" t="s">
         <v>172</v>
       </c>
@@ -5198,7 +5261,7 @@
       <c r="BK3" s="15"/>
       <c r="BL3" s="16"/>
     </row>
-    <row r="4" spans="1:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:64" s="5" customFormat="1" ht="15">
       <c r="B4" s="40" t="s">
         <v>173</v>
       </c>
@@ -5266,7 +5329,7 @@
       <c r="BK4" s="19"/>
       <c r="BL4" s="20"/>
     </row>
-    <row r="5" spans="1:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:64" s="5" customFormat="1" ht="15">
       <c r="B5" s="22" t="s">
         <v>34</v>
       </c>
@@ -5334,7 +5397,7 @@
       <c r="BK5" s="19"/>
       <c r="BL5" s="20"/>
     </row>
-    <row r="6" spans="1:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:64" s="5" customFormat="1" ht="15">
       <c r="B6" s="22" t="s">
         <v>35</v>
       </c>
@@ -5402,7 +5465,7 @@
       <c r="BK6" s="19"/>
       <c r="BL6" s="20"/>
     </row>
-    <row r="7" spans="1:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:64" s="5" customFormat="1" ht="15">
       <c r="B7" s="25" t="s">
         <v>36</v>
       </c>
@@ -5470,7 +5533,7 @@
       <c r="BK7" s="19"/>
       <c r="BL7" s="20"/>
     </row>
-    <row r="8" spans="1:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:64" s="5" customFormat="1" ht="15">
       <c r="B8" s="25" t="s">
         <v>37</v>
       </c>
@@ -5538,7 +5601,7 @@
       <c r="BK8" s="19"/>
       <c r="BL8" s="20"/>
     </row>
-    <row r="9" spans="1:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:64" s="5" customFormat="1">
       <c r="B9" s="25" t="s">
         <v>101</v>
       </c>
@@ -5604,7 +5667,7 @@
       <c r="BK9" s="19"/>
       <c r="BL9" s="20"/>
     </row>
-    <row r="10" spans="1:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:64" s="5" customFormat="1" ht="15">
       <c r="B10" s="25" t="s">
         <v>38</v>
       </c>
@@ -5672,7 +5735,7 @@
       <c r="BK10" s="19"/>
       <c r="BL10" s="20"/>
     </row>
-    <row r="11" spans="1:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:64" s="5" customFormat="1">
       <c r="B11" s="25" t="s">
         <v>39</v>
       </c>
@@ -5740,7 +5803,7 @@
       <c r="BK11" s="19"/>
       <c r="BL11" s="20"/>
     </row>
-    <row r="12" spans="1:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:64" s="5" customFormat="1" ht="15">
       <c r="B12" s="78" t="s">
         <v>178</v>
       </c>
@@ -5807,7 +5870,7 @@
       <c r="BK12" s="19"/>
       <c r="BL12" s="20"/>
     </row>
-    <row r="13" spans="1:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:64" s="5" customFormat="1" ht="15">
       <c r="B13" s="40" t="s">
         <v>174</v>
       </c>
@@ -5874,7 +5937,7 @@
       <c r="BK13" s="19"/>
       <c r="BL13" s="20"/>
     </row>
-    <row r="14" spans="1:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:64" s="5" customFormat="1">
       <c r="B14" s="22" t="s">
         <v>104</v>
       </c>
@@ -5939,7 +6002,7 @@
       <c r="BK14" s="19"/>
       <c r="BL14" s="20"/>
     </row>
-    <row r="15" spans="1:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:64" s="5" customFormat="1" ht="15">
       <c r="B15" s="22" t="s">
         <v>93</v>
       </c>
@@ -6007,7 +6070,7 @@
       <c r="BK15" s="19"/>
       <c r="BL15" s="20"/>
     </row>
-    <row r="16" spans="1:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:64" s="5" customFormat="1" ht="15">
       <c r="B16" s="80" t="s">
         <v>179</v>
       </c>
@@ -6075,7 +6138,7 @@
       <c r="BK16" s="19"/>
       <c r="BL16" s="20"/>
     </row>
-    <row r="17" spans="2:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:64" s="5" customFormat="1" ht="15">
       <c r="B17" s="40" t="s">
         <v>175</v>
       </c>
@@ -6143,7 +6206,7 @@
       <c r="BK17" s="19"/>
       <c r="BL17" s="20"/>
     </row>
-    <row r="18" spans="2:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:64" s="5" customFormat="1" ht="15">
       <c r="B18" s="22" t="s">
         <v>105</v>
       </c>
@@ -6211,7 +6274,7 @@
       <c r="BK18" s="19"/>
       <c r="BL18" s="20"/>
     </row>
-    <row r="19" spans="2:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:64" s="5" customFormat="1" ht="15">
       <c r="B19" s="22" t="s">
         <v>106</v>
       </c>
@@ -6279,7 +6342,7 @@
       <c r="BK19" s="19"/>
       <c r="BL19" s="20"/>
     </row>
-    <row r="20" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:64" s="5" customFormat="1">
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
       <c r="D20" s="19"/>
@@ -6345,7 +6408,7 @@
       <c r="BK20" s="19"/>
       <c r="BL20" s="20"/>
     </row>
-    <row r="21" spans="2:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:64" s="5" customFormat="1" ht="15">
       <c r="B21" s="40" t="s">
         <v>176</v>
       </c>
@@ -6411,7 +6474,7 @@
       <c r="BK21" s="19"/>
       <c r="BL21" s="20"/>
     </row>
-    <row r="22" spans="2:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:64" s="5" customFormat="1" ht="15">
       <c r="B22" s="22" t="s">
         <v>109</v>
       </c>
@@ -6441,26 +6504,26 @@
       <c r="Z22" s="19"/>
       <c r="AA22" s="20"/>
       <c r="AC22" s="21"/>
-      <c r="AD22" s="114" t="s">
+      <c r="AD22" s="105" t="s">
         <v>107</v>
       </c>
-      <c r="AE22" s="112"/>
-      <c r="AF22" s="113"/>
-      <c r="AG22" s="113"/>
-      <c r="AH22" s="113"/>
-      <c r="AI22" s="113"/>
-      <c r="AJ22" s="113"/>
-      <c r="AK22" s="113"/>
-      <c r="AL22" s="113"/>
-      <c r="AM22" s="113"/>
-      <c r="AN22" s="113"/>
-      <c r="AO22" s="113"/>
-      <c r="AP22" s="113"/>
-      <c r="AQ22" s="113"/>
-      <c r="AR22" s="113"/>
-      <c r="AS22" s="113"/>
-      <c r="AT22" s="113"/>
-      <c r="AU22" s="113"/>
+      <c r="AE22" s="103"/>
+      <c r="AF22" s="104"/>
+      <c r="AG22" s="104"/>
+      <c r="AH22" s="104"/>
+      <c r="AI22" s="104"/>
+      <c r="AJ22" s="104"/>
+      <c r="AK22" s="104"/>
+      <c r="AL22" s="104"/>
+      <c r="AM22" s="104"/>
+      <c r="AN22" s="104"/>
+      <c r="AO22" s="104"/>
+      <c r="AP22" s="104"/>
+      <c r="AQ22" s="104"/>
+      <c r="AR22" s="104"/>
+      <c r="AS22" s="104"/>
+      <c r="AT22" s="104"/>
+      <c r="AU22" s="104"/>
       <c r="AV22" s="19"/>
       <c r="AW22" s="19"/>
       <c r="AX22" s="19"/>
@@ -6479,7 +6542,7 @@
       <c r="BK22" s="19"/>
       <c r="BL22" s="20"/>
     </row>
-    <row r="23" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:64" s="5" customFormat="1">
       <c r="B23" s="22" t="s">
         <v>40</v>
       </c>
@@ -6509,26 +6572,26 @@
       <c r="Z23" s="19"/>
       <c r="AA23" s="20"/>
       <c r="AC23" s="21"/>
-      <c r="AD23" s="111" t="s">
+      <c r="AD23" s="102" t="s">
         <v>108</v>
       </c>
-      <c r="AE23" s="112"/>
-      <c r="AF23" s="113"/>
-      <c r="AG23" s="113"/>
-      <c r="AH23" s="113"/>
-      <c r="AI23" s="113"/>
-      <c r="AJ23" s="113"/>
-      <c r="AK23" s="113"/>
-      <c r="AL23" s="113"/>
-      <c r="AM23" s="113"/>
-      <c r="AN23" s="113"/>
-      <c r="AO23" s="113"/>
-      <c r="AP23" s="113"/>
-      <c r="AQ23" s="113"/>
-      <c r="AR23" s="113"/>
-      <c r="AS23" s="113"/>
-      <c r="AT23" s="113"/>
-      <c r="AU23" s="113"/>
+      <c r="AE23" s="103"/>
+      <c r="AF23" s="104"/>
+      <c r="AG23" s="104"/>
+      <c r="AH23" s="104"/>
+      <c r="AI23" s="104"/>
+      <c r="AJ23" s="104"/>
+      <c r="AK23" s="104"/>
+      <c r="AL23" s="104"/>
+      <c r="AM23" s="104"/>
+      <c r="AN23" s="104"/>
+      <c r="AO23" s="104"/>
+      <c r="AP23" s="104"/>
+      <c r="AQ23" s="104"/>
+      <c r="AR23" s="104"/>
+      <c r="AS23" s="104"/>
+      <c r="AT23" s="104"/>
+      <c r="AU23" s="104"/>
       <c r="AV23" s="19"/>
       <c r="AW23" s="19"/>
       <c r="AX23" s="19"/>
@@ -6547,7 +6610,7 @@
       <c r="BK23" s="19"/>
       <c r="BL23" s="20"/>
     </row>
-    <row r="24" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:64" s="5" customFormat="1">
       <c r="B24" s="22" t="s">
         <v>111</v>
       </c>
@@ -6577,26 +6640,26 @@
       <c r="Z24" s="19"/>
       <c r="AA24" s="20"/>
       <c r="AC24" s="21"/>
-      <c r="AD24" s="111" t="s">
+      <c r="AD24" s="102" t="s">
         <v>110</v>
       </c>
-      <c r="AE24" s="112"/>
-      <c r="AF24" s="113"/>
-      <c r="AG24" s="113"/>
-      <c r="AH24" s="113"/>
-      <c r="AI24" s="113"/>
-      <c r="AJ24" s="113"/>
-      <c r="AK24" s="113"/>
-      <c r="AL24" s="113"/>
-      <c r="AM24" s="113"/>
-      <c r="AN24" s="113"/>
-      <c r="AO24" s="113"/>
-      <c r="AP24" s="113"/>
-      <c r="AQ24" s="113"/>
-      <c r="AR24" s="113"/>
-      <c r="AS24" s="113"/>
-      <c r="AT24" s="113"/>
-      <c r="AU24" s="113"/>
+      <c r="AE24" s="103"/>
+      <c r="AF24" s="104"/>
+      <c r="AG24" s="104"/>
+      <c r="AH24" s="104"/>
+      <c r="AI24" s="104"/>
+      <c r="AJ24" s="104"/>
+      <c r="AK24" s="104"/>
+      <c r="AL24" s="104"/>
+      <c r="AM24" s="104"/>
+      <c r="AN24" s="104"/>
+      <c r="AO24" s="104"/>
+      <c r="AP24" s="104"/>
+      <c r="AQ24" s="104"/>
+      <c r="AR24" s="104"/>
+      <c r="AS24" s="104"/>
+      <c r="AT24" s="104"/>
+      <c r="AU24" s="104"/>
       <c r="AV24" s="19"/>
       <c r="AW24" s="19"/>
       <c r="AX24" s="19"/>
@@ -6615,7 +6678,7 @@
       <c r="BK24" s="19"/>
       <c r="BL24" s="20"/>
     </row>
-    <row r="25" spans="2:64" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:64" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
       <c r="D25" s="19"/>
@@ -6643,26 +6706,26 @@
       <c r="Z25" s="19"/>
       <c r="AA25" s="20"/>
       <c r="AC25" s="21"/>
-      <c r="AD25" s="111" t="s">
+      <c r="AD25" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="AE25" s="112"/>
-      <c r="AF25" s="113"/>
-      <c r="AG25" s="113"/>
-      <c r="AH25" s="113"/>
-      <c r="AI25" s="113"/>
-      <c r="AJ25" s="113"/>
-      <c r="AK25" s="113"/>
-      <c r="AL25" s="113"/>
-      <c r="AM25" s="113"/>
-      <c r="AN25" s="113"/>
-      <c r="AO25" s="113"/>
-      <c r="AP25" s="113"/>
-      <c r="AQ25" s="113"/>
-      <c r="AR25" s="113"/>
-      <c r="AS25" s="113"/>
-      <c r="AT25" s="113"/>
-      <c r="AU25" s="113"/>
+      <c r="AE25" s="103"/>
+      <c r="AF25" s="104"/>
+      <c r="AG25" s="104"/>
+      <c r="AH25" s="104"/>
+      <c r="AI25" s="104"/>
+      <c r="AJ25" s="104"/>
+      <c r="AK25" s="104"/>
+      <c r="AL25" s="104"/>
+      <c r="AM25" s="104"/>
+      <c r="AN25" s="104"/>
+      <c r="AO25" s="104"/>
+      <c r="AP25" s="104"/>
+      <c r="AQ25" s="104"/>
+      <c r="AR25" s="104"/>
+      <c r="AS25" s="104"/>
+      <c r="AT25" s="104"/>
+      <c r="AU25" s="104"/>
       <c r="AV25" s="19"/>
       <c r="AW25" s="19"/>
       <c r="AX25" s="19"/>
@@ -6681,7 +6744,7 @@
       <c r="BK25" s="19"/>
       <c r="BL25" s="20"/>
     </row>
-    <row r="26" spans="2:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:64" s="5" customFormat="1" ht="15">
       <c r="B26" s="40" t="s">
         <v>177</v>
       </c>
@@ -6711,26 +6774,26 @@
       <c r="Z26" s="19"/>
       <c r="AA26" s="20"/>
       <c r="AC26" s="21"/>
-      <c r="AD26" s="111" t="s">
+      <c r="AD26" s="102" t="s">
         <v>112</v>
       </c>
-      <c r="AE26" s="112"/>
-      <c r="AF26" s="113"/>
-      <c r="AG26" s="113"/>
-      <c r="AH26" s="113"/>
-      <c r="AI26" s="113"/>
-      <c r="AJ26" s="113"/>
-      <c r="AK26" s="113"/>
-      <c r="AL26" s="113"/>
-      <c r="AM26" s="113"/>
-      <c r="AN26" s="113"/>
-      <c r="AO26" s="113"/>
-      <c r="AP26" s="113"/>
-      <c r="AQ26" s="113"/>
-      <c r="AR26" s="113"/>
-      <c r="AS26" s="113"/>
-      <c r="AT26" s="113"/>
-      <c r="AU26" s="113"/>
+      <c r="AE26" s="103"/>
+      <c r="AF26" s="104"/>
+      <c r="AG26" s="104"/>
+      <c r="AH26" s="104"/>
+      <c r="AI26" s="104"/>
+      <c r="AJ26" s="104"/>
+      <c r="AK26" s="104"/>
+      <c r="AL26" s="104"/>
+      <c r="AM26" s="104"/>
+      <c r="AN26" s="104"/>
+      <c r="AO26" s="104"/>
+      <c r="AP26" s="104"/>
+      <c r="AQ26" s="104"/>
+      <c r="AR26" s="104"/>
+      <c r="AS26" s="104"/>
+      <c r="AT26" s="104"/>
+      <c r="AU26" s="104"/>
       <c r="AV26" s="19"/>
       <c r="AW26" s="19"/>
       <c r="AX26" s="19"/>
@@ -6749,31 +6812,31 @@
       <c r="BK26" s="19"/>
       <c r="BL26" s="20"/>
     </row>
-    <row r="27" spans="2:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:64" s="5" customFormat="1" ht="15">
       <c r="B27" s="21"/>
-      <c r="C27" s="86" t="s">
+      <c r="C27" s="125" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="86"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="86"/>
-      <c r="H27" s="86" t="s">
+      <c r="D27" s="125"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="125"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="I27" s="86"/>
-      <c r="J27" s="86"/>
-      <c r="K27" s="86"/>
-      <c r="L27" s="86"/>
-      <c r="M27" s="86"/>
-      <c r="N27" s="86"/>
-      <c r="O27" s="86"/>
-      <c r="P27" s="86"/>
-      <c r="Q27" s="86"/>
-      <c r="R27" s="86"/>
-      <c r="S27" s="86"/>
-      <c r="T27" s="86"/>
-      <c r="U27" s="86"/>
+      <c r="I27" s="125"/>
+      <c r="J27" s="125"/>
+      <c r="K27" s="125"/>
+      <c r="L27" s="125"/>
+      <c r="M27" s="125"/>
+      <c r="N27" s="125"/>
+      <c r="O27" s="125"/>
+      <c r="P27" s="125"/>
+      <c r="Q27" s="125"/>
+      <c r="R27" s="125"/>
+      <c r="S27" s="125"/>
+      <c r="T27" s="125"/>
+      <c r="U27" s="125"/>
       <c r="V27" s="19"/>
       <c r="W27" s="19"/>
       <c r="X27" s="19"/>
@@ -6817,31 +6880,31 @@
       <c r="BK27" s="19"/>
       <c r="BL27" s="20"/>
     </row>
-    <row r="28" spans="2:64" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:64" s="5" customFormat="1" ht="15">
       <c r="B28" s="21"/>
-      <c r="C28" s="83" t="s">
+      <c r="C28" s="122" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83" t="s">
+      <c r="D28" s="122"/>
+      <c r="E28" s="122"/>
+      <c r="F28" s="122"/>
+      <c r="G28" s="122"/>
+      <c r="H28" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
-      <c r="M28" s="83"/>
-      <c r="N28" s="83"/>
-      <c r="O28" s="83"/>
-      <c r="P28" s="83"/>
-      <c r="Q28" s="83"/>
-      <c r="R28" s="83"/>
-      <c r="S28" s="83"/>
-      <c r="T28" s="83"/>
-      <c r="U28" s="83"/>
+      <c r="I28" s="122"/>
+      <c r="J28" s="122"/>
+      <c r="K28" s="122"/>
+      <c r="L28" s="122"/>
+      <c r="M28" s="122"/>
+      <c r="N28" s="122"/>
+      <c r="O28" s="122"/>
+      <c r="P28" s="122"/>
+      <c r="Q28" s="122"/>
+      <c r="R28" s="122"/>
+      <c r="S28" s="122"/>
+      <c r="T28" s="122"/>
+      <c r="U28" s="122"/>
       <c r="V28" s="19"/>
       <c r="W28" s="19"/>
       <c r="X28" s="19"/>
@@ -6887,31 +6950,31 @@
       <c r="BK28" s="19"/>
       <c r="BL28" s="20"/>
     </row>
-    <row r="29" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:64" s="5" customFormat="1">
       <c r="B29" s="21"/>
-      <c r="C29" s="83" t="s">
+      <c r="C29" s="122" t="s">
         <v>45</v>
       </c>
-      <c r="D29" s="83"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="83"/>
-      <c r="H29" s="83" t="s">
+      <c r="D29" s="122"/>
+      <c r="E29" s="122"/>
+      <c r="F29" s="122"/>
+      <c r="G29" s="122"/>
+      <c r="H29" s="122" t="s">
         <v>46</v>
       </c>
-      <c r="I29" s="83"/>
-      <c r="J29" s="83"/>
-      <c r="K29" s="83"/>
-      <c r="L29" s="83"/>
-      <c r="M29" s="83"/>
-      <c r="N29" s="83"/>
-      <c r="O29" s="83"/>
-      <c r="P29" s="83"/>
-      <c r="Q29" s="83"/>
-      <c r="R29" s="83"/>
-      <c r="S29" s="83"/>
-      <c r="T29" s="83"/>
-      <c r="U29" s="83"/>
+      <c r="I29" s="122"/>
+      <c r="J29" s="122"/>
+      <c r="K29" s="122"/>
+      <c r="L29" s="122"/>
+      <c r="M29" s="122"/>
+      <c r="N29" s="122"/>
+      <c r="O29" s="122"/>
+      <c r="P29" s="122"/>
+      <c r="Q29" s="122"/>
+      <c r="R29" s="122"/>
+      <c r="S29" s="122"/>
+      <c r="T29" s="122"/>
+      <c r="U29" s="122"/>
       <c r="V29" s="19"/>
       <c r="W29" s="19"/>
       <c r="X29" s="19"/>
@@ -6957,31 +7020,31 @@
       <c r="BK29" s="19"/>
       <c r="BL29" s="20"/>
     </row>
-    <row r="30" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:64" s="5" customFormat="1">
       <c r="B30" s="21"/>
-      <c r="C30" s="83" t="s">
+      <c r="C30" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="83"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="83"/>
-      <c r="G30" s="83"/>
-      <c r="H30" s="83" t="s">
+      <c r="D30" s="122"/>
+      <c r="E30" s="122"/>
+      <c r="F30" s="122"/>
+      <c r="G30" s="122"/>
+      <c r="H30" s="122" t="s">
         <v>114</v>
       </c>
-      <c r="I30" s="83"/>
-      <c r="J30" s="83"/>
-      <c r="K30" s="83"/>
-      <c r="L30" s="83"/>
-      <c r="M30" s="83"/>
-      <c r="N30" s="83"/>
-      <c r="O30" s="83"/>
-      <c r="P30" s="83"/>
-      <c r="Q30" s="83"/>
-      <c r="R30" s="83"/>
-      <c r="S30" s="83"/>
-      <c r="T30" s="83"/>
-      <c r="U30" s="83"/>
+      <c r="I30" s="122"/>
+      <c r="J30" s="122"/>
+      <c r="K30" s="122"/>
+      <c r="L30" s="122"/>
+      <c r="M30" s="122"/>
+      <c r="N30" s="122"/>
+      <c r="O30" s="122"/>
+      <c r="P30" s="122"/>
+      <c r="Q30" s="122"/>
+      <c r="R30" s="122"/>
+      <c r="S30" s="122"/>
+      <c r="T30" s="122"/>
+      <c r="U30" s="122"/>
       <c r="V30" s="19"/>
       <c r="W30" s="19"/>
       <c r="X30" s="19"/>
@@ -7027,31 +7090,31 @@
       <c r="BK30" s="19"/>
       <c r="BL30" s="20"/>
     </row>
-    <row r="31" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:64" s="5" customFormat="1">
       <c r="B31" s="21"/>
-      <c r="C31" s="83" t="s">
+      <c r="C31" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="83"/>
-      <c r="H31" s="83" t="s">
+      <c r="D31" s="122"/>
+      <c r="E31" s="122"/>
+      <c r="F31" s="122"/>
+      <c r="G31" s="122"/>
+      <c r="H31" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="I31" s="83"/>
-      <c r="J31" s="83"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="83"/>
-      <c r="M31" s="83"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="83"/>
-      <c r="P31" s="83"/>
-      <c r="Q31" s="83"/>
-      <c r="R31" s="83"/>
-      <c r="S31" s="83"/>
-      <c r="T31" s="83"/>
-      <c r="U31" s="83"/>
+      <c r="I31" s="122"/>
+      <c r="J31" s="122"/>
+      <c r="K31" s="122"/>
+      <c r="L31" s="122"/>
+      <c r="M31" s="122"/>
+      <c r="N31" s="122"/>
+      <c r="O31" s="122"/>
+      <c r="P31" s="122"/>
+      <c r="Q31" s="122"/>
+      <c r="R31" s="122"/>
+      <c r="S31" s="122"/>
+      <c r="T31" s="122"/>
+      <c r="U31" s="122"/>
       <c r="V31" s="19"/>
       <c r="W31" s="19"/>
       <c r="X31" s="19"/>
@@ -7097,7 +7160,7 @@
       <c r="BK31" s="19"/>
       <c r="BL31" s="20"/>
     </row>
-    <row r="32" spans="2:64" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:64" s="5" customFormat="1" ht="15" thickBot="1">
       <c r="B32" s="26"/>
       <c r="C32" s="27"/>
       <c r="D32" s="28"/>
@@ -7163,7 +7226,7 @@
       <c r="BK32" s="19"/>
       <c r="BL32" s="20"/>
     </row>
-    <row r="33" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:64" s="5" customFormat="1">
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
       <c r="AC33" s="21"/>
@@ -7205,7 +7268,7 @@
       <c r="BK33" s="19"/>
       <c r="BL33" s="20"/>
     </row>
-    <row r="34" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:64" s="5" customFormat="1">
       <c r="AC34" s="21"/>
       <c r="AD34" s="19"/>
       <c r="AE34" s="23" t="s">
@@ -7245,7 +7308,7 @@
       <c r="BK34" s="19"/>
       <c r="BL34" s="20"/>
     </row>
-    <row r="35" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:64" s="5" customFormat="1">
       <c r="AC35" s="21"/>
       <c r="AD35" s="19"/>
       <c r="AE35" s="23" t="s">
@@ -7285,7 +7348,7 @@
       <c r="BK35" s="19"/>
       <c r="BL35" s="20"/>
     </row>
-    <row r="36" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:64" s="5" customFormat="1">
       <c r="AC36" s="21"/>
       <c r="AD36" s="19"/>
       <c r="AE36" s="23" t="s">
@@ -7325,7 +7388,7 @@
       <c r="BK36" s="19"/>
       <c r="BL36" s="20"/>
     </row>
-    <row r="37" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:64" s="5" customFormat="1">
       <c r="AC37" s="21"/>
       <c r="AD37" s="82" t="s">
         <v>62</v>
@@ -7365,7 +7428,7 @@
       <c r="BK37" s="19"/>
       <c r="BL37" s="20"/>
     </row>
-    <row r="38" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:64" s="5" customFormat="1">
       <c r="AC38" s="21"/>
       <c r="AD38" s="19"/>
       <c r="AE38" s="23" t="s">
@@ -7405,7 +7468,7 @@
       <c r="BK38" s="19"/>
       <c r="BL38" s="20"/>
     </row>
-    <row r="39" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:64" s="5" customFormat="1">
       <c r="AC39" s="21"/>
       <c r="AD39" s="82" t="s">
         <v>64</v>
@@ -7445,7 +7508,7 @@
       <c r="BK39" s="19"/>
       <c r="BL39" s="20"/>
     </row>
-    <row r="40" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:64" s="5" customFormat="1">
       <c r="AC40" s="21"/>
       <c r="AD40" s="24" t="s">
         <v>65</v>
@@ -7485,7 +7548,7 @@
       <c r="BK40" s="19"/>
       <c r="BL40" s="20"/>
     </row>
-    <row r="41" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:64" s="5" customFormat="1">
       <c r="AC41" s="21"/>
       <c r="AD41" s="19"/>
       <c r="AE41" s="24" t="s">
@@ -7525,7 +7588,7 @@
       <c r="BK41" s="19"/>
       <c r="BL41" s="20"/>
     </row>
-    <row r="42" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:64" s="5" customFormat="1">
       <c r="AC42" s="21"/>
       <c r="AD42" s="19"/>
       <c r="AE42" s="24" t="s">
@@ -7565,7 +7628,7 @@
       <c r="BK42" s="19"/>
       <c r="BL42" s="20"/>
     </row>
-    <row r="43" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:64" s="5" customFormat="1">
       <c r="AC43" s="21"/>
       <c r="AD43" s="19"/>
       <c r="AE43" s="24" t="s">
@@ -7605,7 +7668,7 @@
       <c r="BK43" s="19"/>
       <c r="BL43" s="20"/>
     </row>
-    <row r="44" spans="2:64" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:64" s="5" customFormat="1" ht="15" thickBot="1">
       <c r="AC44" s="30"/>
       <c r="AD44" s="28"/>
       <c r="AE44" s="28"/>
@@ -7643,34 +7706,34 @@
       <c r="BK44" s="28"/>
       <c r="BL44" s="29"/>
     </row>
-    <row r="45" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="2:64" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="49" spans="38:38" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="50" spans="38:38" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="51" spans="38:38" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="52" spans="38:38" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="53" spans="38:38" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:64" s="5" customFormat="1"/>
+    <row r="46" spans="2:64" s="5" customFormat="1"/>
+    <row r="47" spans="2:64" s="5" customFormat="1"/>
+    <row r="48" spans="2:64" s="5" customFormat="1"/>
+    <row r="49" spans="38:38" s="5" customFormat="1"/>
+    <row r="50" spans="38:38" s="5" customFormat="1"/>
+    <row r="51" spans="38:38" s="5" customFormat="1"/>
+    <row r="52" spans="38:38" s="5" customFormat="1"/>
+    <row r="53" spans="38:38" s="5" customFormat="1">
       <c r="AL53" s="6"/>
     </row>
-    <row r="54" spans="38:38" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="38:38" s="5" customFormat="1">
       <c r="AL54" s="6"/>
     </row>
-    <row r="55" spans="38:38" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="56" spans="38:38" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="38:38" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="58" spans="38:38" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="59" spans="38:38" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="38:38" s="5" customFormat="1"/>
+    <row r="56" spans="38:38" s="5" customFormat="1"/>
+    <row r="57" spans="38:38" s="5" customFormat="1"/>
+    <row r="58" spans="38:38" s="5" customFormat="1"/>
+    <row r="59" spans="38:38" s="5" customFormat="1">
       <c r="AL59" s="6"/>
     </row>
-    <row r="60" spans="38:38" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="38:38" s="5" customFormat="1">
       <c r="AL60" s="6"/>
     </row>
-    <row r="61" spans="38:38" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="38:38" s="5" customFormat="1">
       <c r="AL61" s="6"/>
     </row>
-    <row r="62" spans="38:38" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="38:38" s="5" customFormat="1" ht="15">
       <c r="AL62" s="2"/>
     </row>
   </sheetData>
@@ -7693,359 +7756,359 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BH70"/>
-  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="16384" width="3.125" style="60"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" s="58" customFormat="1" ht="15.75" thickBot="1">
       <c r="A1" s="57" t="s">
         <v>85</v>
       </c>
       <c r="C1" s="59"/>
       <c r="D1" s="59"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15">
       <c r="B2" s="61" t="s">
         <v>129</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
     </row>
-    <row r="3" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" ht="15">
       <c r="B3" s="63"/>
       <c r="C3" s="64" t="s">
         <v>162</v>
       </c>
       <c r="D3" s="62"/>
     </row>
-    <row r="4" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="15">
       <c r="C4" s="64" t="s">
         <v>163</v>
       </c>
       <c r="D4" s="62"/>
     </row>
-    <row r="5" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="15">
       <c r="B5" s="61" t="s">
         <v>130</v>
       </c>
       <c r="C5" s="62"/>
       <c r="D5" s="62"/>
     </row>
-    <row r="6" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="C6" s="90" t="s">
+    <row r="6" spans="1:26" ht="15">
+      <c r="C6" s="130" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90" t="s">
+      <c r="D6" s="130"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130"/>
+      <c r="H6" s="130"/>
+      <c r="I6" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="90"/>
-      <c r="K6" s="90"/>
-      <c r="L6" s="90"/>
-      <c r="M6" s="90"/>
-      <c r="N6" s="90"/>
-      <c r="O6" s="90"/>
-      <c r="P6" s="90"/>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90"/>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90" t="s">
+      <c r="J6" s="130"/>
+      <c r="K6" s="130"/>
+      <c r="L6" s="130"/>
+      <c r="M6" s="130"/>
+      <c r="N6" s="130"/>
+      <c r="O6" s="130"/>
+      <c r="P6" s="130"/>
+      <c r="Q6" s="130"/>
+      <c r="R6" s="130"/>
+      <c r="S6" s="130"/>
+      <c r="T6" s="130"/>
+      <c r="U6" s="130" t="s">
         <v>70</v>
       </c>
-      <c r="V6" s="90"/>
-      <c r="W6" s="90"/>
-      <c r="X6" s="90"/>
-      <c r="Y6" s="90"/>
-      <c r="Z6" s="90"/>
-    </row>
-    <row r="7" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="C7" s="89" t="s">
+      <c r="V6" s="130"/>
+      <c r="W6" s="130"/>
+      <c r="X6" s="130"/>
+      <c r="Y6" s="130"/>
+      <c r="Z6" s="130"/>
+    </row>
+    <row r="7" spans="1:26" ht="15">
+      <c r="C7" s="128" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="89"/>
-      <c r="E7" s="89"/>
-      <c r="F7" s="89"/>
-      <c r="G7" s="89"/>
-      <c r="H7" s="89"/>
-      <c r="I7" s="88" t="s">
+      <c r="D7" s="128"/>
+      <c r="E7" s="128"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="127" t="s">
         <v>72</v>
       </c>
-      <c r="J7" s="88"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="88"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="88"/>
-      <c r="O7" s="88"/>
-      <c r="P7" s="88"/>
-      <c r="Q7" s="88"/>
-      <c r="R7" s="88"/>
-      <c r="S7" s="88"/>
-      <c r="T7" s="88"/>
-      <c r="U7" s="88" t="s">
+      <c r="J7" s="127"/>
+      <c r="K7" s="127"/>
+      <c r="L7" s="127"/>
+      <c r="M7" s="127"/>
+      <c r="N7" s="127"/>
+      <c r="O7" s="127"/>
+      <c r="P7" s="127"/>
+      <c r="Q7" s="127"/>
+      <c r="R7" s="127"/>
+      <c r="S7" s="127"/>
+      <c r="T7" s="127"/>
+      <c r="U7" s="127" t="s">
         <v>154</v>
       </c>
-      <c r="V7" s="88"/>
-      <c r="W7" s="88"/>
-      <c r="X7" s="88"/>
-      <c r="Y7" s="88"/>
-      <c r="Z7" s="88"/>
-    </row>
-    <row r="8" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="C8" s="89" t="s">
+      <c r="V7" s="127"/>
+      <c r="W7" s="127"/>
+      <c r="X7" s="127"/>
+      <c r="Y7" s="127"/>
+      <c r="Z7" s="127"/>
+    </row>
+    <row r="8" spans="1:26" ht="15">
+      <c r="C8" s="128" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="89"/>
-      <c r="E8" s="89"/>
-      <c r="F8" s="89"/>
-      <c r="G8" s="89"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="88" t="s">
+      <c r="D8" s="128"/>
+      <c r="E8" s="128"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="128"/>
+      <c r="H8" s="128"/>
+      <c r="I8" s="127" t="s">
         <v>74</v>
       </c>
-      <c r="J8" s="88"/>
-      <c r="K8" s="88"/>
-      <c r="L8" s="88"/>
-      <c r="M8" s="88"/>
-      <c r="N8" s="88"/>
-      <c r="O8" s="88"/>
-      <c r="P8" s="88"/>
-      <c r="Q8" s="88"/>
-      <c r="R8" s="88"/>
-      <c r="S8" s="88"/>
-      <c r="T8" s="88"/>
-      <c r="U8" s="88" t="s">
+      <c r="J8" s="127"/>
+      <c r="K8" s="127"/>
+      <c r="L8" s="127"/>
+      <c r="M8" s="127"/>
+      <c r="N8" s="127"/>
+      <c r="O8" s="127"/>
+      <c r="P8" s="127"/>
+      <c r="Q8" s="127"/>
+      <c r="R8" s="127"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="127"/>
+      <c r="U8" s="127" t="s">
         <v>155</v>
       </c>
-      <c r="V8" s="88"/>
-      <c r="W8" s="88"/>
-      <c r="X8" s="88"/>
-      <c r="Y8" s="88"/>
-      <c r="Z8" s="88"/>
-    </row>
-    <row r="9" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="V8" s="127"/>
+      <c r="W8" s="127"/>
+      <c r="X8" s="127"/>
+      <c r="Y8" s="127"/>
+      <c r="Z8" s="127"/>
+    </row>
+    <row r="9" spans="1:26" ht="15">
       <c r="B9" s="61" t="s">
         <v>156</v>
       </c>
       <c r="C9" s="62"/>
       <c r="D9" s="62"/>
     </row>
-    <row r="10" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" ht="15">
       <c r="C10" s="65" t="s">
         <v>157</v>
       </c>
       <c r="D10" s="62"/>
     </row>
-    <row r="11" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="15">
       <c r="C11" s="63" t="s">
         <v>164</v>
       </c>
       <c r="D11" s="62"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26">
       <c r="C12" s="63" t="s">
         <v>75</v>
       </c>
       <c r="D12" s="62"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26">
       <c r="C13" s="63" t="s">
         <v>158</v>
       </c>
       <c r="D13" s="62"/>
     </row>
-    <row r="14" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" ht="15">
       <c r="C14" s="65" t="s">
         <v>165</v>
       </c>
       <c r="D14" s="62"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26">
       <c r="C15" s="63" t="s">
         <v>76</v>
       </c>
       <c r="D15" s="62"/>
     </row>
-    <row r="16" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" ht="15">
       <c r="B16" s="61" t="s">
         <v>131</v>
       </c>
       <c r="C16" s="62"/>
       <c r="D16" s="62"/>
     </row>
-    <row r="17" spans="1:49" ht="15" x14ac:dyDescent="0.2">
-      <c r="D17" s="89" t="s">
+    <row r="17" spans="1:49" ht="15">
+      <c r="D17" s="128" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="89"/>
-      <c r="F17" s="89"/>
-      <c r="G17" s="89"/>
-      <c r="H17" s="89"/>
-      <c r="I17" s="89"/>
-      <c r="J17" s="89"/>
-      <c r="K17" s="90" t="s">
+      <c r="E17" s="128"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="128"/>
+      <c r="H17" s="128"/>
+      <c r="I17" s="128"/>
+      <c r="J17" s="128"/>
+      <c r="K17" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="L17" s="90"/>
-      <c r="M17" s="90"/>
-      <c r="N17" s="90"/>
-      <c r="O17" s="90"/>
-      <c r="P17" s="90"/>
-      <c r="Q17" s="90"/>
-      <c r="R17" s="90"/>
-      <c r="S17" s="90"/>
-      <c r="T17" s="90"/>
-      <c r="U17" s="90"/>
-      <c r="V17" s="90"/>
-      <c r="W17" s="90"/>
-    </row>
-    <row r="18" spans="1:49" ht="15" x14ac:dyDescent="0.2">
-      <c r="D18" s="89" t="s">
+      <c r="L17" s="130"/>
+      <c r="M17" s="130"/>
+      <c r="N17" s="130"/>
+      <c r="O17" s="130"/>
+      <c r="P17" s="130"/>
+      <c r="Q17" s="130"/>
+      <c r="R17" s="130"/>
+      <c r="S17" s="130"/>
+      <c r="T17" s="130"/>
+      <c r="U17" s="130"/>
+      <c r="V17" s="130"/>
+      <c r="W17" s="130"/>
+    </row>
+    <row r="18" spans="1:49" ht="15">
+      <c r="D18" s="128" t="s">
         <v>77</v>
       </c>
-      <c r="E18" s="89"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="89"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="89"/>
-      <c r="K18" s="88" t="s">
+      <c r="E18" s="128"/>
+      <c r="F18" s="128"/>
+      <c r="G18" s="128"/>
+      <c r="H18" s="128"/>
+      <c r="I18" s="128"/>
+      <c r="J18" s="128"/>
+      <c r="K18" s="127" t="s">
         <v>78</v>
       </c>
-      <c r="L18" s="88"/>
-      <c r="M18" s="88"/>
-      <c r="N18" s="88"/>
-      <c r="O18" s="88"/>
-      <c r="P18" s="88"/>
-      <c r="Q18" s="88"/>
-      <c r="R18" s="88"/>
-      <c r="S18" s="88"/>
-      <c r="T18" s="88"/>
-      <c r="U18" s="88"/>
-      <c r="V18" s="88"/>
-      <c r="W18" s="88"/>
-    </row>
-    <row r="19" spans="1:49" ht="15" x14ac:dyDescent="0.2">
-      <c r="D19" s="89" t="s">
+      <c r="L18" s="127"/>
+      <c r="M18" s="127"/>
+      <c r="N18" s="127"/>
+      <c r="O18" s="127"/>
+      <c r="P18" s="127"/>
+      <c r="Q18" s="127"/>
+      <c r="R18" s="127"/>
+      <c r="S18" s="127"/>
+      <c r="T18" s="127"/>
+      <c r="U18" s="127"/>
+      <c r="V18" s="127"/>
+      <c r="W18" s="127"/>
+    </row>
+    <row r="19" spans="1:49" ht="15">
+      <c r="D19" s="128" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="89"/>
-      <c r="K19" s="88" t="s">
+      <c r="E19" s="128"/>
+      <c r="F19" s="128"/>
+      <c r="G19" s="128"/>
+      <c r="H19" s="128"/>
+      <c r="I19" s="128"/>
+      <c r="J19" s="128"/>
+      <c r="K19" s="127" t="s">
         <v>79</v>
       </c>
-      <c r="L19" s="88"/>
-      <c r="M19" s="88"/>
-      <c r="N19" s="88"/>
-      <c r="O19" s="88"/>
-      <c r="P19" s="88"/>
-      <c r="Q19" s="88"/>
-      <c r="R19" s="88"/>
-      <c r="S19" s="88"/>
-      <c r="T19" s="88"/>
-      <c r="U19" s="88"/>
-      <c r="V19" s="88"/>
-      <c r="W19" s="88"/>
-    </row>
-    <row r="20" spans="1:49" ht="15" x14ac:dyDescent="0.2">
-      <c r="D20" s="89" t="s">
+      <c r="L19" s="127"/>
+      <c r="M19" s="127"/>
+      <c r="N19" s="127"/>
+      <c r="O19" s="127"/>
+      <c r="P19" s="127"/>
+      <c r="Q19" s="127"/>
+      <c r="R19" s="127"/>
+      <c r="S19" s="127"/>
+      <c r="T19" s="127"/>
+      <c r="U19" s="127"/>
+      <c r="V19" s="127"/>
+      <c r="W19" s="127"/>
+    </row>
+    <row r="20" spans="1:49" ht="15">
+      <c r="D20" s="128" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="89"/>
-      <c r="K20" s="88" t="s">
+      <c r="E20" s="128"/>
+      <c r="F20" s="128"/>
+      <c r="G20" s="128"/>
+      <c r="H20" s="128"/>
+      <c r="I20" s="128"/>
+      <c r="J20" s="128"/>
+      <c r="K20" s="127" t="s">
         <v>80</v>
       </c>
-      <c r="L20" s="88"/>
-      <c r="M20" s="88"/>
-      <c r="N20" s="88"/>
-      <c r="O20" s="88"/>
-      <c r="P20" s="88"/>
-      <c r="Q20" s="88"/>
-      <c r="R20" s="88"/>
-      <c r="S20" s="88"/>
-      <c r="T20" s="88"/>
-      <c r="U20" s="88"/>
-      <c r="V20" s="88"/>
-      <c r="W20" s="88"/>
-    </row>
-    <row r="21" spans="1:49" ht="15" x14ac:dyDescent="0.2">
-      <c r="D21" s="89" t="s">
+      <c r="L20" s="127"/>
+      <c r="M20" s="127"/>
+      <c r="N20" s="127"/>
+      <c r="O20" s="127"/>
+      <c r="P20" s="127"/>
+      <c r="Q20" s="127"/>
+      <c r="R20" s="127"/>
+      <c r="S20" s="127"/>
+      <c r="T20" s="127"/>
+      <c r="U20" s="127"/>
+      <c r="V20" s="127"/>
+      <c r="W20" s="127"/>
+    </row>
+    <row r="21" spans="1:49" ht="15">
+      <c r="D21" s="128" t="s">
         <v>81</v>
       </c>
-      <c r="E21" s="89"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="89"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="89"/>
-      <c r="J21" s="89"/>
-      <c r="K21" s="88" t="s">
+      <c r="E21" s="128"/>
+      <c r="F21" s="128"/>
+      <c r="G21" s="128"/>
+      <c r="H21" s="128"/>
+      <c r="I21" s="128"/>
+      <c r="J21" s="128"/>
+      <c r="K21" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="L21" s="88"/>
-      <c r="M21" s="88"/>
-      <c r="N21" s="88"/>
-      <c r="O21" s="88"/>
-      <c r="P21" s="88"/>
-      <c r="Q21" s="88"/>
-      <c r="R21" s="88"/>
-      <c r="S21" s="88"/>
-      <c r="T21" s="88"/>
-      <c r="U21" s="88"/>
-      <c r="V21" s="88"/>
-      <c r="W21" s="88"/>
-    </row>
-    <row r="22" spans="1:49" ht="15" x14ac:dyDescent="0.2">
-      <c r="D22" s="89" t="s">
+      <c r="L21" s="127"/>
+      <c r="M21" s="127"/>
+      <c r="N21" s="127"/>
+      <c r="O21" s="127"/>
+      <c r="P21" s="127"/>
+      <c r="Q21" s="127"/>
+      <c r="R21" s="127"/>
+      <c r="S21" s="127"/>
+      <c r="T21" s="127"/>
+      <c r="U21" s="127"/>
+      <c r="V21" s="127"/>
+      <c r="W21" s="127"/>
+    </row>
+    <row r="22" spans="1:49" ht="15">
+      <c r="D22" s="128" t="s">
         <v>83</v>
       </c>
-      <c r="E22" s="89"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="89"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="89"/>
-      <c r="J22" s="89"/>
-      <c r="K22" s="88" t="s">
+      <c r="E22" s="128"/>
+      <c r="F22" s="128"/>
+      <c r="G22" s="128"/>
+      <c r="H22" s="128"/>
+      <c r="I22" s="128"/>
+      <c r="J22" s="128"/>
+      <c r="K22" s="127" t="s">
         <v>84</v>
       </c>
-      <c r="L22" s="88"/>
-      <c r="M22" s="88"/>
-      <c r="N22" s="88"/>
-      <c r="O22" s="88"/>
-      <c r="P22" s="88"/>
-      <c r="Q22" s="88"/>
-      <c r="R22" s="88"/>
-      <c r="S22" s="88"/>
-      <c r="T22" s="88"/>
-      <c r="U22" s="88"/>
-      <c r="V22" s="88"/>
-      <c r="W22" s="88"/>
-    </row>
-    <row r="23" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L22" s="127"/>
+      <c r="M22" s="127"/>
+      <c r="N22" s="127"/>
+      <c r="O22" s="127"/>
+      <c r="P22" s="127"/>
+      <c r="Q22" s="127"/>
+      <c r="R22" s="127"/>
+      <c r="S22" s="127"/>
+      <c r="T22" s="127"/>
+      <c r="U22" s="127"/>
+      <c r="V22" s="127"/>
+      <c r="W22" s="127"/>
+    </row>
+    <row r="23" spans="1:49" ht="15" thickBot="1">
       <c r="B23" s="62"/>
       <c r="C23" s="62"/>
       <c r="D23" s="62"/>
     </row>
-    <row r="24" spans="1:49" s="67" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:49" s="67" customFormat="1" ht="15.75" thickBot="1">
       <c r="A24" s="66" t="s">
         <v>133</v>
       </c>
       <c r="C24" s="68"/>
     </row>
-    <row r="25" spans="1:49" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:49" s="72" customFormat="1" ht="15">
       <c r="A25" s="69" t="s">
         <v>136</v>
       </c>
@@ -8072,7 +8135,7 @@
       <c r="AT25" s="70"/>
       <c r="AU25" s="70"/>
     </row>
-    <row r="26" spans="1:49" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:49" s="72" customFormat="1" ht="15">
       <c r="A26" s="63" t="s">
         <v>134</v>
       </c>
@@ -8082,7 +8145,7 @@
       </c>
       <c r="AO26" s="73"/>
     </row>
-    <row r="27" spans="1:49" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:49" s="72" customFormat="1" ht="15">
       <c r="A27" s="63" t="s">
         <v>0</v>
       </c>
@@ -8092,7 +8155,7 @@
       </c>
       <c r="AO27" s="73"/>
     </row>
-    <row r="28" spans="1:49" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:49" s="72" customFormat="1" ht="15">
       <c r="A28" s="74" t="s">
         <v>168</v>
       </c>
@@ -8102,7 +8165,7 @@
       <c r="AO28" s="62"/>
       <c r="AP28" s="62"/>
     </row>
-    <row r="29" spans="1:49" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:49" s="72" customFormat="1" ht="15">
       <c r="A29" s="74" t="s">
         <v>169</v>
       </c>
@@ -8121,7 +8184,7 @@
       <c r="AV29" s="70"/>
       <c r="AW29" s="70"/>
     </row>
-    <row r="30" spans="1:49" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:49" s="72" customFormat="1" ht="15">
       <c r="A30" s="62"/>
       <c r="C30" s="73"/>
       <c r="AM30" s="63" t="s">
@@ -8131,7 +8194,7 @@
       <c r="AO30" s="60"/>
       <c r="AP30" s="62"/>
     </row>
-    <row r="31" spans="1:49" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:49" s="72" customFormat="1" ht="15">
       <c r="A31" s="69" t="s">
         <v>137</v>
       </c>
@@ -8146,647 +8209,647 @@
       <c r="J31" s="70"/>
       <c r="K31" s="70"/>
     </row>
-    <row r="32" spans="1:49" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:49" s="72" customFormat="1" ht="15">
       <c r="A32" s="63" t="s">
         <v>159</v>
       </c>
       <c r="C32" s="73"/>
     </row>
-    <row r="33" spans="1:60" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:60" s="72" customFormat="1" ht="15">
       <c r="A33" s="62"/>
       <c r="C33" s="73"/>
     </row>
-    <row r="34" spans="1:60" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:60" s="72" customFormat="1" ht="15">
       <c r="A34" s="76" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="35" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:60">
       <c r="B35" s="64" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:60">
       <c r="B36" s="63" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="37" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:60" ht="15">
       <c r="B37" s="45" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:60">
       <c r="B38" s="63"/>
-      <c r="D38" s="102" t="s">
+      <c r="D38" s="93" t="s">
         <v>188</v>
       </c>
-      <c r="E38" s="103"/>
-      <c r="F38" s="103"/>
-      <c r="G38" s="103"/>
-      <c r="H38" s="103"/>
-      <c r="I38" s="103"/>
-      <c r="J38" s="103"/>
-      <c r="K38" s="103"/>
-      <c r="L38" s="103"/>
-      <c r="M38" s="103"/>
-      <c r="N38" s="104"/>
-    </row>
-    <row r="39" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="E38" s="94"/>
+      <c r="F38" s="94"/>
+      <c r="G38" s="94"/>
+      <c r="H38" s="94"/>
+      <c r="I38" s="94"/>
+      <c r="J38" s="94"/>
+      <c r="K38" s="94"/>
+      <c r="L38" s="94"/>
+      <c r="M38" s="94"/>
+      <c r="N38" s="95"/>
+    </row>
+    <row r="39" spans="1:60">
       <c r="B39" s="63"/>
     </row>
-    <row r="40" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:60">
       <c r="B40" s="63"/>
-      <c r="D40" s="92" t="s">
+      <c r="D40" s="83" t="s">
         <v>189</v>
       </c>
-      <c r="E40" s="93"/>
-      <c r="F40" s="93"/>
-      <c r="G40" s="93"/>
-      <c r="H40" s="93"/>
-      <c r="I40" s="93"/>
-      <c r="J40" s="93"/>
-      <c r="K40" s="93"/>
-      <c r="L40" s="93"/>
-      <c r="M40" s="93"/>
-      <c r="N40" s="94"/>
-      <c r="P40" s="92" t="s">
+      <c r="E40" s="84"/>
+      <c r="F40" s="84"/>
+      <c r="G40" s="84"/>
+      <c r="H40" s="84"/>
+      <c r="I40" s="84"/>
+      <c r="J40" s="84"/>
+      <c r="K40" s="84"/>
+      <c r="L40" s="84"/>
+      <c r="M40" s="84"/>
+      <c r="N40" s="85"/>
+      <c r="P40" s="83" t="s">
         <v>195</v>
       </c>
-      <c r="Q40" s="93"/>
-      <c r="R40" s="93"/>
-      <c r="S40" s="93"/>
-      <c r="T40" s="93"/>
-      <c r="U40" s="93"/>
-      <c r="V40" s="93"/>
-      <c r="W40" s="93"/>
-      <c r="X40" s="93"/>
-      <c r="Y40" s="94"/>
-      <c r="AA40" s="92" t="s">
+      <c r="Q40" s="84"/>
+      <c r="R40" s="84"/>
+      <c r="S40" s="84"/>
+      <c r="T40" s="84"/>
+      <c r="U40" s="84"/>
+      <c r="V40" s="84"/>
+      <c r="W40" s="84"/>
+      <c r="X40" s="84"/>
+      <c r="Y40" s="85"/>
+      <c r="AA40" s="83" t="s">
         <v>200</v>
       </c>
-      <c r="AB40" s="93"/>
-      <c r="AC40" s="93"/>
-      <c r="AD40" s="93"/>
-      <c r="AE40" s="93"/>
-      <c r="AF40" s="93"/>
-      <c r="AG40" s="93"/>
-      <c r="AH40" s="93"/>
-      <c r="AI40" s="93"/>
-      <c r="AJ40" s="94"/>
-      <c r="AL40" s="92" t="s">
+      <c r="AB40" s="84"/>
+      <c r="AC40" s="84"/>
+      <c r="AD40" s="84"/>
+      <c r="AE40" s="84"/>
+      <c r="AF40" s="84"/>
+      <c r="AG40" s="84"/>
+      <c r="AH40" s="84"/>
+      <c r="AI40" s="84"/>
+      <c r="AJ40" s="85"/>
+      <c r="AL40" s="83" t="s">
         <v>210</v>
       </c>
-      <c r="AM40" s="93"/>
-      <c r="AN40" s="93"/>
-      <c r="AO40" s="93"/>
-      <c r="AP40" s="93"/>
-      <c r="AQ40" s="93"/>
-      <c r="AR40" s="93"/>
-      <c r="AS40" s="93"/>
-      <c r="AT40" s="93"/>
-      <c r="AU40" s="93"/>
-      <c r="AV40" s="94"/>
-      <c r="AX40" s="92" t="s">
+      <c r="AM40" s="84"/>
+      <c r="AN40" s="84"/>
+      <c r="AO40" s="84"/>
+      <c r="AP40" s="84"/>
+      <c r="AQ40" s="84"/>
+      <c r="AR40" s="84"/>
+      <c r="AS40" s="84"/>
+      <c r="AT40" s="84"/>
+      <c r="AU40" s="84"/>
+      <c r="AV40" s="85"/>
+      <c r="AX40" s="83" t="s">
         <v>218</v>
       </c>
-      <c r="AY40" s="93"/>
-      <c r="AZ40" s="93"/>
-      <c r="BA40" s="93"/>
-      <c r="BB40" s="93"/>
-      <c r="BC40" s="93"/>
-      <c r="BD40" s="93"/>
-      <c r="BE40" s="93"/>
-      <c r="BF40" s="93"/>
-      <c r="BG40" s="93"/>
-      <c r="BH40" s="94"/>
-    </row>
-    <row r="41" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="AY40" s="84"/>
+      <c r="AZ40" s="84"/>
+      <c r="BA40" s="84"/>
+      <c r="BB40" s="84"/>
+      <c r="BC40" s="84"/>
+      <c r="BD40" s="84"/>
+      <c r="BE40" s="84"/>
+      <c r="BF40" s="84"/>
+      <c r="BG40" s="84"/>
+      <c r="BH40" s="85"/>
+    </row>
+    <row r="41" spans="1:60">
       <c r="B41" s="63"/>
-      <c r="D41" s="95"/>
-      <c r="E41" s="96"/>
-      <c r="F41" s="96"/>
-      <c r="G41" s="96"/>
-      <c r="H41" s="96"/>
-      <c r="I41" s="96"/>
-      <c r="J41" s="96"/>
-      <c r="K41" s="96"/>
-      <c r="L41" s="96"/>
-      <c r="M41" s="96"/>
-      <c r="N41" s="97"/>
-      <c r="P41" s="95"/>
-      <c r="Q41" s="98" t="s">
+      <c r="D41" s="86"/>
+      <c r="E41" s="87"/>
+      <c r="F41" s="87"/>
+      <c r="G41" s="87"/>
+      <c r="H41" s="87"/>
+      <c r="I41" s="87"/>
+      <c r="J41" s="87"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="87"/>
+      <c r="M41" s="87"/>
+      <c r="N41" s="88"/>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="89" t="s">
         <v>196</v>
       </c>
-      <c r="R41" s="96"/>
-      <c r="S41" s="96"/>
-      <c r="T41" s="96"/>
-      <c r="U41" s="96"/>
-      <c r="V41" s="96"/>
-      <c r="W41" s="96"/>
-      <c r="X41" s="96"/>
-      <c r="Y41" s="97"/>
-      <c r="AA41" s="95"/>
-      <c r="AB41" s="107" t="s">
+      <c r="R41" s="87"/>
+      <c r="S41" s="87"/>
+      <c r="T41" s="87"/>
+      <c r="U41" s="87"/>
+      <c r="V41" s="87"/>
+      <c r="W41" s="87"/>
+      <c r="X41" s="87"/>
+      <c r="Y41" s="88"/>
+      <c r="AA41" s="86"/>
+      <c r="AB41" s="98" t="s">
         <v>201</v>
       </c>
-      <c r="AC41" s="96"/>
-      <c r="AD41" s="96"/>
-      <c r="AE41" s="96"/>
-      <c r="AF41" s="96"/>
-      <c r="AG41" s="96"/>
-      <c r="AH41" s="96"/>
-      <c r="AI41" s="96"/>
-      <c r="AJ41" s="97"/>
-      <c r="AL41" s="95"/>
-      <c r="AM41" s="96" t="s">
+      <c r="AC41" s="87"/>
+      <c r="AD41" s="87"/>
+      <c r="AE41" s="87"/>
+      <c r="AF41" s="87"/>
+      <c r="AG41" s="87"/>
+      <c r="AH41" s="87"/>
+      <c r="AI41" s="87"/>
+      <c r="AJ41" s="88"/>
+      <c r="AL41" s="86"/>
+      <c r="AM41" s="87" t="s">
         <v>211</v>
       </c>
-      <c r="AN41" s="96"/>
-      <c r="AO41" s="96"/>
-      <c r="AP41" s="96"/>
-      <c r="AQ41" s="96"/>
-      <c r="AR41" s="96"/>
-      <c r="AS41" s="96"/>
-      <c r="AT41" s="96"/>
-      <c r="AU41" s="96"/>
-      <c r="AV41" s="97"/>
-      <c r="AX41" s="95"/>
-      <c r="AY41" s="96" t="s">
+      <c r="AN41" s="87"/>
+      <c r="AO41" s="87"/>
+      <c r="AP41" s="87"/>
+      <c r="AQ41" s="87"/>
+      <c r="AR41" s="87"/>
+      <c r="AS41" s="87"/>
+      <c r="AT41" s="87"/>
+      <c r="AU41" s="87"/>
+      <c r="AV41" s="88"/>
+      <c r="AX41" s="86"/>
+      <c r="AY41" s="87" t="s">
         <v>219</v>
       </c>
-      <c r="AZ41" s="96"/>
-      <c r="BA41" s="96"/>
-      <c r="BB41" s="96"/>
-      <c r="BC41" s="96"/>
-      <c r="BD41" s="96"/>
-      <c r="BE41" s="96"/>
-      <c r="BF41" s="96"/>
-      <c r="BG41" s="96"/>
-      <c r="BH41" s="97"/>
-    </row>
-    <row r="42" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="AZ41" s="87"/>
+      <c r="BA41" s="87"/>
+      <c r="BB41" s="87"/>
+      <c r="BC41" s="87"/>
+      <c r="BD41" s="87"/>
+      <c r="BE41" s="87"/>
+      <c r="BF41" s="87"/>
+      <c r="BG41" s="87"/>
+      <c r="BH41" s="88"/>
+    </row>
+    <row r="42" spans="1:60">
       <c r="B42" s="63"/>
-      <c r="D42" s="95"/>
-      <c r="E42" s="98" t="s">
+      <c r="D42" s="86"/>
+      <c r="E42" s="89" t="s">
         <v>190</v>
       </c>
-      <c r="F42" s="96"/>
-      <c r="G42" s="96"/>
-      <c r="H42" s="96"/>
-      <c r="I42" s="96"/>
-      <c r="J42" s="96"/>
-      <c r="K42" s="96"/>
-      <c r="L42" s="96"/>
-      <c r="M42" s="96"/>
-      <c r="N42" s="97"/>
-      <c r="P42" s="95"/>
-      <c r="Q42" s="98" t="s">
+      <c r="F42" s="87"/>
+      <c r="G42" s="87"/>
+      <c r="H42" s="87"/>
+      <c r="I42" s="87"/>
+      <c r="J42" s="87"/>
+      <c r="K42" s="87"/>
+      <c r="L42" s="87"/>
+      <c r="M42" s="87"/>
+      <c r="N42" s="88"/>
+      <c r="P42" s="86"/>
+      <c r="Q42" s="89" t="s">
         <v>197</v>
       </c>
-      <c r="R42" s="96"/>
-      <c r="S42" s="96"/>
-      <c r="T42" s="96"/>
-      <c r="U42" s="96"/>
-      <c r="V42" s="96"/>
-      <c r="W42" s="96"/>
-      <c r="X42" s="96"/>
-      <c r="Y42" s="97"/>
-      <c r="AA42" s="95"/>
-      <c r="AB42" s="98" t="s">
+      <c r="R42" s="87"/>
+      <c r="S42" s="87"/>
+      <c r="T42" s="87"/>
+      <c r="U42" s="87"/>
+      <c r="V42" s="87"/>
+      <c r="W42" s="87"/>
+      <c r="X42" s="87"/>
+      <c r="Y42" s="88"/>
+      <c r="AA42" s="86"/>
+      <c r="AB42" s="89" t="s">
         <v>202</v>
       </c>
-      <c r="AC42" s="96"/>
-      <c r="AD42" s="96"/>
-      <c r="AE42" s="96"/>
-      <c r="AF42" s="96"/>
-      <c r="AG42" s="96"/>
-      <c r="AH42" s="96"/>
-      <c r="AI42" s="96"/>
-      <c r="AJ42" s="97"/>
-      <c r="AL42" s="95"/>
-      <c r="AM42" s="96" t="s">
+      <c r="AC42" s="87"/>
+      <c r="AD42" s="87"/>
+      <c r="AE42" s="87"/>
+      <c r="AF42" s="87"/>
+      <c r="AG42" s="87"/>
+      <c r="AH42" s="87"/>
+      <c r="AI42" s="87"/>
+      <c r="AJ42" s="88"/>
+      <c r="AL42" s="86"/>
+      <c r="AM42" s="87" t="s">
         <v>212</v>
       </c>
-      <c r="AN42" s="96"/>
-      <c r="AO42" s="96"/>
-      <c r="AP42" s="96"/>
-      <c r="AQ42" s="96"/>
-      <c r="AR42" s="96"/>
-      <c r="AS42" s="96"/>
-      <c r="AT42" s="96"/>
-      <c r="AU42" s="96"/>
-      <c r="AV42" s="97"/>
-      <c r="AX42" s="95"/>
-      <c r="AY42" s="96" t="s">
+      <c r="AN42" s="87"/>
+      <c r="AO42" s="87"/>
+      <c r="AP42" s="87"/>
+      <c r="AQ42" s="87"/>
+      <c r="AR42" s="87"/>
+      <c r="AS42" s="87"/>
+      <c r="AT42" s="87"/>
+      <c r="AU42" s="87"/>
+      <c r="AV42" s="88"/>
+      <c r="AX42" s="86"/>
+      <c r="AY42" s="87" t="s">
         <v>220</v>
       </c>
-      <c r="AZ42" s="96"/>
-      <c r="BA42" s="96"/>
-      <c r="BB42" s="96"/>
-      <c r="BC42" s="96"/>
-      <c r="BD42" s="96"/>
-      <c r="BE42" s="96"/>
-      <c r="BF42" s="96"/>
-      <c r="BG42" s="96"/>
-      <c r="BH42" s="97"/>
-    </row>
-    <row r="43" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="AZ42" s="87"/>
+      <c r="BA42" s="87"/>
+      <c r="BB42" s="87"/>
+      <c r="BC42" s="87"/>
+      <c r="BD42" s="87"/>
+      <c r="BE42" s="87"/>
+      <c r="BF42" s="87"/>
+      <c r="BG42" s="87"/>
+      <c r="BH42" s="88"/>
+    </row>
+    <row r="43" spans="1:60">
       <c r="B43" s="63"/>
-      <c r="D43" s="95"/>
-      <c r="E43" s="96"/>
-      <c r="F43" s="91" t="s">
+      <c r="D43" s="86"/>
+      <c r="E43" s="87"/>
+      <c r="F43" s="129" t="s">
         <v>191</v>
       </c>
-      <c r="G43" s="91"/>
-      <c r="H43" s="91"/>
-      <c r="I43" s="91"/>
-      <c r="J43" s="98" t="s">
+      <c r="G43" s="129"/>
+      <c r="H43" s="129"/>
+      <c r="I43" s="129"/>
+      <c r="J43" s="89" t="s">
         <v>192</v>
       </c>
-      <c r="K43" s="96"/>
-      <c r="L43" s="96"/>
-      <c r="M43" s="96"/>
-      <c r="N43" s="97"/>
-      <c r="P43" s="95"/>
-      <c r="Q43" s="98" t="s">
+      <c r="K43" s="87"/>
+      <c r="L43" s="87"/>
+      <c r="M43" s="87"/>
+      <c r="N43" s="88"/>
+      <c r="P43" s="86"/>
+      <c r="Q43" s="89" t="s">
         <v>198</v>
       </c>
-      <c r="R43" s="96"/>
-      <c r="S43" s="96"/>
-      <c r="T43" s="96"/>
-      <c r="U43" s="96"/>
-      <c r="V43" s="96"/>
-      <c r="W43" s="96"/>
-      <c r="X43" s="96"/>
-      <c r="Y43" s="97"/>
-      <c r="AA43" s="95"/>
-      <c r="AB43" s="96" t="s">
+      <c r="R43" s="87"/>
+      <c r="S43" s="87"/>
+      <c r="T43" s="87"/>
+      <c r="U43" s="87"/>
+      <c r="V43" s="87"/>
+      <c r="W43" s="87"/>
+      <c r="X43" s="87"/>
+      <c r="Y43" s="88"/>
+      <c r="AA43" s="86"/>
+      <c r="AB43" s="87" t="s">
         <v>203</v>
       </c>
-      <c r="AC43" s="96"/>
-      <c r="AD43" s="96"/>
-      <c r="AE43" s="96"/>
-      <c r="AF43" s="96"/>
-      <c r="AG43" s="96"/>
-      <c r="AH43" s="96"/>
-      <c r="AI43" s="96"/>
-      <c r="AJ43" s="97"/>
-      <c r="AL43" s="95"/>
-      <c r="AM43" s="96"/>
-      <c r="AN43" s="96"/>
-      <c r="AO43" s="96"/>
-      <c r="AP43" s="96"/>
-      <c r="AQ43" s="96"/>
-      <c r="AR43" s="96"/>
-      <c r="AS43" s="96"/>
-      <c r="AT43" s="96"/>
-      <c r="AU43" s="96"/>
-      <c r="AV43" s="97"/>
-      <c r="AX43" s="95"/>
-      <c r="AY43" s="108" t="s">
+      <c r="AC43" s="87"/>
+      <c r="AD43" s="87"/>
+      <c r="AE43" s="87"/>
+      <c r="AF43" s="87"/>
+      <c r="AG43" s="87"/>
+      <c r="AH43" s="87"/>
+      <c r="AI43" s="87"/>
+      <c r="AJ43" s="88"/>
+      <c r="AL43" s="86"/>
+      <c r="AM43" s="87"/>
+      <c r="AN43" s="87"/>
+      <c r="AO43" s="87"/>
+      <c r="AP43" s="87"/>
+      <c r="AQ43" s="87"/>
+      <c r="AR43" s="87"/>
+      <c r="AS43" s="87"/>
+      <c r="AT43" s="87"/>
+      <c r="AU43" s="87"/>
+      <c r="AV43" s="88"/>
+      <c r="AX43" s="86"/>
+      <c r="AY43" s="99" t="s">
         <v>221</v>
       </c>
-      <c r="AZ43" s="96"/>
-      <c r="BA43" s="96"/>
-      <c r="BB43" s="96"/>
-      <c r="BC43" s="96"/>
-      <c r="BD43" s="96"/>
-      <c r="BE43" s="96"/>
-      <c r="BF43" s="96"/>
-      <c r="BG43" s="96"/>
-      <c r="BH43" s="97"/>
-    </row>
-    <row r="44" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="AZ43" s="87"/>
+      <c r="BA43" s="87"/>
+      <c r="BB43" s="87"/>
+      <c r="BC43" s="87"/>
+      <c r="BD43" s="87"/>
+      <c r="BE43" s="87"/>
+      <c r="BF43" s="87"/>
+      <c r="BG43" s="87"/>
+      <c r="BH43" s="88"/>
+    </row>
+    <row r="44" spans="1:60">
       <c r="B44" s="63"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="96"/>
-      <c r="F44" s="91" t="s">
+      <c r="D44" s="86"/>
+      <c r="E44" s="87"/>
+      <c r="F44" s="129" t="s">
         <v>193</v>
       </c>
-      <c r="G44" s="91"/>
-      <c r="H44" s="91"/>
-      <c r="I44" s="91"/>
-      <c r="J44" s="98" t="s">
+      <c r="G44" s="129"/>
+      <c r="H44" s="129"/>
+      <c r="I44" s="129"/>
+      <c r="J44" s="89" t="s">
         <v>194</v>
       </c>
-      <c r="K44" s="96"/>
-      <c r="L44" s="96"/>
-      <c r="M44" s="96"/>
-      <c r="N44" s="97"/>
-      <c r="P44" s="99"/>
-      <c r="Q44" s="105" t="s">
+      <c r="K44" s="87"/>
+      <c r="L44" s="87"/>
+      <c r="M44" s="87"/>
+      <c r="N44" s="88"/>
+      <c r="P44" s="90"/>
+      <c r="Q44" s="96" t="s">
         <v>199</v>
       </c>
-      <c r="R44" s="100"/>
-      <c r="S44" s="100"/>
-      <c r="T44" s="100"/>
-      <c r="U44" s="100"/>
-      <c r="V44" s="100"/>
-      <c r="W44" s="100"/>
-      <c r="X44" s="100"/>
-      <c r="Y44" s="101"/>
-      <c r="AA44" s="95"/>
-      <c r="AB44" s="96" t="s">
+      <c r="R44" s="91"/>
+      <c r="S44" s="91"/>
+      <c r="T44" s="91"/>
+      <c r="U44" s="91"/>
+      <c r="V44" s="91"/>
+      <c r="W44" s="91"/>
+      <c r="X44" s="91"/>
+      <c r="Y44" s="92"/>
+      <c r="AA44" s="86"/>
+      <c r="AB44" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="AC44" s="96"/>
-      <c r="AD44" s="96"/>
-      <c r="AE44" s="96"/>
-      <c r="AF44" s="96"/>
-      <c r="AG44" s="96"/>
-      <c r="AH44" s="96"/>
-      <c r="AI44" s="96"/>
-      <c r="AJ44" s="97"/>
-      <c r="AL44" s="95"/>
-      <c r="AM44" s="96" t="s">
+      <c r="AC44" s="87"/>
+      <c r="AD44" s="87"/>
+      <c r="AE44" s="87"/>
+      <c r="AF44" s="87"/>
+      <c r="AG44" s="87"/>
+      <c r="AH44" s="87"/>
+      <c r="AI44" s="87"/>
+      <c r="AJ44" s="88"/>
+      <c r="AL44" s="86"/>
+      <c r="AM44" s="87" t="s">
         <v>213</v>
       </c>
-      <c r="AN44" s="96"/>
-      <c r="AO44" s="96"/>
-      <c r="AP44" s="96"/>
-      <c r="AQ44" s="96"/>
-      <c r="AR44" s="96"/>
-      <c r="AS44" s="96"/>
-      <c r="AT44" s="96"/>
-      <c r="AU44" s="96"/>
-      <c r="AV44" s="97"/>
-      <c r="AX44" s="95"/>
-      <c r="AY44" s="108" t="s">
+      <c r="AN44" s="87"/>
+      <c r="AO44" s="87"/>
+      <c r="AP44" s="87"/>
+      <c r="AQ44" s="87"/>
+      <c r="AR44" s="87"/>
+      <c r="AS44" s="87"/>
+      <c r="AT44" s="87"/>
+      <c r="AU44" s="87"/>
+      <c r="AV44" s="88"/>
+      <c r="AX44" s="86"/>
+      <c r="AY44" s="99" t="s">
         <v>222</v>
       </c>
-      <c r="AZ44" s="96"/>
-      <c r="BA44" s="96"/>
-      <c r="BB44" s="96"/>
-      <c r="BC44" s="96"/>
-      <c r="BD44" s="96"/>
-      <c r="BE44" s="96"/>
-      <c r="BF44" s="96"/>
-      <c r="BG44" s="96"/>
-      <c r="BH44" s="97"/>
-    </row>
-    <row r="45" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="AZ44" s="87"/>
+      <c r="BA44" s="87"/>
+      <c r="BB44" s="87"/>
+      <c r="BC44" s="87"/>
+      <c r="BD44" s="87"/>
+      <c r="BE44" s="87"/>
+      <c r="BF44" s="87"/>
+      <c r="BG44" s="87"/>
+      <c r="BH44" s="88"/>
+    </row>
+    <row r="45" spans="1:60">
       <c r="B45" s="63"/>
-      <c r="D45" s="99"/>
-      <c r="E45" s="100"/>
-      <c r="F45" s="100"/>
-      <c r="G45" s="100"/>
-      <c r="H45" s="100"/>
-      <c r="I45" s="100"/>
-      <c r="J45" s="100"/>
-      <c r="K45" s="100"/>
-      <c r="L45" s="100"/>
-      <c r="M45" s="100"/>
-      <c r="N45" s="101"/>
-      <c r="AA45" s="95"/>
-      <c r="AB45" s="96"/>
-      <c r="AC45" s="96"/>
-      <c r="AD45" s="96"/>
-      <c r="AE45" s="96"/>
-      <c r="AF45" s="96"/>
-      <c r="AG45" s="96"/>
-      <c r="AH45" s="96"/>
-      <c r="AI45" s="96"/>
-      <c r="AJ45" s="97"/>
-      <c r="AL45" s="95"/>
-      <c r="AM45" s="96" t="s">
+      <c r="D45" s="90"/>
+      <c r="E45" s="91"/>
+      <c r="F45" s="91"/>
+      <c r="G45" s="91"/>
+      <c r="H45" s="91"/>
+      <c r="I45" s="91"/>
+      <c r="J45" s="91"/>
+      <c r="K45" s="91"/>
+      <c r="L45" s="91"/>
+      <c r="M45" s="91"/>
+      <c r="N45" s="92"/>
+      <c r="AA45" s="86"/>
+      <c r="AB45" s="87"/>
+      <c r="AC45" s="87"/>
+      <c r="AD45" s="87"/>
+      <c r="AE45" s="87"/>
+      <c r="AF45" s="87"/>
+      <c r="AG45" s="87"/>
+      <c r="AH45" s="87"/>
+      <c r="AI45" s="87"/>
+      <c r="AJ45" s="88"/>
+      <c r="AL45" s="86"/>
+      <c r="AM45" s="87" t="s">
         <v>214</v>
       </c>
-      <c r="AN45" s="96"/>
-      <c r="AO45" s="96"/>
-      <c r="AP45" s="96"/>
-      <c r="AQ45" s="96"/>
-      <c r="AR45" s="96"/>
-      <c r="AS45" s="96"/>
-      <c r="AT45" s="96"/>
-      <c r="AU45" s="96"/>
-      <c r="AV45" s="97"/>
-      <c r="AX45" s="99"/>
-      <c r="AY45" s="109" t="s">
+      <c r="AN45" s="87"/>
+      <c r="AO45" s="87"/>
+      <c r="AP45" s="87"/>
+      <c r="AQ45" s="87"/>
+      <c r="AR45" s="87"/>
+      <c r="AS45" s="87"/>
+      <c r="AT45" s="87"/>
+      <c r="AU45" s="87"/>
+      <c r="AV45" s="88"/>
+      <c r="AX45" s="90"/>
+      <c r="AY45" s="100" t="s">
         <v>223</v>
       </c>
-      <c r="AZ45" s="100"/>
-      <c r="BA45" s="100"/>
-      <c r="BB45" s="100"/>
-      <c r="BC45" s="100"/>
-      <c r="BD45" s="100"/>
-      <c r="BE45" s="100"/>
-      <c r="BF45" s="100"/>
-      <c r="BG45" s="100"/>
-      <c r="BH45" s="101"/>
-    </row>
-    <row r="46" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="AZ45" s="91"/>
+      <c r="BA45" s="91"/>
+      <c r="BB45" s="91"/>
+      <c r="BC45" s="91"/>
+      <c r="BD45" s="91"/>
+      <c r="BE45" s="91"/>
+      <c r="BF45" s="91"/>
+      <c r="BG45" s="91"/>
+      <c r="BH45" s="92"/>
+    </row>
+    <row r="46" spans="1:60">
       <c r="B46" s="63"/>
-      <c r="AA46" s="95"/>
-      <c r="AB46" s="96" t="s">
+      <c r="AA46" s="86"/>
+      <c r="AB46" s="87" t="s">
         <v>205</v>
       </c>
-      <c r="AC46" s="96"/>
-      <c r="AD46" s="96"/>
-      <c r="AE46" s="96"/>
-      <c r="AF46" s="96"/>
-      <c r="AG46" s="96"/>
-      <c r="AH46" s="96"/>
-      <c r="AI46" s="96"/>
-      <c r="AJ46" s="97"/>
-      <c r="AL46" s="95"/>
-      <c r="AM46" s="96" t="s">
+      <c r="AC46" s="87"/>
+      <c r="AD46" s="87"/>
+      <c r="AE46" s="87"/>
+      <c r="AF46" s="87"/>
+      <c r="AG46" s="87"/>
+      <c r="AH46" s="87"/>
+      <c r="AI46" s="87"/>
+      <c r="AJ46" s="88"/>
+      <c r="AL46" s="86"/>
+      <c r="AM46" s="87" t="s">
         <v>215</v>
       </c>
-      <c r="AN46" s="96"/>
-      <c r="AO46" s="96"/>
-      <c r="AP46" s="96"/>
-      <c r="AQ46" s="96"/>
-      <c r="AR46" s="96"/>
-      <c r="AS46" s="96"/>
-      <c r="AT46" s="96"/>
-      <c r="AU46" s="96"/>
-      <c r="AV46" s="97"/>
-    </row>
-    <row r="47" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+      <c r="AN46" s="87"/>
+      <c r="AO46" s="87"/>
+      <c r="AP46" s="87"/>
+      <c r="AQ46" s="87"/>
+      <c r="AR46" s="87"/>
+      <c r="AS46" s="87"/>
+      <c r="AT46" s="87"/>
+      <c r="AU46" s="87"/>
+      <c r="AV46" s="88"/>
+    </row>
+    <row r="47" spans="1:60" ht="15">
       <c r="B47" s="63"/>
-      <c r="AA47" s="95"/>
-      <c r="AB47" s="110" t="s">
+      <c r="AA47" s="86"/>
+      <c r="AB47" s="101" t="s">
         <v>206</v>
       </c>
-      <c r="AC47" s="96"/>
-      <c r="AD47" s="96"/>
-      <c r="AE47" s="96"/>
-      <c r="AF47" s="96"/>
-      <c r="AG47" s="96"/>
-      <c r="AH47" s="96"/>
-      <c r="AI47" s="96"/>
-      <c r="AJ47" s="97"/>
-      <c r="AL47" s="95"/>
-      <c r="AM47" s="96"/>
-      <c r="AN47" s="96"/>
-      <c r="AO47" s="96"/>
-      <c r="AP47" s="96"/>
-      <c r="AQ47" s="96"/>
-      <c r="AR47" s="96"/>
-      <c r="AS47" s="96"/>
-      <c r="AT47" s="96"/>
-      <c r="AU47" s="96"/>
-      <c r="AV47" s="97"/>
-    </row>
-    <row r="48" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+      <c r="AC47" s="87"/>
+      <c r="AD47" s="87"/>
+      <c r="AE47" s="87"/>
+      <c r="AF47" s="87"/>
+      <c r="AG47" s="87"/>
+      <c r="AH47" s="87"/>
+      <c r="AI47" s="87"/>
+      <c r="AJ47" s="88"/>
+      <c r="AL47" s="86"/>
+      <c r="AM47" s="87"/>
+      <c r="AN47" s="87"/>
+      <c r="AO47" s="87"/>
+      <c r="AP47" s="87"/>
+      <c r="AQ47" s="87"/>
+      <c r="AR47" s="87"/>
+      <c r="AS47" s="87"/>
+      <c r="AT47" s="87"/>
+      <c r="AU47" s="87"/>
+      <c r="AV47" s="88"/>
+    </row>
+    <row r="48" spans="1:60" ht="15">
       <c r="B48" s="63"/>
-      <c r="AA48" s="95"/>
-      <c r="AB48" s="110" t="s">
+      <c r="AA48" s="86"/>
+      <c r="AB48" s="101" t="s">
         <v>207</v>
       </c>
-      <c r="AC48" s="96"/>
-      <c r="AD48" s="96"/>
-      <c r="AE48" s="96"/>
-      <c r="AF48" s="96"/>
-      <c r="AG48" s="96"/>
-      <c r="AH48" s="96"/>
-      <c r="AI48" s="96"/>
-      <c r="AJ48" s="97"/>
-      <c r="AL48" s="95"/>
-      <c r="AM48" s="96" t="s">
+      <c r="AC48" s="87"/>
+      <c r="AD48" s="87"/>
+      <c r="AE48" s="87"/>
+      <c r="AF48" s="87"/>
+      <c r="AG48" s="87"/>
+      <c r="AH48" s="87"/>
+      <c r="AI48" s="87"/>
+      <c r="AJ48" s="88"/>
+      <c r="AL48" s="86"/>
+      <c r="AM48" s="87" t="s">
         <v>216</v>
       </c>
-      <c r="AN48" s="96"/>
-      <c r="AO48" s="96"/>
-      <c r="AP48" s="96"/>
-      <c r="AQ48" s="96"/>
-      <c r="AR48" s="96"/>
-      <c r="AS48" s="96"/>
-      <c r="AT48" s="96"/>
-      <c r="AU48" s="96"/>
-      <c r="AV48" s="97"/>
-    </row>
-    <row r="49" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="AN48" s="87"/>
+      <c r="AO48" s="87"/>
+      <c r="AP48" s="87"/>
+      <c r="AQ48" s="87"/>
+      <c r="AR48" s="87"/>
+      <c r="AS48" s="87"/>
+      <c r="AT48" s="87"/>
+      <c r="AU48" s="87"/>
+      <c r="AV48" s="88"/>
+    </row>
+    <row r="49" spans="1:48">
       <c r="B49" s="63"/>
-      <c r="AA49" s="95"/>
-      <c r="AB49" s="96" t="s">
+      <c r="AA49" s="86"/>
+      <c r="AB49" s="87" t="s">
         <v>209</v>
       </c>
-      <c r="AC49" s="96"/>
-      <c r="AD49" s="96"/>
-      <c r="AE49" s="96"/>
-      <c r="AF49" s="96"/>
-      <c r="AG49" s="96"/>
-      <c r="AH49" s="96"/>
-      <c r="AI49" s="96"/>
-      <c r="AJ49" s="97"/>
-      <c r="AL49" s="99"/>
-      <c r="AM49" s="100" t="s">
+      <c r="AC49" s="87"/>
+      <c r="AD49" s="87"/>
+      <c r="AE49" s="87"/>
+      <c r="AF49" s="87"/>
+      <c r="AG49" s="87"/>
+      <c r="AH49" s="87"/>
+      <c r="AI49" s="87"/>
+      <c r="AJ49" s="88"/>
+      <c r="AL49" s="90"/>
+      <c r="AM49" s="91" t="s">
         <v>217</v>
       </c>
-      <c r="AN49" s="100"/>
-      <c r="AO49" s="100"/>
-      <c r="AP49" s="100"/>
-      <c r="AQ49" s="100"/>
-      <c r="AR49" s="100"/>
-      <c r="AS49" s="100"/>
-      <c r="AT49" s="100"/>
-      <c r="AU49" s="100"/>
-      <c r="AV49" s="101"/>
-    </row>
-    <row r="50" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="AN49" s="91"/>
+      <c r="AO49" s="91"/>
+      <c r="AP49" s="91"/>
+      <c r="AQ49" s="91"/>
+      <c r="AR49" s="91"/>
+      <c r="AS49" s="91"/>
+      <c r="AT49" s="91"/>
+      <c r="AU49" s="91"/>
+      <c r="AV49" s="92"/>
+    </row>
+    <row r="50" spans="1:48">
       <c r="B50" s="63"/>
-      <c r="AA50" s="99"/>
-      <c r="AB50" s="100" t="s">
+      <c r="AA50" s="90"/>
+      <c r="AB50" s="91" t="s">
         <v>208</v>
       </c>
-      <c r="AC50" s="100"/>
-      <c r="AD50" s="100"/>
-      <c r="AE50" s="100"/>
-      <c r="AF50" s="100"/>
-      <c r="AG50" s="100"/>
-      <c r="AH50" s="100"/>
-      <c r="AI50" s="100"/>
-      <c r="AJ50" s="101"/>
-    </row>
-    <row r="51" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AC50" s="91"/>
+      <c r="AD50" s="91"/>
+      <c r="AE50" s="91"/>
+      <c r="AF50" s="91"/>
+      <c r="AG50" s="91"/>
+      <c r="AH50" s="91"/>
+      <c r="AI50" s="91"/>
+      <c r="AJ50" s="92"/>
+    </row>
+    <row r="51" spans="1:48" ht="15" thickBot="1">
       <c r="D51" s="62"/>
       <c r="E51" s="62"/>
     </row>
-    <row r="52" spans="1:48" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:48" s="58" customFormat="1" ht="15.75" thickBot="1">
       <c r="A52" s="77" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="53" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:48" ht="15">
       <c r="A53" s="61" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="54" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:48">
       <c r="A54" s="63" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="55" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:48">
       <c r="A55" s="63" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="56" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:48">
       <c r="A56" s="64"/>
     </row>
-    <row r="57" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:48" ht="15">
       <c r="A57" s="61" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="58" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:48" ht="15">
       <c r="A58" s="63" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="59" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:48">
       <c r="A59" s="63" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="60" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:48">
       <c r="A60" s="64"/>
     </row>
-    <row r="61" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:48" ht="15">
       <c r="A61" s="61" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="62" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:48">
       <c r="A62" s="63" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="63" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:48">
       <c r="A63" s="63" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="64" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:48">
       <c r="A64" s="64"/>
     </row>
-    <row r="65" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1" ht="15">
       <c r="A65" s="61" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1">
       <c r="A66" s="63" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1">
       <c r="A67" s="64"/>
     </row>
-    <row r="68" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1" ht="15">
       <c r="A68" s="61" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1">
       <c r="A69" s="63" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1">
       <c r="A70" s="63" t="s">
         <v>153</v>
       </c>
@@ -8809,13 +8872,13 @@
     <mergeCell ref="D17:J17"/>
     <mergeCell ref="D18:J18"/>
     <mergeCell ref="D19:J19"/>
+    <mergeCell ref="K22:W22"/>
     <mergeCell ref="D20:J20"/>
     <mergeCell ref="D21:J21"/>
     <mergeCell ref="K18:W18"/>
     <mergeCell ref="K19:W19"/>
     <mergeCell ref="K20:W20"/>
     <mergeCell ref="K21:W21"/>
-    <mergeCell ref="K22:W22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8826,78 +8889,78 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BG255"/>
-  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16384" width="3.125" style="116"/>
+    <col min="1" max="16384" width="3.125" style="107"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="120" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="119" t="s">
+    <row r="1" spans="1:13" s="111" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A1" s="110" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="15">
       <c r="A2" s="45" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="117" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="108" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="117" t="s">
+    <row r="4" spans="1:13">
+      <c r="A4" s="108" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="117" t="s">
+    <row r="5" spans="1:13">
+      <c r="A5" s="108" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="117" t="s">
+    <row r="6" spans="1:13">
+      <c r="A6" s="108" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="106"/>
-    </row>
-    <row r="8" spans="1:13" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13">
+      <c r="A7" s="97"/>
+    </row>
+    <row r="8" spans="1:13" ht="15">
       <c r="A8" s="42" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9" s="115" t="s">
+    <row r="9" spans="1:13" ht="15">
+      <c r="A9" s="106" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15">
+      <c r="A10" s="106" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="115" t="s">
+    <row r="11" spans="1:13" ht="15">
+      <c r="A11" s="106" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11" s="115" t="s">
+    <row r="12" spans="1:13" ht="15">
+      <c r="A12" s="106" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="115" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="106"/>
-    </row>
-    <row r="14" spans="1:13" s="120" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="119" t="s">
+    <row r="13" spans="1:13" ht="15" thickBot="1">
+      <c r="A13" s="97"/>
+    </row>
+    <row r="14" spans="1:13" s="111" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A14" s="110" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="15">
       <c r="A15" s="42" t="s">
         <v>230</v>
       </c>
@@ -8905,1283 +8968,1283 @@
         <v>256</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="118" t="s">
+    <row r="16" spans="1:13">
+      <c r="A16" s="109" t="s">
         <v>231</v>
       </c>
-      <c r="M16" s="118" t="s">
+      <c r="M16" s="109" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="118" t="s">
+    <row r="17" spans="1:13">
+      <c r="A17" s="109" t="s">
         <v>232</v>
       </c>
-      <c r="M17" s="118" t="s">
+      <c r="M17" s="109" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="118" t="s">
+    <row r="18" spans="1:13">
+      <c r="A18" s="109" t="s">
         <v>233</v>
       </c>
-      <c r="M18" s="118" t="s">
+      <c r="M18" s="109" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="118" t="s">
+    <row r="19" spans="1:13">
+      <c r="A19" s="109" t="s">
         <v>234</v>
       </c>
-      <c r="M19" s="118"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="118" t="s">
+      <c r="M19" s="109"/>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="109" t="s">
         <v>235</v>
       </c>
-      <c r="M20" s="118" t="s">
+      <c r="M20" s="109" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="118" t="s">
+    <row r="21" spans="1:13">
+      <c r="A21" s="109" t="s">
         <v>236</v>
       </c>
-      <c r="M21" s="118" t="s">
+      <c r="M21" s="109" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="118" t="s">
+    <row r="22" spans="1:13">
+      <c r="A22" s="109" t="s">
         <v>237</v>
       </c>
-      <c r="M22" s="118" t="s">
+      <c r="M22" s="109" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="118" t="s">
+    <row r="23" spans="1:13">
+      <c r="A23" s="109" t="s">
         <v>238</v>
       </c>
-      <c r="M23" s="118" t="s">
+      <c r="M23" s="109" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="118" t="s">
+    <row r="24" spans="1:13">
+      <c r="A24" s="109" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="118" t="s">
+    <row r="25" spans="1:13">
+      <c r="A25" s="109" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="118" t="s">
+    <row r="26" spans="1:13">
+      <c r="A26" s="109" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="118" t="s">
+    <row r="27" spans="1:13">
+      <c r="A27" s="109" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="118" t="s">
+    <row r="28" spans="1:13">
+      <c r="A28" s="109" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="118" t="s">
+    <row r="29" spans="1:13">
+      <c r="A29" s="109" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="118" t="s">
+    <row r="30" spans="1:13">
+      <c r="A30" s="109" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="118" t="s">
+    <row r="31" spans="1:13">
+      <c r="A31" s="109" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="118" t="s">
+    <row r="32" spans="1:13">
+      <c r="A32" s="109" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="118" t="s">
+    <row r="33" spans="1:1">
+      <c r="A33" s="109" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" s="118" t="s">
+    <row r="34" spans="1:1">
+      <c r="A34" s="109" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" s="118" t="s">
+    <row r="35" spans="1:1">
+      <c r="A35" s="109" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" s="118" t="s">
+    <row r="36" spans="1:1">
+      <c r="A36" s="109" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" s="118" t="s">
+    <row r="37" spans="1:1">
+      <c r="A37" s="109" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" s="118" t="s">
+    <row r="38" spans="1:1">
+      <c r="A38" s="109" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" s="118" t="s">
+    <row r="39" spans="1:1">
+      <c r="A39" s="109" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" s="118" t="s">
+    <row r="40" spans="1:1">
+      <c r="A40" s="109" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="106"/>
-    </row>
-    <row r="42" spans="1:1" s="120" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="119" t="s">
+    <row r="41" spans="1:1" ht="15" thickBot="1">
+      <c r="A41" s="97"/>
+    </row>
+    <row r="42" spans="1:1" s="111" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A42" s="110" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" ht="15">
       <c r="A43" s="42" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" s="118" t="s">
+    <row r="44" spans="1:1">
+      <c r="A44" s="109" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" s="118" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" s="109" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" s="118"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" s="118" t="s">
+    <row r="46" spans="1:1">
+      <c r="A46" s="109"/>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="109" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" s="118" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" s="109" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="49" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A49" s="118"/>
-    </row>
-    <row r="50" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A50" s="118" t="s">
+    <row r="49" spans="1:48">
+      <c r="A49" s="109"/>
+    </row>
+    <row r="50" spans="1:48">
+      <c r="A50" s="109" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="51" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A51" s="118" t="s">
+    <row r="51" spans="1:48">
+      <c r="A51" s="109" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="52" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A52" s="106"/>
-    </row>
-    <row r="53" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:48">
+      <c r="A52" s="97"/>
+    </row>
+    <row r="53" spans="1:48" ht="15">
       <c r="A53" s="42" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="54" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A54" s="118" t="s">
+    <row r="54" spans="1:48">
+      <c r="A54" s="109" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="55" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A55" s="106"/>
-    </row>
-    <row r="56" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:48">
+      <c r="A55" s="97"/>
+    </row>
+    <row r="56" spans="1:48" ht="15">
       <c r="A56" s="42" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="57" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:48" ht="15">
       <c r="A57" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="B57" s="121"/>
-      <c r="C57" s="121"/>
-      <c r="D57" s="121"/>
-      <c r="E57" s="121"/>
-      <c r="F57" s="121"/>
-      <c r="G57" s="121"/>
-      <c r="H57" s="121"/>
-      <c r="I57" s="121"/>
-      <c r="J57" s="121"/>
-      <c r="K57" s="121"/>
-      <c r="L57" s="121"/>
-      <c r="M57" s="121"/>
-      <c r="N57" s="121"/>
-      <c r="O57" s="121"/>
+      <c r="B57" s="112"/>
+      <c r="C57" s="112"/>
+      <c r="D57" s="112"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="112"/>
+      <c r="H57" s="112"/>
+      <c r="I57" s="112"/>
+      <c r="J57" s="112"/>
+      <c r="K57" s="112"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
       <c r="P57" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="Q57" s="121"/>
-      <c r="R57" s="121"/>
-      <c r="S57" s="121"/>
-      <c r="T57" s="121"/>
-      <c r="U57" s="121"/>
-      <c r="V57" s="121"/>
-      <c r="W57" s="121"/>
-      <c r="X57" s="121"/>
-      <c r="Y57" s="121"/>
-      <c r="Z57" s="121"/>
-      <c r="AA57" s="121"/>
-      <c r="AB57" s="121"/>
-      <c r="AC57" s="121"/>
-      <c r="AD57" s="121"/>
-      <c r="AE57" s="121"/>
-      <c r="AF57" s="121"/>
-      <c r="AG57" s="121"/>
-      <c r="AH57" s="121"/>
-      <c r="AI57" s="121"/>
+      <c r="Q57" s="112"/>
+      <c r="R57" s="112"/>
+      <c r="S57" s="112"/>
+      <c r="T57" s="112"/>
+      <c r="U57" s="112"/>
+      <c r="V57" s="112"/>
+      <c r="W57" s="112"/>
+      <c r="X57" s="112"/>
+      <c r="Y57" s="112"/>
+      <c r="Z57" s="112"/>
+      <c r="AA57" s="112"/>
+      <c r="AB57" s="112"/>
+      <c r="AC57" s="112"/>
+      <c r="AD57" s="112"/>
+      <c r="AE57" s="112"/>
+      <c r="AF57" s="112"/>
+      <c r="AG57" s="112"/>
+      <c r="AH57" s="112"/>
+      <c r="AI57" s="112"/>
       <c r="AJ57" s="42" t="s">
         <v>286</v>
       </c>
-      <c r="AK57" s="121"/>
-      <c r="AL57" s="121"/>
-      <c r="AM57" s="121"/>
-      <c r="AN57" s="121"/>
-      <c r="AO57" s="121"/>
-      <c r="AP57" s="121"/>
-      <c r="AQ57" s="121"/>
-      <c r="AR57" s="121"/>
-      <c r="AS57" s="121"/>
-      <c r="AT57" s="121"/>
-      <c r="AU57" s="121"/>
-      <c r="AV57" s="121"/>
-    </row>
-    <row r="58" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A58" s="118" t="s">
+      <c r="AK57" s="112"/>
+      <c r="AL57" s="112"/>
+      <c r="AM57" s="112"/>
+      <c r="AN57" s="112"/>
+      <c r="AO57" s="112"/>
+      <c r="AP57" s="112"/>
+      <c r="AQ57" s="112"/>
+      <c r="AR57" s="112"/>
+      <c r="AS57" s="112"/>
+      <c r="AT57" s="112"/>
+      <c r="AU57" s="112"/>
+      <c r="AV57" s="112"/>
+    </row>
+    <row r="58" spans="1:48">
+      <c r="A58" s="109" t="s">
         <v>276</v>
       </c>
-      <c r="B58" s="121"/>
-      <c r="C58" s="121"/>
-      <c r="D58" s="121"/>
-      <c r="E58" s="121"/>
-      <c r="F58" s="121"/>
-      <c r="G58" s="121"/>
-      <c r="H58" s="121"/>
-      <c r="I58" s="121"/>
-      <c r="J58" s="121"/>
-      <c r="K58" s="121"/>
-      <c r="L58" s="121"/>
-      <c r="M58" s="121"/>
-      <c r="N58" s="121"/>
-      <c r="O58" s="121"/>
-      <c r="P58" s="118" t="s">
+      <c r="B58" s="112"/>
+      <c r="C58" s="112"/>
+      <c r="D58" s="112"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="112"/>
+      <c r="H58" s="112"/>
+      <c r="I58" s="112"/>
+      <c r="J58" s="112"/>
+      <c r="K58" s="112"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="109" t="s">
         <v>281</v>
       </c>
-      <c r="Q58" s="121"/>
-      <c r="R58" s="121"/>
-      <c r="S58" s="121"/>
-      <c r="T58" s="121"/>
-      <c r="U58" s="121"/>
-      <c r="V58" s="121"/>
-      <c r="W58" s="121"/>
-      <c r="X58" s="121"/>
-      <c r="Y58" s="121"/>
-      <c r="Z58" s="121"/>
-      <c r="AA58" s="121"/>
-      <c r="AB58" s="121"/>
-      <c r="AC58" s="121"/>
-      <c r="AD58" s="121"/>
-      <c r="AE58" s="121"/>
-      <c r="AF58" s="121"/>
-      <c r="AG58" s="121"/>
-      <c r="AH58" s="121"/>
-      <c r="AI58" s="121"/>
-      <c r="AJ58" s="118" t="s">
+      <c r="Q58" s="112"/>
+      <c r="R58" s="112"/>
+      <c r="S58" s="112"/>
+      <c r="T58" s="112"/>
+      <c r="U58" s="112"/>
+      <c r="V58" s="112"/>
+      <c r="W58" s="112"/>
+      <c r="X58" s="112"/>
+      <c r="Y58" s="112"/>
+      <c r="Z58" s="112"/>
+      <c r="AA58" s="112"/>
+      <c r="AB58" s="112"/>
+      <c r="AC58" s="112"/>
+      <c r="AD58" s="112"/>
+      <c r="AE58" s="112"/>
+      <c r="AF58" s="112"/>
+      <c r="AG58" s="112"/>
+      <c r="AH58" s="112"/>
+      <c r="AI58" s="112"/>
+      <c r="AJ58" s="109" t="s">
         <v>287</v>
       </c>
-      <c r="AK58" s="121"/>
-      <c r="AL58" s="121"/>
-      <c r="AM58" s="121"/>
-      <c r="AN58" s="121"/>
-      <c r="AO58" s="121"/>
-      <c r="AP58" s="121"/>
-      <c r="AQ58" s="121"/>
-      <c r="AR58" s="121"/>
-      <c r="AS58" s="121"/>
-      <c r="AT58" s="121"/>
-      <c r="AU58" s="121"/>
-      <c r="AV58" s="121"/>
-    </row>
-    <row r="59" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A59" s="118" t="s">
+      <c r="AK58" s="112"/>
+      <c r="AL58" s="112"/>
+      <c r="AM58" s="112"/>
+      <c r="AN58" s="112"/>
+      <c r="AO58" s="112"/>
+      <c r="AP58" s="112"/>
+      <c r="AQ58" s="112"/>
+      <c r="AR58" s="112"/>
+      <c r="AS58" s="112"/>
+      <c r="AT58" s="112"/>
+      <c r="AU58" s="112"/>
+      <c r="AV58" s="112"/>
+    </row>
+    <row r="59" spans="1:48">
+      <c r="A59" s="109" t="s">
         <v>277</v>
       </c>
-      <c r="B59" s="121"/>
-      <c r="C59" s="121"/>
-      <c r="D59" s="121"/>
-      <c r="E59" s="121"/>
-      <c r="F59" s="121"/>
-      <c r="G59" s="121"/>
-      <c r="H59" s="121"/>
-      <c r="I59" s="121"/>
-      <c r="J59" s="121"/>
-      <c r="K59" s="121"/>
-      <c r="L59" s="121"/>
-      <c r="M59" s="121"/>
-      <c r="N59" s="121"/>
-      <c r="O59" s="121"/>
-      <c r="P59" s="118" t="s">
+      <c r="B59" s="112"/>
+      <c r="C59" s="112"/>
+      <c r="D59" s="112"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="112"/>
+      <c r="H59" s="112"/>
+      <c r="I59" s="112"/>
+      <c r="J59" s="112"/>
+      <c r="K59" s="112"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="109" t="s">
         <v>282</v>
       </c>
-      <c r="Q59" s="121"/>
-      <c r="R59" s="121"/>
-      <c r="S59" s="121"/>
-      <c r="T59" s="121"/>
-      <c r="U59" s="121"/>
-      <c r="V59" s="121"/>
-      <c r="W59" s="121"/>
-      <c r="X59" s="121"/>
-      <c r="Y59" s="121"/>
-      <c r="Z59" s="121"/>
-      <c r="AA59" s="121"/>
-      <c r="AB59" s="121"/>
-      <c r="AC59" s="121"/>
-      <c r="AD59" s="121"/>
-      <c r="AE59" s="121"/>
-      <c r="AF59" s="121"/>
-      <c r="AG59" s="121"/>
-      <c r="AH59" s="121"/>
-      <c r="AI59" s="121"/>
-      <c r="AJ59" s="118" t="s">
+      <c r="Q59" s="112"/>
+      <c r="R59" s="112"/>
+      <c r="S59" s="112"/>
+      <c r="T59" s="112"/>
+      <c r="U59" s="112"/>
+      <c r="V59" s="112"/>
+      <c r="W59" s="112"/>
+      <c r="X59" s="112"/>
+      <c r="Y59" s="112"/>
+      <c r="Z59" s="112"/>
+      <c r="AA59" s="112"/>
+      <c r="AB59" s="112"/>
+      <c r="AC59" s="112"/>
+      <c r="AD59" s="112"/>
+      <c r="AE59" s="112"/>
+      <c r="AF59" s="112"/>
+      <c r="AG59" s="112"/>
+      <c r="AH59" s="112"/>
+      <c r="AI59" s="112"/>
+      <c r="AJ59" s="109" t="s">
         <v>288</v>
       </c>
-      <c r="AK59" s="121"/>
-      <c r="AL59" s="121"/>
-      <c r="AM59" s="121"/>
-      <c r="AN59" s="121"/>
-      <c r="AO59" s="121"/>
-      <c r="AP59" s="121"/>
-      <c r="AQ59" s="121"/>
-      <c r="AR59" s="121"/>
-      <c r="AS59" s="121"/>
-      <c r="AT59" s="121"/>
-      <c r="AU59" s="121"/>
-      <c r="AV59" s="121"/>
-    </row>
-    <row r="60" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A60" s="118" t="s">
+      <c r="AK59" s="112"/>
+      <c r="AL59" s="112"/>
+      <c r="AM59" s="112"/>
+      <c r="AN59" s="112"/>
+      <c r="AO59" s="112"/>
+      <c r="AP59" s="112"/>
+      <c r="AQ59" s="112"/>
+      <c r="AR59" s="112"/>
+      <c r="AS59" s="112"/>
+      <c r="AT59" s="112"/>
+      <c r="AU59" s="112"/>
+      <c r="AV59" s="112"/>
+    </row>
+    <row r="60" spans="1:48">
+      <c r="A60" s="109" t="s">
         <v>278</v>
       </c>
-      <c r="B60" s="121"/>
-      <c r="C60" s="121"/>
-      <c r="D60" s="121"/>
-      <c r="E60" s="121"/>
-      <c r="F60" s="121"/>
-      <c r="G60" s="121"/>
-      <c r="H60" s="121"/>
-      <c r="I60" s="121"/>
-      <c r="J60" s="121"/>
-      <c r="K60" s="121"/>
-      <c r="L60" s="121"/>
-      <c r="M60" s="121"/>
-      <c r="N60" s="121"/>
-      <c r="O60" s="121"/>
-      <c r="P60" s="118" t="s">
+      <c r="B60" s="112"/>
+      <c r="C60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="112"/>
+      <c r="L60" s="112"/>
+      <c r="M60" s="112"/>
+      <c r="N60" s="112"/>
+      <c r="O60" s="112"/>
+      <c r="P60" s="109" t="s">
         <v>283</v>
       </c>
-      <c r="Q60" s="121"/>
-      <c r="R60" s="121"/>
-      <c r="S60" s="121"/>
-      <c r="T60" s="121"/>
-      <c r="U60" s="121"/>
-      <c r="V60" s="121"/>
-      <c r="W60" s="121"/>
-      <c r="X60" s="121"/>
-      <c r="Y60" s="121"/>
-      <c r="Z60" s="121"/>
-      <c r="AA60" s="121"/>
-      <c r="AB60" s="121"/>
-      <c r="AC60" s="121"/>
-      <c r="AD60" s="121"/>
-      <c r="AE60" s="121"/>
-      <c r="AF60" s="121"/>
-      <c r="AG60" s="121"/>
-      <c r="AH60" s="121"/>
-      <c r="AI60" s="121"/>
-      <c r="AJ60" s="118" t="s">
+      <c r="Q60" s="112"/>
+      <c r="R60" s="112"/>
+      <c r="S60" s="112"/>
+      <c r="T60" s="112"/>
+      <c r="U60" s="112"/>
+      <c r="V60" s="112"/>
+      <c r="W60" s="112"/>
+      <c r="X60" s="112"/>
+      <c r="Y60" s="112"/>
+      <c r="Z60" s="112"/>
+      <c r="AA60" s="112"/>
+      <c r="AB60" s="112"/>
+      <c r="AC60" s="112"/>
+      <c r="AD60" s="112"/>
+      <c r="AE60" s="112"/>
+      <c r="AF60" s="112"/>
+      <c r="AG60" s="112"/>
+      <c r="AH60" s="112"/>
+      <c r="AI60" s="112"/>
+      <c r="AJ60" s="109" t="s">
         <v>289</v>
       </c>
-      <c r="AK60" s="121"/>
-      <c r="AL60" s="121"/>
-      <c r="AM60" s="121"/>
-      <c r="AN60" s="121"/>
-      <c r="AO60" s="121"/>
-      <c r="AP60" s="121"/>
-      <c r="AQ60" s="121"/>
-      <c r="AR60" s="121"/>
-      <c r="AS60" s="121"/>
-      <c r="AT60" s="121"/>
-      <c r="AU60" s="121"/>
-      <c r="AV60" s="121"/>
-    </row>
-    <row r="61" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A61" s="118" t="s">
+      <c r="AK60" s="112"/>
+      <c r="AL60" s="112"/>
+      <c r="AM60" s="112"/>
+      <c r="AN60" s="112"/>
+      <c r="AO60" s="112"/>
+      <c r="AP60" s="112"/>
+      <c r="AQ60" s="112"/>
+      <c r="AR60" s="112"/>
+      <c r="AS60" s="112"/>
+      <c r="AT60" s="112"/>
+      <c r="AU60" s="112"/>
+      <c r="AV60" s="112"/>
+    </row>
+    <row r="61" spans="1:48">
+      <c r="A61" s="109" t="s">
         <v>279</v>
       </c>
-      <c r="B61" s="121"/>
-      <c r="C61" s="121"/>
-      <c r="D61" s="121"/>
-      <c r="E61" s="121"/>
-      <c r="F61" s="121"/>
-      <c r="G61" s="121"/>
-      <c r="H61" s="121"/>
-      <c r="I61" s="121"/>
-      <c r="J61" s="121"/>
-      <c r="K61" s="121"/>
-      <c r="L61" s="121"/>
-      <c r="M61" s="121"/>
-      <c r="N61" s="121"/>
-      <c r="O61" s="121"/>
-      <c r="P61" s="118" t="s">
+      <c r="B61" s="112"/>
+      <c r="C61" s="112"/>
+      <c r="D61" s="112"/>
+      <c r="E61" s="112"/>
+      <c r="F61" s="112"/>
+      <c r="G61" s="112"/>
+      <c r="H61" s="112"/>
+      <c r="I61" s="112"/>
+      <c r="J61" s="112"/>
+      <c r="K61" s="112"/>
+      <c r="L61" s="112"/>
+      <c r="M61" s="112"/>
+      <c r="N61" s="112"/>
+      <c r="O61" s="112"/>
+      <c r="P61" s="109" t="s">
         <v>284</v>
       </c>
-      <c r="Q61" s="121"/>
-      <c r="R61" s="121"/>
-      <c r="S61" s="121"/>
-      <c r="T61" s="121"/>
-      <c r="U61" s="121"/>
-      <c r="V61" s="121"/>
-      <c r="W61" s="121"/>
-      <c r="X61" s="121"/>
-      <c r="Y61" s="121"/>
-      <c r="Z61" s="121"/>
-      <c r="AA61" s="121"/>
-      <c r="AB61" s="121"/>
-      <c r="AC61" s="121"/>
-      <c r="AD61" s="121"/>
-      <c r="AE61" s="121"/>
-      <c r="AF61" s="121"/>
-      <c r="AG61" s="121"/>
-      <c r="AH61" s="121"/>
-      <c r="AI61" s="121"/>
-      <c r="AJ61" s="118" t="s">
+      <c r="Q61" s="112"/>
+      <c r="R61" s="112"/>
+      <c r="S61" s="112"/>
+      <c r="T61" s="112"/>
+      <c r="U61" s="112"/>
+      <c r="V61" s="112"/>
+      <c r="W61" s="112"/>
+      <c r="X61" s="112"/>
+      <c r="Y61" s="112"/>
+      <c r="Z61" s="112"/>
+      <c r="AA61" s="112"/>
+      <c r="AB61" s="112"/>
+      <c r="AC61" s="112"/>
+      <c r="AD61" s="112"/>
+      <c r="AE61" s="112"/>
+      <c r="AF61" s="112"/>
+      <c r="AG61" s="112"/>
+      <c r="AH61" s="112"/>
+      <c r="AI61" s="112"/>
+      <c r="AJ61" s="109" t="s">
         <v>290</v>
       </c>
-      <c r="AK61" s="121"/>
-      <c r="AL61" s="121"/>
-      <c r="AM61" s="121"/>
-      <c r="AN61" s="121"/>
-      <c r="AO61" s="121"/>
-      <c r="AP61" s="121"/>
-      <c r="AQ61" s="121"/>
-      <c r="AR61" s="121"/>
-      <c r="AS61" s="121"/>
-      <c r="AT61" s="121"/>
-      <c r="AU61" s="121"/>
-      <c r="AV61" s="121"/>
-    </row>
-    <row r="62" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A62" s="122"/>
-      <c r="B62" s="121"/>
-      <c r="C62" s="121"/>
-      <c r="D62" s="121"/>
-      <c r="E62" s="121"/>
-      <c r="F62" s="121"/>
-      <c r="G62" s="121"/>
-      <c r="H62" s="121"/>
-      <c r="I62" s="121"/>
-      <c r="J62" s="121"/>
-      <c r="K62" s="121"/>
-      <c r="L62" s="121"/>
-      <c r="M62" s="121"/>
-      <c r="N62" s="121"/>
-      <c r="O62" s="121"/>
-      <c r="P62" s="118" t="s">
+      <c r="AK61" s="112"/>
+      <c r="AL61" s="112"/>
+      <c r="AM61" s="112"/>
+      <c r="AN61" s="112"/>
+      <c r="AO61" s="112"/>
+      <c r="AP61" s="112"/>
+      <c r="AQ61" s="112"/>
+      <c r="AR61" s="112"/>
+      <c r="AS61" s="112"/>
+      <c r="AT61" s="112"/>
+      <c r="AU61" s="112"/>
+      <c r="AV61" s="112"/>
+    </row>
+    <row r="62" spans="1:48">
+      <c r="A62" s="113"/>
+      <c r="B62" s="112"/>
+      <c r="C62" s="112"/>
+      <c r="D62" s="112"/>
+      <c r="E62" s="112"/>
+      <c r="F62" s="112"/>
+      <c r="G62" s="112"/>
+      <c r="H62" s="112"/>
+      <c r="I62" s="112"/>
+      <c r="J62" s="112"/>
+      <c r="K62" s="112"/>
+      <c r="L62" s="112"/>
+      <c r="M62" s="112"/>
+      <c r="N62" s="112"/>
+      <c r="O62" s="112"/>
+      <c r="P62" s="109" t="s">
         <v>285</v>
       </c>
-      <c r="Q62" s="121"/>
-      <c r="R62" s="121"/>
-      <c r="S62" s="121"/>
-      <c r="T62" s="121"/>
-      <c r="U62" s="121"/>
-      <c r="V62" s="121"/>
-      <c r="W62" s="121"/>
-      <c r="X62" s="121"/>
-      <c r="Y62" s="121"/>
-      <c r="Z62" s="121"/>
-      <c r="AA62" s="121"/>
-      <c r="AB62" s="121"/>
-      <c r="AC62" s="121"/>
-      <c r="AD62" s="121"/>
-      <c r="AE62" s="121"/>
-      <c r="AF62" s="121"/>
-      <c r="AG62" s="121"/>
-      <c r="AH62" s="121"/>
-      <c r="AI62" s="121"/>
-      <c r="AJ62" s="118" t="s">
+      <c r="Q62" s="112"/>
+      <c r="R62" s="112"/>
+      <c r="S62" s="112"/>
+      <c r="T62" s="112"/>
+      <c r="U62" s="112"/>
+      <c r="V62" s="112"/>
+      <c r="W62" s="112"/>
+      <c r="X62" s="112"/>
+      <c r="Y62" s="112"/>
+      <c r="Z62" s="112"/>
+      <c r="AA62" s="112"/>
+      <c r="AB62" s="112"/>
+      <c r="AC62" s="112"/>
+      <c r="AD62" s="112"/>
+      <c r="AE62" s="112"/>
+      <c r="AF62" s="112"/>
+      <c r="AG62" s="112"/>
+      <c r="AH62" s="112"/>
+      <c r="AI62" s="112"/>
+      <c r="AJ62" s="109" t="s">
         <v>291</v>
       </c>
-      <c r="AK62" s="121"/>
-      <c r="AL62" s="121"/>
-      <c r="AM62" s="121"/>
-      <c r="AN62" s="121"/>
-      <c r="AO62" s="121"/>
-      <c r="AP62" s="121"/>
-      <c r="AQ62" s="121"/>
-      <c r="AR62" s="121"/>
-      <c r="AS62" s="121"/>
-      <c r="AT62" s="121"/>
-      <c r="AU62" s="121"/>
-      <c r="AV62" s="121"/>
-    </row>
-    <row r="63" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A63" s="121"/>
-      <c r="B63" s="121"/>
-      <c r="C63" s="121"/>
-      <c r="D63" s="121"/>
-      <c r="E63" s="121"/>
-      <c r="F63" s="121"/>
-      <c r="G63" s="121"/>
-      <c r="H63" s="121"/>
-      <c r="I63" s="121"/>
-      <c r="J63" s="121"/>
-      <c r="K63" s="121"/>
-      <c r="L63" s="121"/>
-      <c r="M63" s="121"/>
-      <c r="N63" s="121"/>
-      <c r="O63" s="121"/>
-      <c r="P63" s="121"/>
-      <c r="Q63" s="121"/>
-      <c r="R63" s="121"/>
-      <c r="S63" s="121"/>
-      <c r="T63" s="121"/>
-      <c r="U63" s="121"/>
-      <c r="V63" s="121"/>
-      <c r="W63" s="121"/>
-      <c r="X63" s="121"/>
-      <c r="Y63" s="121"/>
-      <c r="Z63" s="121"/>
-      <c r="AA63" s="121"/>
-      <c r="AB63" s="121"/>
-      <c r="AC63" s="121"/>
-      <c r="AD63" s="121"/>
-      <c r="AE63" s="121"/>
-      <c r="AF63" s="121"/>
-      <c r="AG63" s="121"/>
-      <c r="AH63" s="121"/>
-      <c r="AI63" s="121"/>
-      <c r="AJ63" s="118" t="s">
+      <c r="AK62" s="112"/>
+      <c r="AL62" s="112"/>
+      <c r="AM62" s="112"/>
+      <c r="AN62" s="112"/>
+      <c r="AO62" s="112"/>
+      <c r="AP62" s="112"/>
+      <c r="AQ62" s="112"/>
+      <c r="AR62" s="112"/>
+      <c r="AS62" s="112"/>
+      <c r="AT62" s="112"/>
+      <c r="AU62" s="112"/>
+      <c r="AV62" s="112"/>
+    </row>
+    <row r="63" spans="1:48">
+      <c r="A63" s="112"/>
+      <c r="B63" s="112"/>
+      <c r="C63" s="112"/>
+      <c r="D63" s="112"/>
+      <c r="E63" s="112"/>
+      <c r="F63" s="112"/>
+      <c r="G63" s="112"/>
+      <c r="H63" s="112"/>
+      <c r="I63" s="112"/>
+      <c r="J63" s="112"/>
+      <c r="K63" s="112"/>
+      <c r="L63" s="112"/>
+      <c r="M63" s="112"/>
+      <c r="N63" s="112"/>
+      <c r="O63" s="112"/>
+      <c r="P63" s="112"/>
+      <c r="Q63" s="112"/>
+      <c r="R63" s="112"/>
+      <c r="S63" s="112"/>
+      <c r="T63" s="112"/>
+      <c r="U63" s="112"/>
+      <c r="V63" s="112"/>
+      <c r="W63" s="112"/>
+      <c r="X63" s="112"/>
+      <c r="Y63" s="112"/>
+      <c r="Z63" s="112"/>
+      <c r="AA63" s="112"/>
+      <c r="AB63" s="112"/>
+      <c r="AC63" s="112"/>
+      <c r="AD63" s="112"/>
+      <c r="AE63" s="112"/>
+      <c r="AF63" s="112"/>
+      <c r="AG63" s="112"/>
+      <c r="AH63" s="112"/>
+      <c r="AI63" s="112"/>
+      <c r="AJ63" s="109" t="s">
         <v>292</v>
       </c>
-      <c r="AK63" s="121"/>
-      <c r="AL63" s="121"/>
-      <c r="AM63" s="121"/>
-      <c r="AN63" s="121"/>
-      <c r="AO63" s="121"/>
-      <c r="AP63" s="121"/>
-      <c r="AQ63" s="121"/>
-      <c r="AR63" s="121"/>
-      <c r="AS63" s="121"/>
-      <c r="AT63" s="121"/>
-      <c r="AU63" s="121"/>
-      <c r="AV63" s="121"/>
-    </row>
-    <row r="64" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A64" s="121"/>
-      <c r="B64" s="121"/>
-      <c r="C64" s="121"/>
-      <c r="D64" s="121"/>
-      <c r="E64" s="121"/>
-      <c r="F64" s="121"/>
-      <c r="G64" s="121"/>
-      <c r="H64" s="121"/>
-      <c r="I64" s="121"/>
-      <c r="J64" s="121"/>
-      <c r="K64" s="121"/>
-      <c r="L64" s="121"/>
-      <c r="M64" s="121"/>
-      <c r="N64" s="121"/>
-      <c r="O64" s="121"/>
-      <c r="P64" s="121"/>
-      <c r="Q64" s="121"/>
-      <c r="R64" s="121"/>
-      <c r="S64" s="121"/>
-      <c r="T64" s="121"/>
-      <c r="U64" s="121"/>
-      <c r="V64" s="121"/>
-      <c r="W64" s="121"/>
-      <c r="X64" s="121"/>
-      <c r="Y64" s="121"/>
-      <c r="Z64" s="121"/>
-      <c r="AA64" s="121"/>
-      <c r="AB64" s="121"/>
-      <c r="AC64" s="121"/>
-      <c r="AD64" s="121"/>
-      <c r="AE64" s="121"/>
-      <c r="AF64" s="121"/>
-      <c r="AG64" s="121"/>
-      <c r="AH64" s="121"/>
-      <c r="AI64" s="121"/>
-      <c r="AJ64" s="118" t="s">
+      <c r="AK63" s="112"/>
+      <c r="AL63" s="112"/>
+      <c r="AM63" s="112"/>
+      <c r="AN63" s="112"/>
+      <c r="AO63" s="112"/>
+      <c r="AP63" s="112"/>
+      <c r="AQ63" s="112"/>
+      <c r="AR63" s="112"/>
+      <c r="AS63" s="112"/>
+      <c r="AT63" s="112"/>
+      <c r="AU63" s="112"/>
+      <c r="AV63" s="112"/>
+    </row>
+    <row r="64" spans="1:48">
+      <c r="A64" s="112"/>
+      <c r="B64" s="112"/>
+      <c r="C64" s="112"/>
+      <c r="D64" s="112"/>
+      <c r="E64" s="112"/>
+      <c r="F64" s="112"/>
+      <c r="G64" s="112"/>
+      <c r="H64" s="112"/>
+      <c r="I64" s="112"/>
+      <c r="J64" s="112"/>
+      <c r="K64" s="112"/>
+      <c r="L64" s="112"/>
+      <c r="M64" s="112"/>
+      <c r="N64" s="112"/>
+      <c r="O64" s="112"/>
+      <c r="P64" s="112"/>
+      <c r="Q64" s="112"/>
+      <c r="R64" s="112"/>
+      <c r="S64" s="112"/>
+      <c r="T64" s="112"/>
+      <c r="U64" s="112"/>
+      <c r="V64" s="112"/>
+      <c r="W64" s="112"/>
+      <c r="X64" s="112"/>
+      <c r="Y64" s="112"/>
+      <c r="Z64" s="112"/>
+      <c r="AA64" s="112"/>
+      <c r="AB64" s="112"/>
+      <c r="AC64" s="112"/>
+      <c r="AD64" s="112"/>
+      <c r="AE64" s="112"/>
+      <c r="AF64" s="112"/>
+      <c r="AG64" s="112"/>
+      <c r="AH64" s="112"/>
+      <c r="AI64" s="112"/>
+      <c r="AJ64" s="109" t="s">
         <v>293</v>
       </c>
-      <c r="AK64" s="121"/>
-      <c r="AL64" s="121"/>
-      <c r="AM64" s="121"/>
-      <c r="AN64" s="121"/>
-      <c r="AO64" s="121"/>
-      <c r="AP64" s="121"/>
-      <c r="AQ64" s="121"/>
-      <c r="AR64" s="121"/>
-      <c r="AS64" s="121"/>
-      <c r="AT64" s="121"/>
-      <c r="AU64" s="121"/>
-      <c r="AV64" s="121"/>
-    </row>
-    <row r="65" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A65" s="122"/>
-      <c r="B65" s="121"/>
-      <c r="C65" s="121"/>
-      <c r="D65" s="121"/>
-      <c r="E65" s="121"/>
-      <c r="F65" s="121"/>
-      <c r="G65" s="121"/>
-      <c r="H65" s="121"/>
-      <c r="I65" s="121"/>
-      <c r="J65" s="121"/>
-      <c r="K65" s="121"/>
-      <c r="L65" s="121"/>
-      <c r="M65" s="121"/>
-      <c r="N65" s="121"/>
-      <c r="O65" s="121"/>
-      <c r="P65" s="121"/>
-      <c r="Q65" s="121"/>
-      <c r="R65" s="121"/>
-      <c r="S65" s="121"/>
-      <c r="T65" s="121"/>
-      <c r="U65" s="121"/>
-      <c r="V65" s="121"/>
-      <c r="W65" s="121"/>
-      <c r="X65" s="121"/>
-      <c r="Y65" s="121"/>
-      <c r="Z65" s="121"/>
-      <c r="AA65" s="121"/>
-      <c r="AB65" s="121"/>
-      <c r="AC65" s="121"/>
-      <c r="AD65" s="121"/>
-      <c r="AE65" s="121"/>
-      <c r="AF65" s="121"/>
-      <c r="AG65" s="121"/>
-      <c r="AH65" s="121"/>
-      <c r="AI65" s="121"/>
-      <c r="AJ65" s="121"/>
-      <c r="AK65" s="121"/>
-      <c r="AL65" s="121"/>
-      <c r="AM65" s="121"/>
-      <c r="AN65" s="121"/>
-      <c r="AO65" s="121"/>
-      <c r="AP65" s="121"/>
-      <c r="AQ65" s="121"/>
-      <c r="AR65" s="121"/>
-      <c r="AS65" s="121"/>
-      <c r="AT65" s="121"/>
-      <c r="AU65" s="121"/>
-      <c r="AV65" s="121"/>
-    </row>
-    <row r="66" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+      <c r="AK64" s="112"/>
+      <c r="AL64" s="112"/>
+      <c r="AM64" s="112"/>
+      <c r="AN64" s="112"/>
+      <c r="AO64" s="112"/>
+      <c r="AP64" s="112"/>
+      <c r="AQ64" s="112"/>
+      <c r="AR64" s="112"/>
+      <c r="AS64" s="112"/>
+      <c r="AT64" s="112"/>
+      <c r="AU64" s="112"/>
+      <c r="AV64" s="112"/>
+    </row>
+    <row r="65" spans="1:48">
+      <c r="A65" s="113"/>
+      <c r="B65" s="112"/>
+      <c r="C65" s="112"/>
+      <c r="D65" s="112"/>
+      <c r="E65" s="112"/>
+      <c r="F65" s="112"/>
+      <c r="G65" s="112"/>
+      <c r="H65" s="112"/>
+      <c r="I65" s="112"/>
+      <c r="J65" s="112"/>
+      <c r="K65" s="112"/>
+      <c r="L65" s="112"/>
+      <c r="M65" s="112"/>
+      <c r="N65" s="112"/>
+      <c r="O65" s="112"/>
+      <c r="P65" s="112"/>
+      <c r="Q65" s="112"/>
+      <c r="R65" s="112"/>
+      <c r="S65" s="112"/>
+      <c r="T65" s="112"/>
+      <c r="U65" s="112"/>
+      <c r="V65" s="112"/>
+      <c r="W65" s="112"/>
+      <c r="X65" s="112"/>
+      <c r="Y65" s="112"/>
+      <c r="Z65" s="112"/>
+      <c r="AA65" s="112"/>
+      <c r="AB65" s="112"/>
+      <c r="AC65" s="112"/>
+      <c r="AD65" s="112"/>
+      <c r="AE65" s="112"/>
+      <c r="AF65" s="112"/>
+      <c r="AG65" s="112"/>
+      <c r="AH65" s="112"/>
+      <c r="AI65" s="112"/>
+      <c r="AJ65" s="112"/>
+      <c r="AK65" s="112"/>
+      <c r="AL65" s="112"/>
+      <c r="AM65" s="112"/>
+      <c r="AN65" s="112"/>
+      <c r="AO65" s="112"/>
+      <c r="AP65" s="112"/>
+      <c r="AQ65" s="112"/>
+      <c r="AR65" s="112"/>
+      <c r="AS65" s="112"/>
+      <c r="AT65" s="112"/>
+      <c r="AU65" s="112"/>
+      <c r="AV65" s="112"/>
+    </row>
+    <row r="66" spans="1:48" ht="15">
       <c r="A66" s="42" t="s">
         <v>294</v>
       </c>
-      <c r="B66" s="121"/>
-      <c r="C66" s="121"/>
-      <c r="D66" s="121"/>
-      <c r="E66" s="121"/>
-      <c r="F66" s="121"/>
-      <c r="G66" s="121"/>
-      <c r="H66" s="121"/>
-      <c r="I66" s="121"/>
-      <c r="J66" s="121"/>
-      <c r="K66" s="121"/>
-      <c r="L66" s="121"/>
-      <c r="M66" s="121"/>
-      <c r="N66" s="121"/>
-      <c r="O66" s="121"/>
+      <c r="B66" s="112"/>
+      <c r="C66" s="112"/>
+      <c r="D66" s="112"/>
+      <c r="E66" s="112"/>
+      <c r="F66" s="112"/>
+      <c r="G66" s="112"/>
+      <c r="H66" s="112"/>
+      <c r="I66" s="112"/>
+      <c r="J66" s="112"/>
+      <c r="K66" s="112"/>
+      <c r="L66" s="112"/>
+      <c r="M66" s="112"/>
+      <c r="N66" s="112"/>
+      <c r="O66" s="112"/>
       <c r="P66" s="42" t="s">
         <v>304</v>
       </c>
-      <c r="Q66" s="121"/>
-      <c r="R66" s="121"/>
-      <c r="S66" s="121"/>
-      <c r="T66" s="121"/>
-      <c r="U66" s="121"/>
-      <c r="V66" s="121"/>
-      <c r="W66" s="121"/>
-      <c r="X66" s="121"/>
-      <c r="Y66" s="121"/>
-      <c r="Z66" s="121"/>
-      <c r="AA66" s="121"/>
-      <c r="AB66" s="121"/>
-      <c r="AC66" s="121"/>
-      <c r="AD66" s="121"/>
-      <c r="AE66" s="121"/>
-      <c r="AF66" s="121"/>
-      <c r="AG66" s="121"/>
-      <c r="AH66" s="121"/>
-      <c r="AI66" s="121"/>
+      <c r="Q66" s="112"/>
+      <c r="R66" s="112"/>
+      <c r="S66" s="112"/>
+      <c r="T66" s="112"/>
+      <c r="U66" s="112"/>
+      <c r="V66" s="112"/>
+      <c r="W66" s="112"/>
+      <c r="X66" s="112"/>
+      <c r="Y66" s="112"/>
+      <c r="Z66" s="112"/>
+      <c r="AA66" s="112"/>
+      <c r="AB66" s="112"/>
+      <c r="AC66" s="112"/>
+      <c r="AD66" s="112"/>
+      <c r="AE66" s="112"/>
+      <c r="AF66" s="112"/>
+      <c r="AG66" s="112"/>
+      <c r="AH66" s="112"/>
+      <c r="AI66" s="112"/>
       <c r="AJ66" s="42" t="s">
         <v>312</v>
       </c>
-      <c r="AK66" s="121"/>
-      <c r="AL66" s="121"/>
-      <c r="AM66" s="121"/>
-      <c r="AN66" s="121"/>
-      <c r="AO66" s="121"/>
-      <c r="AP66" s="121"/>
-      <c r="AQ66" s="121"/>
-      <c r="AR66" s="121"/>
-      <c r="AS66" s="121"/>
-      <c r="AT66" s="121"/>
-      <c r="AU66" s="121"/>
-      <c r="AV66" s="121"/>
-    </row>
-    <row r="67" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A67" s="118" t="s">
+      <c r="AK66" s="112"/>
+      <c r="AL66" s="112"/>
+      <c r="AM66" s="112"/>
+      <c r="AN66" s="112"/>
+      <c r="AO66" s="112"/>
+      <c r="AP66" s="112"/>
+      <c r="AQ66" s="112"/>
+      <c r="AR66" s="112"/>
+      <c r="AS66" s="112"/>
+      <c r="AT66" s="112"/>
+      <c r="AU66" s="112"/>
+      <c r="AV66" s="112"/>
+    </row>
+    <row r="67" spans="1:48">
+      <c r="A67" s="109" t="s">
         <v>295</v>
       </c>
-      <c r="B67" s="121"/>
-      <c r="C67" s="121"/>
-      <c r="D67" s="121"/>
-      <c r="E67" s="121"/>
-      <c r="F67" s="121"/>
-      <c r="G67" s="121"/>
-      <c r="H67" s="121"/>
-      <c r="I67" s="121"/>
-      <c r="J67" s="121"/>
-      <c r="K67" s="121"/>
-      <c r="L67" s="121"/>
-      <c r="M67" s="121"/>
-      <c r="N67" s="121"/>
-      <c r="O67" s="121"/>
-      <c r="P67" s="118" t="s">
+      <c r="B67" s="112"/>
+      <c r="C67" s="112"/>
+      <c r="D67" s="112"/>
+      <c r="E67" s="112"/>
+      <c r="F67" s="112"/>
+      <c r="G67" s="112"/>
+      <c r="H67" s="112"/>
+      <c r="I67" s="112"/>
+      <c r="J67" s="112"/>
+      <c r="K67" s="112"/>
+      <c r="L67" s="112"/>
+      <c r="M67" s="112"/>
+      <c r="N67" s="112"/>
+      <c r="O67" s="112"/>
+      <c r="P67" s="109" t="s">
         <v>305</v>
       </c>
-      <c r="Q67" s="121"/>
-      <c r="R67" s="121"/>
-      <c r="S67" s="121"/>
-      <c r="T67" s="121"/>
-      <c r="U67" s="121"/>
-      <c r="V67" s="121"/>
-      <c r="W67" s="121"/>
-      <c r="X67" s="121"/>
-      <c r="Y67" s="121"/>
-      <c r="Z67" s="121"/>
-      <c r="AA67" s="121"/>
-      <c r="AB67" s="121"/>
-      <c r="AC67" s="121"/>
-      <c r="AD67" s="121"/>
-      <c r="AE67" s="121"/>
-      <c r="AF67" s="121"/>
-      <c r="AG67" s="121"/>
-      <c r="AH67" s="121"/>
-      <c r="AI67" s="121"/>
-      <c r="AJ67" s="118" t="s">
+      <c r="Q67" s="112"/>
+      <c r="R67" s="112"/>
+      <c r="S67" s="112"/>
+      <c r="T67" s="112"/>
+      <c r="U67" s="112"/>
+      <c r="V67" s="112"/>
+      <c r="W67" s="112"/>
+      <c r="X67" s="112"/>
+      <c r="Y67" s="112"/>
+      <c r="Z67" s="112"/>
+      <c r="AA67" s="112"/>
+      <c r="AB67" s="112"/>
+      <c r="AC67" s="112"/>
+      <c r="AD67" s="112"/>
+      <c r="AE67" s="112"/>
+      <c r="AF67" s="112"/>
+      <c r="AG67" s="112"/>
+      <c r="AH67" s="112"/>
+      <c r="AI67" s="112"/>
+      <c r="AJ67" s="109" t="s">
         <v>313</v>
       </c>
-      <c r="AK67" s="121"/>
-      <c r="AL67" s="121"/>
-      <c r="AM67" s="121"/>
-      <c r="AN67" s="121"/>
-      <c r="AO67" s="121"/>
-      <c r="AP67" s="121"/>
-      <c r="AQ67" s="121"/>
-      <c r="AR67" s="121"/>
-      <c r="AS67" s="121"/>
-      <c r="AT67" s="121"/>
-      <c r="AU67" s="121"/>
-      <c r="AV67" s="121"/>
-    </row>
-    <row r="68" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A68" s="118" t="s">
+      <c r="AK67" s="112"/>
+      <c r="AL67" s="112"/>
+      <c r="AM67" s="112"/>
+      <c r="AN67" s="112"/>
+      <c r="AO67" s="112"/>
+      <c r="AP67" s="112"/>
+      <c r="AQ67" s="112"/>
+      <c r="AR67" s="112"/>
+      <c r="AS67" s="112"/>
+      <c r="AT67" s="112"/>
+      <c r="AU67" s="112"/>
+      <c r="AV67" s="112"/>
+    </row>
+    <row r="68" spans="1:48">
+      <c r="A68" s="109" t="s">
         <v>296</v>
       </c>
-      <c r="B68" s="121"/>
-      <c r="C68" s="121"/>
-      <c r="D68" s="121"/>
-      <c r="E68" s="121"/>
-      <c r="F68" s="121"/>
-      <c r="G68" s="121"/>
-      <c r="H68" s="121"/>
-      <c r="I68" s="121"/>
-      <c r="J68" s="121"/>
-      <c r="K68" s="121"/>
-      <c r="L68" s="121"/>
-      <c r="M68" s="121"/>
-      <c r="N68" s="121"/>
-      <c r="O68" s="121"/>
-      <c r="P68" s="118" t="s">
+      <c r="B68" s="112"/>
+      <c r="C68" s="112"/>
+      <c r="D68" s="112"/>
+      <c r="E68" s="112"/>
+      <c r="F68" s="112"/>
+      <c r="G68" s="112"/>
+      <c r="H68" s="112"/>
+      <c r="I68" s="112"/>
+      <c r="J68" s="112"/>
+      <c r="K68" s="112"/>
+      <c r="L68" s="112"/>
+      <c r="M68" s="112"/>
+      <c r="N68" s="112"/>
+      <c r="O68" s="112"/>
+      <c r="P68" s="109" t="s">
         <v>306</v>
       </c>
-      <c r="Q68" s="121"/>
-      <c r="R68" s="121"/>
-      <c r="S68" s="121"/>
-      <c r="T68" s="121"/>
-      <c r="U68" s="121"/>
-      <c r="V68" s="121"/>
-      <c r="W68" s="121"/>
-      <c r="X68" s="121"/>
-      <c r="Y68" s="121"/>
-      <c r="Z68" s="121"/>
-      <c r="AA68" s="121"/>
-      <c r="AB68" s="121"/>
-      <c r="AC68" s="121"/>
-      <c r="AD68" s="121"/>
-      <c r="AE68" s="121"/>
-      <c r="AF68" s="121"/>
-      <c r="AG68" s="121"/>
-      <c r="AH68" s="121"/>
-      <c r="AI68" s="121"/>
-      <c r="AJ68" s="118" t="s">
+      <c r="Q68" s="112"/>
+      <c r="R68" s="112"/>
+      <c r="S68" s="112"/>
+      <c r="T68" s="112"/>
+      <c r="U68" s="112"/>
+      <c r="V68" s="112"/>
+      <c r="W68" s="112"/>
+      <c r="X68" s="112"/>
+      <c r="Y68" s="112"/>
+      <c r="Z68" s="112"/>
+      <c r="AA68" s="112"/>
+      <c r="AB68" s="112"/>
+      <c r="AC68" s="112"/>
+      <c r="AD68" s="112"/>
+      <c r="AE68" s="112"/>
+      <c r="AF68" s="112"/>
+      <c r="AG68" s="112"/>
+      <c r="AH68" s="112"/>
+      <c r="AI68" s="112"/>
+      <c r="AJ68" s="109" t="s">
         <v>314</v>
       </c>
-      <c r="AK68" s="121"/>
-      <c r="AL68" s="121"/>
-      <c r="AM68" s="121"/>
-      <c r="AN68" s="121"/>
-      <c r="AO68" s="121"/>
-      <c r="AP68" s="121"/>
-      <c r="AQ68" s="121"/>
-      <c r="AR68" s="121"/>
-      <c r="AS68" s="121"/>
-      <c r="AT68" s="121"/>
-      <c r="AU68" s="121"/>
-      <c r="AV68" s="121"/>
-    </row>
-    <row r="69" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A69" s="118" t="s">
+      <c r="AK68" s="112"/>
+      <c r="AL68" s="112"/>
+      <c r="AM68" s="112"/>
+      <c r="AN68" s="112"/>
+      <c r="AO68" s="112"/>
+      <c r="AP68" s="112"/>
+      <c r="AQ68" s="112"/>
+      <c r="AR68" s="112"/>
+      <c r="AS68" s="112"/>
+      <c r="AT68" s="112"/>
+      <c r="AU68" s="112"/>
+      <c r="AV68" s="112"/>
+    </row>
+    <row r="69" spans="1:48">
+      <c r="A69" s="109" t="s">
         <v>297</v>
       </c>
-      <c r="B69" s="121"/>
-      <c r="C69" s="121"/>
-      <c r="D69" s="121"/>
-      <c r="E69" s="121"/>
-      <c r="F69" s="121"/>
-      <c r="G69" s="121"/>
-      <c r="H69" s="121"/>
-      <c r="I69" s="121"/>
-      <c r="J69" s="121"/>
-      <c r="K69" s="121"/>
-      <c r="L69" s="121"/>
-      <c r="M69" s="121"/>
-      <c r="N69" s="121"/>
-      <c r="O69" s="121"/>
-      <c r="P69" s="118" t="s">
+      <c r="B69" s="112"/>
+      <c r="C69" s="112"/>
+      <c r="D69" s="112"/>
+      <c r="E69" s="112"/>
+      <c r="F69" s="112"/>
+      <c r="G69" s="112"/>
+      <c r="H69" s="112"/>
+      <c r="I69" s="112"/>
+      <c r="J69" s="112"/>
+      <c r="K69" s="112"/>
+      <c r="L69" s="112"/>
+      <c r="M69" s="112"/>
+      <c r="N69" s="112"/>
+      <c r="O69" s="112"/>
+      <c r="P69" s="109" t="s">
         <v>307</v>
       </c>
-      <c r="Q69" s="121"/>
-      <c r="R69" s="121"/>
-      <c r="S69" s="121"/>
-      <c r="T69" s="121"/>
-      <c r="U69" s="121"/>
-      <c r="V69" s="121"/>
-      <c r="W69" s="121"/>
-      <c r="X69" s="121"/>
-      <c r="Y69" s="121"/>
-      <c r="Z69" s="121"/>
-      <c r="AA69" s="121"/>
-      <c r="AB69" s="121"/>
-      <c r="AC69" s="121"/>
-      <c r="AD69" s="121"/>
-      <c r="AE69" s="121"/>
-      <c r="AF69" s="121"/>
-      <c r="AG69" s="121"/>
-      <c r="AH69" s="121"/>
-      <c r="AI69" s="121"/>
-      <c r="AJ69" s="118" t="s">
+      <c r="Q69" s="112"/>
+      <c r="R69" s="112"/>
+      <c r="S69" s="112"/>
+      <c r="T69" s="112"/>
+      <c r="U69" s="112"/>
+      <c r="V69" s="112"/>
+      <c r="W69" s="112"/>
+      <c r="X69" s="112"/>
+      <c r="Y69" s="112"/>
+      <c r="Z69" s="112"/>
+      <c r="AA69" s="112"/>
+      <c r="AB69" s="112"/>
+      <c r="AC69" s="112"/>
+      <c r="AD69" s="112"/>
+      <c r="AE69" s="112"/>
+      <c r="AF69" s="112"/>
+      <c r="AG69" s="112"/>
+      <c r="AH69" s="112"/>
+      <c r="AI69" s="112"/>
+      <c r="AJ69" s="109" t="s">
         <v>315</v>
       </c>
-      <c r="AK69" s="121"/>
-      <c r="AL69" s="121"/>
-      <c r="AM69" s="121"/>
-      <c r="AN69" s="121"/>
-      <c r="AO69" s="121"/>
-      <c r="AP69" s="121"/>
-      <c r="AQ69" s="121"/>
-      <c r="AR69" s="121"/>
-      <c r="AS69" s="121"/>
-      <c r="AT69" s="121"/>
-      <c r="AU69" s="121"/>
-      <c r="AV69" s="121"/>
-    </row>
-    <row r="70" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A70" s="118" t="s">
+      <c r="AK69" s="112"/>
+      <c r="AL69" s="112"/>
+      <c r="AM69" s="112"/>
+      <c r="AN69" s="112"/>
+      <c r="AO69" s="112"/>
+      <c r="AP69" s="112"/>
+      <c r="AQ69" s="112"/>
+      <c r="AR69" s="112"/>
+      <c r="AS69" s="112"/>
+      <c r="AT69" s="112"/>
+      <c r="AU69" s="112"/>
+      <c r="AV69" s="112"/>
+    </row>
+    <row r="70" spans="1:48">
+      <c r="A70" s="109" t="s">
         <v>298</v>
       </c>
-      <c r="B70" s="121"/>
-      <c r="C70" s="121"/>
-      <c r="D70" s="121"/>
-      <c r="E70" s="121"/>
-      <c r="F70" s="121"/>
-      <c r="G70" s="121"/>
-      <c r="H70" s="121"/>
-      <c r="I70" s="121"/>
-      <c r="J70" s="121"/>
-      <c r="K70" s="121"/>
-      <c r="L70" s="121"/>
-      <c r="M70" s="121"/>
-      <c r="N70" s="121"/>
-      <c r="O70" s="121"/>
-      <c r="P70" s="118" t="s">
+      <c r="B70" s="112"/>
+      <c r="C70" s="112"/>
+      <c r="D70" s="112"/>
+      <c r="E70" s="112"/>
+      <c r="F70" s="112"/>
+      <c r="G70" s="112"/>
+      <c r="H70" s="112"/>
+      <c r="I70" s="112"/>
+      <c r="J70" s="112"/>
+      <c r="K70" s="112"/>
+      <c r="L70" s="112"/>
+      <c r="M70" s="112"/>
+      <c r="N70" s="112"/>
+      <c r="O70" s="112"/>
+      <c r="P70" s="109" t="s">
         <v>308</v>
       </c>
-      <c r="Q70" s="121"/>
-      <c r="R70" s="121"/>
-      <c r="S70" s="121"/>
-      <c r="T70" s="121"/>
-      <c r="U70" s="121"/>
-      <c r="V70" s="121"/>
-      <c r="W70" s="121"/>
-      <c r="X70" s="121"/>
-      <c r="Y70" s="121"/>
-      <c r="Z70" s="121"/>
-      <c r="AA70" s="121"/>
-      <c r="AB70" s="121"/>
-      <c r="AC70" s="121"/>
-      <c r="AD70" s="121"/>
-      <c r="AE70" s="121"/>
-      <c r="AF70" s="121"/>
-      <c r="AG70" s="121"/>
-      <c r="AH70" s="121"/>
-      <c r="AI70" s="121"/>
-      <c r="AJ70" s="118" t="s">
+      <c r="Q70" s="112"/>
+      <c r="R70" s="112"/>
+      <c r="S70" s="112"/>
+      <c r="T70" s="112"/>
+      <c r="U70" s="112"/>
+      <c r="V70" s="112"/>
+      <c r="W70" s="112"/>
+      <c r="X70" s="112"/>
+      <c r="Y70" s="112"/>
+      <c r="Z70" s="112"/>
+      <c r="AA70" s="112"/>
+      <c r="AB70" s="112"/>
+      <c r="AC70" s="112"/>
+      <c r="AD70" s="112"/>
+      <c r="AE70" s="112"/>
+      <c r="AF70" s="112"/>
+      <c r="AG70" s="112"/>
+      <c r="AH70" s="112"/>
+      <c r="AI70" s="112"/>
+      <c r="AJ70" s="109" t="s">
         <v>316</v>
       </c>
-      <c r="AK70" s="121"/>
-      <c r="AL70" s="121"/>
-      <c r="AM70" s="121"/>
-      <c r="AN70" s="121"/>
-      <c r="AO70" s="121"/>
-      <c r="AP70" s="121"/>
-      <c r="AQ70" s="121"/>
-      <c r="AR70" s="121"/>
-      <c r="AS70" s="121"/>
-      <c r="AT70" s="121"/>
-      <c r="AU70" s="121"/>
-      <c r="AV70" s="121"/>
-    </row>
-    <row r="71" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A71" s="118" t="s">
+      <c r="AK70" s="112"/>
+      <c r="AL70" s="112"/>
+      <c r="AM70" s="112"/>
+      <c r="AN70" s="112"/>
+      <c r="AO70" s="112"/>
+      <c r="AP70" s="112"/>
+      <c r="AQ70" s="112"/>
+      <c r="AR70" s="112"/>
+      <c r="AS70" s="112"/>
+      <c r="AT70" s="112"/>
+      <c r="AU70" s="112"/>
+      <c r="AV70" s="112"/>
+    </row>
+    <row r="71" spans="1:48">
+      <c r="A71" s="109" t="s">
         <v>299</v>
       </c>
-      <c r="B71" s="121"/>
-      <c r="C71" s="121"/>
-      <c r="D71" s="121"/>
-      <c r="E71" s="121"/>
-      <c r="F71" s="121"/>
-      <c r="G71" s="121"/>
-      <c r="H71" s="121"/>
-      <c r="I71" s="121"/>
-      <c r="J71" s="121"/>
-      <c r="K71" s="121"/>
-      <c r="L71" s="121"/>
-      <c r="M71" s="121"/>
-      <c r="N71" s="121"/>
-      <c r="O71" s="121"/>
-      <c r="P71" s="118" t="s">
+      <c r="B71" s="112"/>
+      <c r="C71" s="112"/>
+      <c r="D71" s="112"/>
+      <c r="E71" s="112"/>
+      <c r="F71" s="112"/>
+      <c r="G71" s="112"/>
+      <c r="H71" s="112"/>
+      <c r="I71" s="112"/>
+      <c r="J71" s="112"/>
+      <c r="K71" s="112"/>
+      <c r="L71" s="112"/>
+      <c r="M71" s="112"/>
+      <c r="N71" s="112"/>
+      <c r="O71" s="112"/>
+      <c r="P71" s="109" t="s">
         <v>309</v>
       </c>
-      <c r="Q71" s="121"/>
-      <c r="R71" s="121"/>
-      <c r="S71" s="121"/>
-      <c r="T71" s="121"/>
-      <c r="U71" s="121"/>
-      <c r="V71" s="121"/>
-      <c r="W71" s="121"/>
-      <c r="X71" s="121"/>
-      <c r="Y71" s="121"/>
-      <c r="Z71" s="121"/>
-      <c r="AA71" s="121"/>
-      <c r="AB71" s="121"/>
-      <c r="AC71" s="121"/>
-      <c r="AD71" s="121"/>
-      <c r="AE71" s="121"/>
-      <c r="AF71" s="121"/>
-      <c r="AG71" s="121"/>
-      <c r="AH71" s="121"/>
-      <c r="AI71" s="121"/>
-      <c r="AJ71" s="118" t="s">
+      <c r="Q71" s="112"/>
+      <c r="R71" s="112"/>
+      <c r="S71" s="112"/>
+      <c r="T71" s="112"/>
+      <c r="U71" s="112"/>
+      <c r="V71" s="112"/>
+      <c r="W71" s="112"/>
+      <c r="X71" s="112"/>
+      <c r="Y71" s="112"/>
+      <c r="Z71" s="112"/>
+      <c r="AA71" s="112"/>
+      <c r="AB71" s="112"/>
+      <c r="AC71" s="112"/>
+      <c r="AD71" s="112"/>
+      <c r="AE71" s="112"/>
+      <c r="AF71" s="112"/>
+      <c r="AG71" s="112"/>
+      <c r="AH71" s="112"/>
+      <c r="AI71" s="112"/>
+      <c r="AJ71" s="109" t="s">
         <v>317</v>
       </c>
-      <c r="AK71" s="121"/>
-      <c r="AL71" s="121"/>
-      <c r="AM71" s="121"/>
-      <c r="AN71" s="121"/>
-      <c r="AO71" s="121"/>
-      <c r="AP71" s="121"/>
-      <c r="AQ71" s="121"/>
-      <c r="AR71" s="121"/>
-      <c r="AS71" s="121"/>
-      <c r="AT71" s="121"/>
-      <c r="AU71" s="121"/>
-      <c r="AV71" s="121"/>
-    </row>
-    <row r="72" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A72" s="118" t="s">
+      <c r="AK71" s="112"/>
+      <c r="AL71" s="112"/>
+      <c r="AM71" s="112"/>
+      <c r="AN71" s="112"/>
+      <c r="AO71" s="112"/>
+      <c r="AP71" s="112"/>
+      <c r="AQ71" s="112"/>
+      <c r="AR71" s="112"/>
+      <c r="AS71" s="112"/>
+      <c r="AT71" s="112"/>
+      <c r="AU71" s="112"/>
+      <c r="AV71" s="112"/>
+    </row>
+    <row r="72" spans="1:48">
+      <c r="A72" s="109" t="s">
         <v>300</v>
       </c>
-      <c r="B72" s="121"/>
-      <c r="C72" s="121"/>
-      <c r="D72" s="121"/>
-      <c r="E72" s="121"/>
-      <c r="F72" s="121"/>
-      <c r="G72" s="121"/>
-      <c r="H72" s="121"/>
-      <c r="I72" s="121"/>
-      <c r="J72" s="121"/>
-      <c r="K72" s="121"/>
-      <c r="L72" s="121"/>
-      <c r="M72" s="121"/>
-      <c r="N72" s="121"/>
-      <c r="O72" s="121"/>
-      <c r="P72" s="118" t="s">
+      <c r="B72" s="112"/>
+      <c r="C72" s="112"/>
+      <c r="D72" s="112"/>
+      <c r="E72" s="112"/>
+      <c r="F72" s="112"/>
+      <c r="G72" s="112"/>
+      <c r="H72" s="112"/>
+      <c r="I72" s="112"/>
+      <c r="J72" s="112"/>
+      <c r="K72" s="112"/>
+      <c r="L72" s="112"/>
+      <c r="M72" s="112"/>
+      <c r="N72" s="112"/>
+      <c r="O72" s="112"/>
+      <c r="P72" s="109" t="s">
         <v>310</v>
       </c>
-      <c r="Q72" s="121"/>
-      <c r="R72" s="121"/>
-      <c r="S72" s="121"/>
-      <c r="T72" s="121"/>
-      <c r="U72" s="121"/>
-      <c r="V72" s="121"/>
-      <c r="W72" s="121"/>
-      <c r="X72" s="121"/>
-      <c r="Y72" s="121"/>
-      <c r="Z72" s="121"/>
-      <c r="AA72" s="121"/>
-      <c r="AB72" s="121"/>
-      <c r="AC72" s="121"/>
-      <c r="AD72" s="121"/>
-      <c r="AE72" s="121"/>
-      <c r="AF72" s="121"/>
-      <c r="AG72" s="121"/>
-      <c r="AH72" s="121"/>
-      <c r="AI72" s="121"/>
-      <c r="AJ72" s="118" t="s">
+      <c r="Q72" s="112"/>
+      <c r="R72" s="112"/>
+      <c r="S72" s="112"/>
+      <c r="T72" s="112"/>
+      <c r="U72" s="112"/>
+      <c r="V72" s="112"/>
+      <c r="W72" s="112"/>
+      <c r="X72" s="112"/>
+      <c r="Y72" s="112"/>
+      <c r="Z72" s="112"/>
+      <c r="AA72" s="112"/>
+      <c r="AB72" s="112"/>
+      <c r="AC72" s="112"/>
+      <c r="AD72" s="112"/>
+      <c r="AE72" s="112"/>
+      <c r="AF72" s="112"/>
+      <c r="AG72" s="112"/>
+      <c r="AH72" s="112"/>
+      <c r="AI72" s="112"/>
+      <c r="AJ72" s="109" t="s">
         <v>318</v>
       </c>
-      <c r="AK72" s="121"/>
-      <c r="AL72" s="121"/>
-      <c r="AM72" s="121"/>
-      <c r="AN72" s="121"/>
-      <c r="AO72" s="121"/>
-      <c r="AP72" s="121"/>
-      <c r="AQ72" s="121"/>
-      <c r="AR72" s="121"/>
-      <c r="AS72" s="121"/>
-      <c r="AT72" s="121"/>
-      <c r="AU72" s="121"/>
-      <c r="AV72" s="121"/>
-    </row>
-    <row r="73" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A73" s="118" t="s">
+      <c r="AK72" s="112"/>
+      <c r="AL72" s="112"/>
+      <c r="AM72" s="112"/>
+      <c r="AN72" s="112"/>
+      <c r="AO72" s="112"/>
+      <c r="AP72" s="112"/>
+      <c r="AQ72" s="112"/>
+      <c r="AR72" s="112"/>
+      <c r="AS72" s="112"/>
+      <c r="AT72" s="112"/>
+      <c r="AU72" s="112"/>
+      <c r="AV72" s="112"/>
+    </row>
+    <row r="73" spans="1:48">
+      <c r="A73" s="109" t="s">
         <v>301</v>
       </c>
-      <c r="B73" s="121"/>
-      <c r="C73" s="121"/>
-      <c r="D73" s="121"/>
-      <c r="E73" s="121"/>
-      <c r="F73" s="121"/>
-      <c r="G73" s="121"/>
-      <c r="H73" s="121"/>
-      <c r="I73" s="121"/>
-      <c r="J73" s="121"/>
-      <c r="K73" s="121"/>
-      <c r="L73" s="121"/>
-      <c r="M73" s="121"/>
-      <c r="N73" s="121"/>
-      <c r="O73" s="121"/>
-      <c r="P73" s="118" t="s">
+      <c r="B73" s="112"/>
+      <c r="C73" s="112"/>
+      <c r="D73" s="112"/>
+      <c r="E73" s="112"/>
+      <c r="F73" s="112"/>
+      <c r="G73" s="112"/>
+      <c r="H73" s="112"/>
+      <c r="I73" s="112"/>
+      <c r="J73" s="112"/>
+      <c r="K73" s="112"/>
+      <c r="L73" s="112"/>
+      <c r="M73" s="112"/>
+      <c r="N73" s="112"/>
+      <c r="O73" s="112"/>
+      <c r="P73" s="109" t="s">
         <v>311</v>
       </c>
-      <c r="Q73" s="121"/>
-      <c r="R73" s="121"/>
-      <c r="S73" s="121"/>
-      <c r="T73" s="121"/>
-      <c r="U73" s="121"/>
-      <c r="V73" s="121"/>
-      <c r="W73" s="121"/>
-      <c r="X73" s="121"/>
-      <c r="Y73" s="121"/>
-      <c r="Z73" s="121"/>
-      <c r="AA73" s="121"/>
-      <c r="AB73" s="121"/>
-      <c r="AC73" s="121"/>
-      <c r="AD73" s="121"/>
-      <c r="AE73" s="121"/>
-      <c r="AF73" s="121"/>
-      <c r="AG73" s="121"/>
-      <c r="AH73" s="121"/>
-      <c r="AI73" s="121"/>
-      <c r="AJ73" s="118" t="s">
+      <c r="Q73" s="112"/>
+      <c r="R73" s="112"/>
+      <c r="S73" s="112"/>
+      <c r="T73" s="112"/>
+      <c r="U73" s="112"/>
+      <c r="V73" s="112"/>
+      <c r="W73" s="112"/>
+      <c r="X73" s="112"/>
+      <c r="Y73" s="112"/>
+      <c r="Z73" s="112"/>
+      <c r="AA73" s="112"/>
+      <c r="AB73" s="112"/>
+      <c r="AC73" s="112"/>
+      <c r="AD73" s="112"/>
+      <c r="AE73" s="112"/>
+      <c r="AF73" s="112"/>
+      <c r="AG73" s="112"/>
+      <c r="AH73" s="112"/>
+      <c r="AI73" s="112"/>
+      <c r="AJ73" s="109" t="s">
         <v>319</v>
       </c>
-      <c r="AK73" s="121"/>
-      <c r="AL73" s="121"/>
-      <c r="AM73" s="121"/>
-      <c r="AN73" s="121"/>
-      <c r="AO73" s="121"/>
-      <c r="AP73" s="121"/>
-      <c r="AQ73" s="121"/>
-      <c r="AR73" s="121"/>
-      <c r="AS73" s="121"/>
-      <c r="AT73" s="121"/>
-      <c r="AU73" s="121"/>
-      <c r="AV73" s="121"/>
-    </row>
-    <row r="74" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A74" s="118" t="s">
+      <c r="AK73" s="112"/>
+      <c r="AL73" s="112"/>
+      <c r="AM73" s="112"/>
+      <c r="AN73" s="112"/>
+      <c r="AO73" s="112"/>
+      <c r="AP73" s="112"/>
+      <c r="AQ73" s="112"/>
+      <c r="AR73" s="112"/>
+      <c r="AS73" s="112"/>
+      <c r="AT73" s="112"/>
+      <c r="AU73" s="112"/>
+      <c r="AV73" s="112"/>
+    </row>
+    <row r="74" spans="1:48">
+      <c r="A74" s="109" t="s">
         <v>302</v>
       </c>
-      <c r="B74" s="121"/>
-      <c r="C74" s="121"/>
-      <c r="D74" s="121"/>
-      <c r="E74" s="121"/>
-      <c r="F74" s="121"/>
-      <c r="G74" s="121"/>
-      <c r="H74" s="121"/>
-      <c r="I74" s="121"/>
-      <c r="J74" s="121"/>
-      <c r="K74" s="121"/>
-      <c r="L74" s="121"/>
-      <c r="M74" s="121"/>
-      <c r="N74" s="121"/>
-      <c r="O74" s="121"/>
-      <c r="P74" s="121"/>
-      <c r="Q74" s="121"/>
-      <c r="R74" s="121"/>
-      <c r="S74" s="121"/>
-      <c r="T74" s="121"/>
-      <c r="U74" s="121"/>
-      <c r="V74" s="121"/>
-      <c r="W74" s="121"/>
-      <c r="X74" s="121"/>
-      <c r="Y74" s="121"/>
-      <c r="Z74" s="121"/>
-      <c r="AA74" s="121"/>
-      <c r="AB74" s="121"/>
-      <c r="AC74" s="121"/>
-      <c r="AD74" s="121"/>
-      <c r="AE74" s="121"/>
-      <c r="AF74" s="121"/>
-      <c r="AG74" s="121"/>
-      <c r="AH74" s="121"/>
-      <c r="AI74" s="121"/>
-      <c r="AJ74" s="121"/>
-      <c r="AK74" s="121"/>
-      <c r="AL74" s="121"/>
-      <c r="AM74" s="121"/>
-      <c r="AN74" s="121"/>
-      <c r="AO74" s="121"/>
-      <c r="AP74" s="121"/>
-      <c r="AQ74" s="121"/>
-      <c r="AR74" s="121"/>
-      <c r="AS74" s="121"/>
-      <c r="AT74" s="121"/>
-      <c r="AU74" s="121"/>
-      <c r="AV74" s="121"/>
-    </row>
-    <row r="75" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A75" s="118" t="s">
+      <c r="B74" s="112"/>
+      <c r="C74" s="112"/>
+      <c r="D74" s="112"/>
+      <c r="E74" s="112"/>
+      <c r="F74" s="112"/>
+      <c r="G74" s="112"/>
+      <c r="H74" s="112"/>
+      <c r="I74" s="112"/>
+      <c r="J74" s="112"/>
+      <c r="K74" s="112"/>
+      <c r="L74" s="112"/>
+      <c r="M74" s="112"/>
+      <c r="N74" s="112"/>
+      <c r="O74" s="112"/>
+      <c r="P74" s="112"/>
+      <c r="Q74" s="112"/>
+      <c r="R74" s="112"/>
+      <c r="S74" s="112"/>
+      <c r="T74" s="112"/>
+      <c r="U74" s="112"/>
+      <c r="V74" s="112"/>
+      <c r="W74" s="112"/>
+      <c r="X74" s="112"/>
+      <c r="Y74" s="112"/>
+      <c r="Z74" s="112"/>
+      <c r="AA74" s="112"/>
+      <c r="AB74" s="112"/>
+      <c r="AC74" s="112"/>
+      <c r="AD74" s="112"/>
+      <c r="AE74" s="112"/>
+      <c r="AF74" s="112"/>
+      <c r="AG74" s="112"/>
+      <c r="AH74" s="112"/>
+      <c r="AI74" s="112"/>
+      <c r="AJ74" s="112"/>
+      <c r="AK74" s="112"/>
+      <c r="AL74" s="112"/>
+      <c r="AM74" s="112"/>
+      <c r="AN74" s="112"/>
+      <c r="AO74" s="112"/>
+      <c r="AP74" s="112"/>
+      <c r="AQ74" s="112"/>
+      <c r="AR74" s="112"/>
+      <c r="AS74" s="112"/>
+      <c r="AT74" s="112"/>
+      <c r="AU74" s="112"/>
+      <c r="AV74" s="112"/>
+    </row>
+    <row r="75" spans="1:48">
+      <c r="A75" s="109" t="s">
         <v>303</v>
       </c>
-      <c r="B75" s="121"/>
-      <c r="C75" s="121"/>
-      <c r="D75" s="121"/>
-      <c r="E75" s="121"/>
-      <c r="F75" s="121"/>
-      <c r="G75" s="121"/>
-      <c r="H75" s="121"/>
-      <c r="I75" s="121"/>
-      <c r="J75" s="121"/>
-      <c r="K75" s="121"/>
-      <c r="L75" s="121"/>
-      <c r="M75" s="121"/>
-      <c r="N75" s="121"/>
-      <c r="O75" s="121"/>
-      <c r="P75" s="121"/>
-      <c r="Q75" s="121"/>
-      <c r="R75" s="121"/>
-      <c r="S75" s="121"/>
-      <c r="T75" s="121"/>
-      <c r="U75" s="121"/>
-      <c r="V75" s="121"/>
-      <c r="W75" s="121"/>
-      <c r="X75" s="121"/>
-      <c r="Y75" s="121"/>
-      <c r="Z75" s="121"/>
-      <c r="AA75" s="121"/>
-      <c r="AB75" s="121"/>
-      <c r="AC75" s="121"/>
-      <c r="AD75" s="121"/>
-      <c r="AE75" s="121"/>
-      <c r="AF75" s="121"/>
-      <c r="AG75" s="121"/>
-      <c r="AH75" s="121"/>
-      <c r="AI75" s="121"/>
-      <c r="AJ75" s="121"/>
-      <c r="AK75" s="121"/>
-      <c r="AL75" s="121"/>
-      <c r="AM75" s="121"/>
-      <c r="AN75" s="121"/>
-      <c r="AO75" s="121"/>
-      <c r="AP75" s="121"/>
-      <c r="AQ75" s="121"/>
-      <c r="AR75" s="121"/>
-      <c r="AS75" s="121"/>
-      <c r="AT75" s="121"/>
-      <c r="AU75" s="121"/>
-      <c r="AV75" s="121"/>
-    </row>
-    <row r="76" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A76" s="106"/>
-    </row>
-    <row r="77" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A77" s="106"/>
-    </row>
-    <row r="78" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+      <c r="B75" s="112"/>
+      <c r="C75" s="112"/>
+      <c r="D75" s="112"/>
+      <c r="E75" s="112"/>
+      <c r="F75" s="112"/>
+      <c r="G75" s="112"/>
+      <c r="H75" s="112"/>
+      <c r="I75" s="112"/>
+      <c r="J75" s="112"/>
+      <c r="K75" s="112"/>
+      <c r="L75" s="112"/>
+      <c r="M75" s="112"/>
+      <c r="N75" s="112"/>
+      <c r="O75" s="112"/>
+      <c r="P75" s="112"/>
+      <c r="Q75" s="112"/>
+      <c r="R75" s="112"/>
+      <c r="S75" s="112"/>
+      <c r="T75" s="112"/>
+      <c r="U75" s="112"/>
+      <c r="V75" s="112"/>
+      <c r="W75" s="112"/>
+      <c r="X75" s="112"/>
+      <c r="Y75" s="112"/>
+      <c r="Z75" s="112"/>
+      <c r="AA75" s="112"/>
+      <c r="AB75" s="112"/>
+      <c r="AC75" s="112"/>
+      <c r="AD75" s="112"/>
+      <c r="AE75" s="112"/>
+      <c r="AF75" s="112"/>
+      <c r="AG75" s="112"/>
+      <c r="AH75" s="112"/>
+      <c r="AI75" s="112"/>
+      <c r="AJ75" s="112"/>
+      <c r="AK75" s="112"/>
+      <c r="AL75" s="112"/>
+      <c r="AM75" s="112"/>
+      <c r="AN75" s="112"/>
+      <c r="AO75" s="112"/>
+      <c r="AP75" s="112"/>
+      <c r="AQ75" s="112"/>
+      <c r="AR75" s="112"/>
+      <c r="AS75" s="112"/>
+      <c r="AT75" s="112"/>
+      <c r="AU75" s="112"/>
+      <c r="AV75" s="112"/>
+    </row>
+    <row r="76" spans="1:48">
+      <c r="A76" s="97"/>
+    </row>
+    <row r="77" spans="1:48">
+      <c r="A77" s="97"/>
+    </row>
+    <row r="78" spans="1:48" ht="15">
       <c r="A78" s="42" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="79" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A79" s="106" t="s">
+    <row r="79" spans="1:48">
+      <c r="A79" s="97" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="80" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A80" s="106"/>
-    </row>
-    <row r="81" spans="1:59" ht="15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:48">
+      <c r="A80" s="97"/>
+    </row>
+    <row r="81" spans="1:59" ht="15">
       <c r="A81" s="45" t="s">
         <v>322</v>
       </c>
@@ -10201,1003 +10264,1818 @@
         <v>344</v>
       </c>
     </row>
-    <row r="82" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A82" s="118" t="s">
+    <row r="82" spans="1:59">
+      <c r="A82" s="109" t="s">
         <v>323</v>
       </c>
-      <c r="O82" s="118" t="s">
+      <c r="O82" s="109" t="s">
         <v>326</v>
       </c>
-      <c r="AA82" s="118" t="s">
+      <c r="AA82" s="109" t="s">
         <v>330</v>
       </c>
-      <c r="AK82" s="118" t="s">
+      <c r="AK82" s="109" t="s">
         <v>334</v>
       </c>
-      <c r="AV82" s="118" t="s">
+      <c r="AV82" s="109" t="s">
         <v>340</v>
       </c>
-      <c r="BG82" s="118" t="s">
+      <c r="BG82" s="109" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="83" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A83" s="118" t="s">
+    <row r="83" spans="1:59">
+      <c r="A83" s="109" t="s">
         <v>324</v>
       </c>
-      <c r="O83" s="118" t="s">
+      <c r="O83" s="109" t="s">
         <v>327</v>
       </c>
-      <c r="AA83" s="118" t="s">
+      <c r="AA83" s="109" t="s">
         <v>331</v>
       </c>
-      <c r="AK83" s="118" t="s">
+      <c r="AK83" s="109" t="s">
         <v>335</v>
       </c>
-      <c r="AV83" s="118" t="s">
+      <c r="AV83" s="109" t="s">
         <v>341</v>
       </c>
-      <c r="BG83" s="118" t="s">
+      <c r="BG83" s="109" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="84" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A84" s="106"/>
-      <c r="O84" s="118" t="s">
+    <row r="84" spans="1:59">
+      <c r="A84" s="97"/>
+      <c r="O84" s="109" t="s">
         <v>328</v>
       </c>
-      <c r="AA84" s="118" t="s">
+      <c r="AA84" s="109" t="s">
         <v>332</v>
       </c>
-      <c r="AK84" s="118" t="s">
+      <c r="AK84" s="109" t="s">
         <v>336</v>
       </c>
-      <c r="AV84" s="118" t="s">
+      <c r="AV84" s="109" t="s">
         <v>342</v>
       </c>
-      <c r="BG84" s="118" t="s">
+      <c r="BG84" s="109" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="85" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="AK85" s="118" t="s">
+    <row r="85" spans="1:59">
+      <c r="AK85" s="109" t="s">
         <v>337</v>
       </c>
-      <c r="AV85" s="118" t="s">
+      <c r="AV85" s="109" t="s">
         <v>343</v>
       </c>
-      <c r="BG85" s="118" t="s">
+      <c r="BG85" s="109" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="86" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="AK86" s="118" t="s">
+    <row r="86" spans="1:59">
+      <c r="AK86" s="109" t="s">
         <v>338</v>
       </c>
-      <c r="AV86" s="106"/>
-      <c r="BG86" s="118" t="s">
+      <c r="AV86" s="97"/>
+      <c r="BG86" s="109" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="87" spans="1:59" ht="15" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:59" ht="15">
       <c r="A87" s="42" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="88" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A88" s="118" t="s">
+    <row r="88" spans="1:59">
+      <c r="A88" s="109" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="89" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A89" s="118" t="s">
+    <row r="89" spans="1:59">
+      <c r="A89" s="109" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="90" spans="1:59">
+      <c r="A90" s="109"/>
+    </row>
+    <row r="91" spans="1:59">
+      <c r="A91" s="109" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="90" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A90" s="118"/>
-    </row>
-    <row r="91" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A91" s="118" t="s">
+    <row r="92" spans="1:59">
+      <c r="A92" s="109" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="92" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A92" s="118" t="s">
+    <row r="93" spans="1:59">
+      <c r="A93" s="109" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="93" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A93" s="118" t="s">
+    <row r="94" spans="1:59" ht="15" thickBot="1">
+      <c r="A94" s="97"/>
+    </row>
+    <row r="95" spans="1:59" s="111" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A95" s="110" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="94" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="106"/>
-    </row>
-    <row r="95" spans="1:59" s="120" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="119" t="s">
+    <row r="96" spans="1:59" ht="15">
+      <c r="A96" s="42" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="96" spans="1:59" ht="15" x14ac:dyDescent="0.2">
-      <c r="A96" s="42" t="s">
+      <c r="N96" s="42" t="s">
+        <v>361</v>
+      </c>
+      <c r="Z96" s="42" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="97" spans="1:26">
+      <c r="A97" s="109" t="s">
         <v>357</v>
       </c>
-      <c r="N96" s="42" t="s">
+      <c r="N97" s="109" t="s">
         <v>362</v>
       </c>
-      <c r="Z96" s="42" t="s">
+      <c r="Z97" s="109" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A97" s="118" t="s">
+    <row r="98" spans="1:26">
+      <c r="A98" s="109" t="s">
         <v>358</v>
       </c>
-      <c r="N97" s="118" t="s">
+      <c r="N98" s="109" t="s">
         <v>363</v>
       </c>
-      <c r="Z97" s="118" t="s">
+      <c r="Z98" s="109" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A98" s="118" t="s">
+    <row r="99" spans="1:26">
+      <c r="A99" s="109"/>
+      <c r="N99" s="109"/>
+      <c r="Z99" s="109"/>
+    </row>
+    <row r="100" spans="1:26">
+      <c r="A100" s="109" t="s">
         <v>359</v>
       </c>
-      <c r="N98" s="118" t="s">
+      <c r="N100" s="109" t="s">
         <v>364</v>
       </c>
-      <c r="Z98" s="118" t="s">
+      <c r="Z100" s="109" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A99" s="118"/>
-      <c r="N99" s="118"/>
-      <c r="Z99" s="118"/>
-    </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A100" s="118" t="s">
+    <row r="101" spans="1:26">
+      <c r="A101" s="109" t="s">
         <v>360</v>
       </c>
-      <c r="N100" s="118" t="s">
+      <c r="N101" s="109" t="s">
         <v>365</v>
       </c>
-      <c r="Z100" s="118" t="s">
+      <c r="Z101" s="109" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A101" s="118" t="s">
-        <v>361</v>
-      </c>
-      <c r="N101" s="118" t="s">
+    <row r="102" spans="1:26">
+      <c r="A102" s="97"/>
+      <c r="N102" s="109"/>
+      <c r="Z102" s="109"/>
+    </row>
+    <row r="103" spans="1:26">
+      <c r="N103" s="109" t="s">
         <v>366</v>
       </c>
-      <c r="Z101" s="118" t="s">
+      <c r="Z103" s="109" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A102" s="106"/>
-      <c r="N102" s="118"/>
-      <c r="Z102" s="118"/>
-    </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="N103" s="118" t="s">
+    <row r="104" spans="1:26">
+      <c r="N104" s="109" t="s">
         <v>367</v>
       </c>
-      <c r="Z103" s="118" t="s">
+      <c r="Z104" s="109" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="N104" s="118" t="s">
+    <row r="105" spans="1:26">
+      <c r="N105" s="109"/>
+    </row>
+    <row r="106" spans="1:26">
+      <c r="N106" s="109" t="s">
         <v>368</v>
       </c>
-      <c r="Z104" s="118" t="s">
+    </row>
+    <row r="107" spans="1:26">
+      <c r="N107" s="109" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="108" spans="1:26">
+      <c r="N108" s="109"/>
+    </row>
+    <row r="109" spans="1:26">
+      <c r="N109" s="109" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="110" spans="1:26">
+      <c r="N110" s="109" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="111" spans="1:26" ht="15" thickBot="1">
+      <c r="A111" s="97"/>
+    </row>
+    <row r="112" spans="1:26" s="111" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A112" s="110" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="N105" s="118"/>
-    </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="N106" s="118" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="N107" s="118" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="N108" s="118"/>
-    </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="N109" s="118" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="N110" s="118" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="111" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="106"/>
-    </row>
-    <row r="112" spans="1:26" s="120" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="119" t="s">
+    <row r="113" spans="1:1">
+      <c r="A113" s="97" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="109" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A113" s="106" t="s">
+    <row r="115" spans="1:1">
+      <c r="A115" s="109"/>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="109" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="109" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="109" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="109" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="109" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="109" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="109" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="109" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" ht="15" thickBot="1">
+      <c r="A124" s="97"/>
+    </row>
+    <row r="125" spans="1:1" s="111" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A125" s="110" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" ht="15">
+      <c r="A126" s="42" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="97" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A114" s="118" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A115" s="118"/>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A116" s="118" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A117" s="118" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A118" s="118" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A119" s="118" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A120" s="118" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A121" s="118" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A122" s="118" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A123" s="118" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="106"/>
-    </row>
-    <row r="125" spans="1:1" s="120" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="119" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A126" s="42" t="s">
+    <row r="128" spans="1:1">
+      <c r="A128" s="109" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A127" s="106" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A128" s="118" t="s">
+    <row r="129" spans="1:14">
+      <c r="A129" s="109" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A129" s="118" t="s">
+    <row r="130" spans="1:14">
+      <c r="A130" s="109"/>
+    </row>
+    <row r="131" spans="1:14">
+      <c r="A131" s="109" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A130" s="118"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A131" s="118" t="s">
+    <row r="132" spans="1:14">
+      <c r="A132" s="109" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A132" s="118" t="s">
+    <row r="133" spans="1:14">
+      <c r="A133" s="109" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A133" s="118" t="s">
+    <row r="134" spans="1:14">
+      <c r="A134" s="97"/>
+    </row>
+    <row r="135" spans="1:14" ht="15">
+      <c r="A135" s="42" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A134" s="106"/>
-    </row>
-    <row r="135" spans="1:14" ht="15" x14ac:dyDescent="0.2">
-      <c r="A135" s="42" t="s">
+    <row r="136" spans="1:14">
+      <c r="A136" s="109" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A136" s="118" t="s">
+    <row r="137" spans="1:14">
+      <c r="A137" s="109" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A137" s="118" t="s">
+    <row r="138" spans="1:14">
+      <c r="A138" s="109"/>
+    </row>
+    <row r="139" spans="1:14">
+      <c r="A139" s="109" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A138" s="118"/>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A139" s="118" t="s">
+    <row r="140" spans="1:14">
+      <c r="A140" s="109" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A140" s="118" t="s">
+    <row r="141" spans="1:14">
+      <c r="A141" s="97"/>
+    </row>
+    <row r="142" spans="1:14" ht="15">
+      <c r="A142" s="45" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A141" s="106"/>
-    </row>
-    <row r="142" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A142" s="45" t="s">
+      <c r="N142" s="45" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14">
+      <c r="A143" s="109" t="s">
         <v>402</v>
       </c>
-      <c r="N142" s="45" t="s">
+      <c r="N143" s="109" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A143" s="118" t="s">
+    <row r="144" spans="1:14">
+      <c r="A144" s="109" t="s">
         <v>403</v>
       </c>
-      <c r="N143" s="118" t="s">
+      <c r="N144" s="109" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A144" s="118" t="s">
+    <row r="145" spans="1:14">
+      <c r="A145" s="109" t="s">
         <v>404</v>
       </c>
-      <c r="N144" s="118" t="s">
+      <c r="N145" s="109"/>
+    </row>
+    <row r="146" spans="1:14">
+      <c r="A146" s="109" t="s">
+        <v>405</v>
+      </c>
+      <c r="N146" s="109" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A145" s="118" t="s">
-        <v>405</v>
-      </c>
-      <c r="N145" s="118"/>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A146" s="118" t="s">
+    <row r="147" spans="1:14">
+      <c r="A147" s="109" t="s">
         <v>406</v>
       </c>
-      <c r="N146" s="118" t="s">
+      <c r="N147" s="109" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A147" s="118" t="s">
+    <row r="148" spans="1:14">
+      <c r="A148" s="109" t="s">
         <v>407</v>
       </c>
-      <c r="N147" s="118" t="s">
+      <c r="N148" s="109"/>
+    </row>
+    <row r="149" spans="1:14">
+      <c r="A149" s="109" t="s">
+        <v>408</v>
+      </c>
+      <c r="N149" s="109" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A148" s="118" t="s">
-        <v>408</v>
-      </c>
-      <c r="N148" s="118"/>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A149" s="118" t="s">
+    <row r="150" spans="1:14">
+      <c r="A150" s="109" t="s">
         <v>409</v>
       </c>
-      <c r="N149" s="118" t="s">
+      <c r="N150" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A150" s="118" t="s">
+    <row r="151" spans="1:14">
+      <c r="A151" s="109" t="s">
         <v>410</v>
       </c>
-      <c r="N150" s="118" t="s">
+      <c r="N151" s="109" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A151" s="118" t="s">
+    <row r="152" spans="1:14">
+      <c r="A152" s="109"/>
+      <c r="N152" s="109" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14">
+      <c r="A153" s="109" t="s">
         <v>411</v>
       </c>
-      <c r="N151" s="118" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A152" s="118"/>
-      <c r="N152" s="118" t="s">
+      <c r="N153" s="109"/>
+    </row>
+    <row r="154" spans="1:14">
+      <c r="A154" s="109" t="s">
+        <v>404</v>
+      </c>
+      <c r="N154" s="109" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A153" s="118" t="s">
+    <row r="155" spans="1:14">
+      <c r="A155" s="109" t="s">
         <v>412</v>
       </c>
-      <c r="N153" s="118"/>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A154" s="118" t="s">
-        <v>405</v>
-      </c>
-      <c r="N154" s="118" t="s">
+      <c r="N155" s="109" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A155" s="118" t="s">
+    <row r="156" spans="1:14">
+      <c r="A156" s="109" t="s">
         <v>413</v>
       </c>
-      <c r="N155" s="118" t="s">
+      <c r="N156" s="109" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A156" s="118" t="s">
+    <row r="157" spans="1:14">
+      <c r="A157" s="109" t="s">
         <v>414</v>
       </c>
-      <c r="N156" s="118" t="s">
+      <c r="N157" s="109" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A157" s="118" t="s">
+    <row r="158" spans="1:14">
+      <c r="A158" s="109" t="s">
         <v>415</v>
       </c>
-      <c r="N157" s="118" t="s">
+      <c r="N158" s="109" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A158" s="118" t="s">
-        <v>416</v>
-      </c>
-      <c r="N158" s="118" t="s">
+    <row r="159" spans="1:14">
+      <c r="A159" s="97"/>
+      <c r="N159" s="109"/>
+    </row>
+    <row r="160" spans="1:14">
+      <c r="N160" s="109" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A159" s="106"/>
-      <c r="N159" s="118"/>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N160" s="118" t="s">
+    <row r="161" spans="1:14">
+      <c r="N161" s="109" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N161" s="118" t="s">
+    <row r="162" spans="1:14">
+      <c r="N162" s="109" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N162" s="118" t="s">
+    <row r="163" spans="1:14">
+      <c r="N163" s="109" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N163" s="118" t="s">
+    <row r="164" spans="1:14">
+      <c r="N164" s="109" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N164" s="118" t="s">
+    <row r="165" spans="1:14">
+      <c r="N165" s="109" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N165" s="118" t="s">
+    <row r="166" spans="1:14">
+      <c r="N166" s="109" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N166" s="118" t="s">
+    <row r="167" spans="1:14">
+      <c r="N167" s="109"/>
+    </row>
+    <row r="168" spans="1:14">
+      <c r="N168" s="109" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N167" s="118"/>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N168" s="118" t="s">
+    <row r="169" spans="1:14">
+      <c r="N169" s="109" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N169" s="118" t="s">
+    <row r="170" spans="1:14">
+      <c r="N170" s="109"/>
+    </row>
+    <row r="171" spans="1:14">
+      <c r="N171" s="109" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N170" s="118"/>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N171" s="118" t="s">
+    <row r="172" spans="1:14">
+      <c r="N172" s="109" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14">
+      <c r="N173" s="109" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N172" s="118" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N173" s="118" t="s">
+    <row r="174" spans="1:14" ht="15" thickBot="1">
+      <c r="A174" s="97"/>
+    </row>
+    <row r="175" spans="1:14" s="111" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A175" s="110" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="174" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="106"/>
-    </row>
-    <row r="175" spans="1:14" s="120" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="119" t="s">
+    <row r="176" spans="1:14" ht="15">
+      <c r="A176" s="42" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="176" spans="1:14" ht="15" x14ac:dyDescent="0.2">
-      <c r="A176" s="42" t="s">
+    <row r="177" spans="1:1">
+      <c r="A177" s="109" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A177" s="118" t="s">
+    <row r="178" spans="1:1">
+      <c r="A178" s="109" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A178" s="118" t="s">
+    <row r="179" spans="1:1">
+      <c r="A179" s="109" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A179" s="118" t="s">
+    <row r="180" spans="1:1">
+      <c r="A180" s="109" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A180" s="118" t="s">
+    <row r="181" spans="1:1">
+      <c r="A181" s="97"/>
+    </row>
+    <row r="182" spans="1:1" ht="15">
+      <c r="A182" s="42" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A181" s="106"/>
-    </row>
-    <row r="182" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A182" s="42" t="s">
+    <row r="183" spans="1:1">
+      <c r="A183" s="108" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A183" s="117" t="s">
+    <row r="184" spans="1:1">
+      <c r="A184" s="108" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A184" s="117" t="s">
+    <row r="185" spans="1:1">
+      <c r="A185" s="108" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A185" s="117" t="s">
+    <row r="186" spans="1:1">
+      <c r="A186" s="108" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A186" s="117" t="s">
+    <row r="187" spans="1:1">
+      <c r="A187" s="108" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A187" s="117" t="s">
+    <row r="188" spans="1:1">
+      <c r="A188" s="108" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A188" s="117" t="s">
+    <row r="189" spans="1:1">
+      <c r="A189" s="97"/>
+    </row>
+    <row r="190" spans="1:1" ht="15">
+      <c r="A190" s="42" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A189" s="106"/>
-    </row>
-    <row r="190" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A190" s="42" t="s">
+    <row r="191" spans="1:1">
+      <c r="A191" s="109" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A191" s="118" t="s">
+    <row r="192" spans="1:1">
+      <c r="A192" s="109" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A192" s="118" t="s">
+    <row r="193" spans="1:54" ht="15" thickBot="1">
+      <c r="A193" s="97"/>
+    </row>
+    <row r="194" spans="1:54" s="111" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A194" s="110" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="193" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="106"/>
-    </row>
-    <row r="194" spans="1:54" s="120" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="119" t="s">
+    <row r="195" spans="1:54" ht="15">
+      <c r="A195" s="42" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="195" spans="1:54" ht="15" x14ac:dyDescent="0.2">
-      <c r="A195" s="42" t="s">
+      <c r="X195" s="42" t="s">
+        <v>465</v>
+      </c>
+      <c r="AQ195" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="BB195" s="42" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="196" spans="1:54">
+      <c r="A196" s="97" t="s">
         <v>459</v>
       </c>
-      <c r="X195" s="42" t="s">
+      <c r="X196" s="97" t="s">
         <v>466</v>
       </c>
-      <c r="AQ195" s="42" t="s">
+      <c r="AQ196" s="109" t="s">
         <v>480</v>
       </c>
-      <c r="BB195" s="42" t="s">
+      <c r="BB196" s="97" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="196" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A196" s="106" t="s">
+    <row r="197" spans="1:54">
+      <c r="A197" s="109" t="s">
         <v>460</v>
       </c>
-      <c r="X196" s="106" t="s">
+      <c r="X197" s="109" t="s">
         <v>467</v>
       </c>
-      <c r="AQ196" s="118" t="s">
+      <c r="AQ197" s="109" t="s">
         <v>481</v>
       </c>
-      <c r="BB196" s="106" t="s">
+      <c r="BB197" s="97"/>
+    </row>
+    <row r="198" spans="1:54">
+      <c r="A198" s="109" t="s">
+        <v>461</v>
+      </c>
+      <c r="X198" s="109" t="s">
+        <v>468</v>
+      </c>
+      <c r="AQ198" s="109" t="s">
+        <v>482</v>
+      </c>
+      <c r="BB198" s="109" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="197" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A197" s="118" t="s">
-        <v>461</v>
-      </c>
-      <c r="X197" s="118" t="s">
-        <v>468</v>
-      </c>
-      <c r="AQ197" s="118" t="s">
-        <v>482</v>
-      </c>
-      <c r="BB197" s="106"/>
-    </row>
-    <row r="198" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A198" s="118" t="s">
+    <row r="199" spans="1:54">
+      <c r="A199" s="97"/>
+      <c r="X199" s="109" t="s">
+        <v>469</v>
+      </c>
+      <c r="AQ199" s="109" t="s">
+        <v>483</v>
+      </c>
+      <c r="BB199" s="109" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="200" spans="1:54">
+      <c r="A200" s="97" t="s">
         <v>462</v>
       </c>
-      <c r="X198" s="118" t="s">
-        <v>469</v>
-      </c>
-      <c r="AQ198" s="118" t="s">
-        <v>483</v>
-      </c>
-      <c r="BB198" s="118" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="199" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A199" s="106"/>
-      <c r="X199" s="118" t="s">
+      <c r="X200" s="109" t="s">
         <v>470</v>
       </c>
-      <c r="AQ199" s="118" t="s">
-        <v>484</v>
-      </c>
-      <c r="BB199" s="118" t="s">
+      <c r="BB200" s="109"/>
+    </row>
+    <row r="201" spans="1:54">
+      <c r="A201" s="109" t="s">
+        <v>463</v>
+      </c>
+      <c r="X201" s="109"/>
+      <c r="BB201" s="109" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="200" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A200" s="106" t="s">
+    <row r="202" spans="1:54">
+      <c r="A202" s="109" t="s">
+        <v>464</v>
+      </c>
+      <c r="X202" s="109" t="s">
+        <v>471</v>
+      </c>
+      <c r="BB202" s="109" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="203" spans="1:54">
+      <c r="A203" s="97"/>
+      <c r="X203" s="109"/>
+      <c r="BB203" s="109" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="204" spans="1:54">
+      <c r="X204" s="109" t="s">
+        <v>472</v>
+      </c>
+      <c r="BB204" s="109" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="205" spans="1:54">
+      <c r="X205" s="109" t="s">
+        <v>473</v>
+      </c>
+      <c r="BB205" s="109"/>
+    </row>
+    <row r="206" spans="1:54">
+      <c r="X206" s="109"/>
+      <c r="BB206" s="109" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="207" spans="1:54">
+      <c r="X207" s="109" t="s">
+        <v>474</v>
+      </c>
+      <c r="BB207" s="109" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="208" spans="1:54">
+      <c r="X208" s="109" t="s">
+        <v>475</v>
+      </c>
+      <c r="BB208" s="109" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="209" spans="1:54">
+      <c r="X209" s="109" t="s">
+        <v>436</v>
+      </c>
+      <c r="BB209" s="109" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="210" spans="1:54">
+      <c r="X210" s="109"/>
+      <c r="BB210" s="109"/>
+    </row>
+    <row r="211" spans="1:54">
+      <c r="X211" s="109" t="s">
+        <v>476</v>
+      </c>
+      <c r="BB211" s="109" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="212" spans="1:54">
+      <c r="X212" s="97"/>
+      <c r="BB212" s="109" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="213" spans="1:54">
+      <c r="X213" s="97" t="s">
+        <v>462</v>
+      </c>
+      <c r="BB213" s="109" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="214" spans="1:54">
+      <c r="X214" s="97"/>
+      <c r="BB214" s="109" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="215" spans="1:54">
+      <c r="X215" s="109" t="s">
         <v>463</v>
       </c>
-      <c r="X200" s="118" t="s">
-        <v>471</v>
-      </c>
-      <c r="BB200" s="118"/>
-    </row>
-    <row r="201" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A201" s="118" t="s">
-        <v>464</v>
-      </c>
-      <c r="X201" s="118"/>
-      <c r="BB201" s="118" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="202" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A202" s="118" t="s">
-        <v>465</v>
-      </c>
-      <c r="X202" s="118" t="s">
-        <v>472</v>
-      </c>
-      <c r="BB202" s="118" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="203" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A203" s="106"/>
-      <c r="X203" s="118"/>
-      <c r="BB203" s="118" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="204" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="X204" s="118" t="s">
-        <v>473</v>
-      </c>
-      <c r="BB204" s="118" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="205" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="X205" s="118" t="s">
-        <v>474</v>
-      </c>
-      <c r="BB205" s="118"/>
-    </row>
-    <row r="206" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="X206" s="118"/>
-      <c r="BB206" s="118" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="207" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="X207" s="118" t="s">
-        <v>475</v>
-      </c>
-      <c r="BB207" s="118" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="208" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="X208" s="118" t="s">
-        <v>476</v>
-      </c>
-      <c r="BB208" s="118" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="209" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="X209" s="118" t="s">
-        <v>437</v>
-      </c>
-      <c r="BB209" s="118" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="210" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="X210" s="118"/>
-      <c r="BB210" s="118"/>
-    </row>
-    <row r="211" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="X211" s="118" t="s">
+      <c r="BB215" s="109" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="216" spans="1:54">
+      <c r="X216" s="109" t="s">
         <v>477</v>
       </c>
-      <c r="BB211" s="118" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="212" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="X212" s="106"/>
-      <c r="BB212" s="118" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="213" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="X213" s="106" t="s">
-        <v>463</v>
-      </c>
-      <c r="BB213" s="118" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="214" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="X214" s="106"/>
-      <c r="BB214" s="118" t="s">
+      <c r="BB216" s="97"/>
+    </row>
+    <row r="217" spans="1:54">
+      <c r="X217" s="109" t="s">
+        <v>478</v>
+      </c>
+      <c r="BB217" s="97" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="215" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="X215" s="118" t="s">
-        <v>464</v>
-      </c>
-      <c r="BB215" s="118" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="216" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="X216" s="118" t="s">
-        <v>478</v>
-      </c>
-      <c r="BB216" s="106"/>
-    </row>
-    <row r="217" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="X217" s="118" t="s">
-        <v>479</v>
-      </c>
-      <c r="BB217" s="106" t="s">
+    <row r="218" spans="1:54">
+      <c r="BB218" s="97"/>
+    </row>
+    <row r="219" spans="1:54">
+      <c r="BB219" s="109" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="218" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="BB218" s="106"/>
-    </row>
-    <row r="219" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="BB219" s="118" t="s">
+    <row r="220" spans="1:54" ht="15" thickBot="1">
+      <c r="BB220" s="109" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="220" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="BB220" s="118" t="s">
+    <row r="221" spans="1:54" s="111" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A221" s="110" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="221" spans="1:54" s="120" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="119" t="s">
+    <row r="222" spans="1:54" ht="15">
+      <c r="A222" s="42" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="222" spans="1:54" ht="15" x14ac:dyDescent="0.2">
-      <c r="A222" s="42" t="s">
+      <c r="L222" s="42" t="s">
+        <v>504</v>
+      </c>
+      <c r="X222" s="42" t="s">
+        <v>506</v>
+      </c>
+      <c r="AG222" s="42" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="223" spans="1:54" ht="15">
+      <c r="A223" s="109" t="s">
         <v>503</v>
       </c>
-      <c r="L222" s="42" t="s">
+      <c r="L223" s="109" t="s">
         <v>505</v>
       </c>
-      <c r="X222" s="42" t="s">
+      <c r="X223" s="109" t="s">
         <v>507</v>
       </c>
-      <c r="AG222" s="42" t="s">
+      <c r="AG223" s="45" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="223" spans="1:54" ht="15" x14ac:dyDescent="0.25">
-      <c r="A223" s="118" t="s">
-        <v>504</v>
-      </c>
-      <c r="L223" s="118" t="s">
-        <v>506</v>
-      </c>
-      <c r="X223" s="118" t="s">
+    <row r="224" spans="1:54">
+      <c r="A224" s="97"/>
+      <c r="X224" s="109" t="s">
         <v>508</v>
       </c>
-      <c r="AG223" s="45" t="s">
+      <c r="AG224" s="97"/>
+    </row>
+    <row r="225" spans="1:33">
+      <c r="AG225" s="109" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="224" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A224" s="106"/>
-      <c r="X224" s="118" t="s">
-        <v>509</v>
-      </c>
-      <c r="AG224" s="106"/>
-    </row>
-    <row r="225" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="AG225" s="118" t="s">
+    <row r="226" spans="1:33">
+      <c r="AG226" s="109" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="226" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="AG226" s="118" t="s">
+    <row r="227" spans="1:33">
+      <c r="A227" s="97"/>
+      <c r="AG227" s="109"/>
+    </row>
+    <row r="228" spans="1:33">
+      <c r="AG228" s="109" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="227" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A227" s="106"/>
-      <c r="AG227" s="118"/>
-    </row>
-    <row r="228" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="AG228" s="118" t="s">
+    <row r="229" spans="1:33">
+      <c r="AG229" s="109" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="229" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="AG229" s="118" t="s">
+    <row r="230" spans="1:33">
+      <c r="AG230" s="109" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="230" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="AG230" s="118" t="s">
+    <row r="231" spans="1:33">
+      <c r="A231" s="97"/>
+      <c r="AG231" s="97"/>
+    </row>
+    <row r="232" spans="1:33" ht="15">
+      <c r="AG232" s="45" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="231" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A231" s="106"/>
-      <c r="AG231" s="106"/>
-    </row>
-    <row r="232" spans="1:33" ht="15" x14ac:dyDescent="0.25">
-      <c r="AG232" s="45" t="s">
+    <row r="233" spans="1:33">
+      <c r="AG233" s="97"/>
+    </row>
+    <row r="234" spans="1:33">
+      <c r="AG234" s="109" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="233" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="AG233" s="106"/>
-    </row>
-    <row r="234" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="AG234" s="118" t="s">
+    <row r="235" spans="1:33">
+      <c r="AG235" s="109" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="235" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="AG235" s="118" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A246" s="106"/>
-    </row>
-    <row r="247" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:1">
+      <c r="A246" s="97"/>
+    </row>
+    <row r="247" spans="1:1" ht="15">
       <c r="A247" s="42"/>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A248" s="117"/>
-    </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A249" s="117"/>
-    </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A250" s="117"/>
-    </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A251" s="117"/>
-    </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A252" s="106"/>
-    </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A253" s="106"/>
-    </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A254" s="106"/>
-    </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A255" s="106"/>
+    <row r="248" spans="1:1">
+      <c r="A248" s="108"/>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="108"/>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="108"/>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="108"/>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="97"/>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="97"/>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="97"/>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="97"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A5:A316"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="15" customHeight="1"/>
+  <sheetData>
+    <row r="5" spans="1:1" ht="15" customHeight="1">
+      <c r="A5" s="114"/>
+    </row>
+    <row r="6" spans="1:1" ht="15" customHeight="1">
+      <c r="A6" s="115"/>
+    </row>
+    <row r="7" spans="1:1" ht="15" customHeight="1">
+      <c r="A7" s="115"/>
+    </row>
+    <row r="8" spans="1:1" ht="15" customHeight="1">
+      <c r="A8" s="115"/>
+    </row>
+    <row r="9" spans="1:1" ht="15" customHeight="1">
+      <c r="A9" s="115"/>
+    </row>
+    <row r="11" spans="1:1" ht="15" customHeight="1">
+      <c r="A11" s="117"/>
+    </row>
+    <row r="12" spans="1:1" ht="15" customHeight="1">
+      <c r="A12" s="117"/>
+    </row>
+    <row r="13" spans="1:1" ht="15" customHeight="1">
+      <c r="A13" s="117"/>
+    </row>
+    <row r="14" spans="1:1" ht="15" customHeight="1">
+      <c r="A14" s="117"/>
+    </row>
+    <row r="15" spans="1:1" ht="15" customHeight="1">
+      <c r="A15" s="117"/>
+    </row>
+    <row r="16" spans="1:1" ht="15" customHeight="1">
+      <c r="A16" s="117"/>
+    </row>
+    <row r="17" spans="1:1" ht="15" customHeight="1">
+      <c r="A17" s="117"/>
+    </row>
+    <row r="18" spans="1:1" ht="15" customHeight="1">
+      <c r="A18" s="117"/>
+    </row>
+    <row r="19" spans="1:1" ht="15" customHeight="1">
+      <c r="A19" s="117"/>
+    </row>
+    <row r="20" spans="1:1" ht="15" customHeight="1">
+      <c r="A20" s="117"/>
+    </row>
+    <row r="21" spans="1:1" ht="15" customHeight="1">
+      <c r="A21" s="117"/>
+    </row>
+    <row r="22" spans="1:1" ht="15" customHeight="1">
+      <c r="A22" s="117"/>
+    </row>
+    <row r="23" spans="1:1" ht="15" customHeight="1">
+      <c r="A23" s="117"/>
+    </row>
+    <row r="24" spans="1:1" ht="15" customHeight="1">
+      <c r="A24" s="117"/>
+    </row>
+    <row r="25" spans="1:1" ht="15" customHeight="1">
+      <c r="A25" s="117"/>
+    </row>
+    <row r="26" spans="1:1" ht="15" customHeight="1">
+      <c r="A26" s="116"/>
+    </row>
+    <row r="27" spans="1:1" ht="15" customHeight="1">
+      <c r="A27" s="117"/>
+    </row>
+    <row r="28" spans="1:1" ht="15" customHeight="1">
+      <c r="A28" s="117"/>
+    </row>
+    <row r="29" spans="1:1" ht="15" customHeight="1">
+      <c r="A29" s="117"/>
+    </row>
+    <row r="30" spans="1:1" ht="15" customHeight="1">
+      <c r="A30" s="117"/>
+    </row>
+    <row r="31" spans="1:1" ht="15" customHeight="1">
+      <c r="A31" s="117"/>
+    </row>
+    <row r="32" spans="1:1" ht="15" customHeight="1">
+      <c r="A32" s="117"/>
+    </row>
+    <row r="33" spans="1:1" ht="15" customHeight="1">
+      <c r="A33" s="117"/>
+    </row>
+    <row r="34" spans="1:1" ht="15" customHeight="1">
+      <c r="A34" s="117"/>
+    </row>
+    <row r="35" spans="1:1" ht="15" customHeight="1">
+      <c r="A35" s="117"/>
+    </row>
+    <row r="36" spans="1:1" ht="15" customHeight="1">
+      <c r="A36" s="117"/>
+    </row>
+    <row r="37" spans="1:1" ht="15" customHeight="1">
+      <c r="A37" s="117"/>
+    </row>
+    <row r="38" spans="1:1" ht="15" customHeight="1">
+      <c r="A38" s="117"/>
+    </row>
+    <row r="39" spans="1:1" ht="15" customHeight="1">
+      <c r="A39" s="117"/>
+    </row>
+    <row r="40" spans="1:1" ht="15" customHeight="1">
+      <c r="A40" s="117"/>
+    </row>
+    <row r="41" spans="1:1" ht="15" customHeight="1">
+      <c r="A41" s="117"/>
+    </row>
+    <row r="42" spans="1:1" ht="15" customHeight="1">
+      <c r="A42" s="117"/>
+    </row>
+    <row r="43" spans="1:1" ht="15" customHeight="1">
+      <c r="A43" s="117"/>
+    </row>
+    <row r="44" spans="1:1" ht="15" customHeight="1">
+      <c r="A44" s="116"/>
+    </row>
+    <row r="45" spans="1:1" ht="15" customHeight="1">
+      <c r="A45" s="117"/>
+    </row>
+    <row r="46" spans="1:1" ht="15" customHeight="1">
+      <c r="A46" s="117"/>
+    </row>
+    <row r="47" spans="1:1" ht="15" customHeight="1">
+      <c r="A47" s="117"/>
+    </row>
+    <row r="48" spans="1:1" ht="15" customHeight="1">
+      <c r="A48" s="117"/>
+    </row>
+    <row r="49" spans="1:1" ht="15" customHeight="1">
+      <c r="A49" s="117"/>
+    </row>
+    <row r="50" spans="1:1" ht="15" customHeight="1">
+      <c r="A50" s="117"/>
+    </row>
+    <row r="51" spans="1:1" ht="15" customHeight="1">
+      <c r="A51" s="117"/>
+    </row>
+    <row r="52" spans="1:1" ht="15" customHeight="1">
+      <c r="A52" s="117"/>
+    </row>
+    <row r="53" spans="1:1" ht="15" customHeight="1">
+      <c r="A53" s="117"/>
+    </row>
+    <row r="54" spans="1:1" ht="15" customHeight="1">
+      <c r="A54" s="117"/>
+    </row>
+    <row r="55" spans="1:1" ht="15" customHeight="1">
+      <c r="A55" s="116"/>
+    </row>
+    <row r="56" spans="1:1" ht="15" customHeight="1">
+      <c r="A56" s="117"/>
+    </row>
+    <row r="57" spans="1:1" ht="15" customHeight="1">
+      <c r="A57" s="117"/>
+    </row>
+    <row r="58" spans="1:1" ht="15" customHeight="1">
+      <c r="A58" s="117"/>
+    </row>
+    <row r="59" spans="1:1" ht="15" customHeight="1">
+      <c r="A59" s="117"/>
+    </row>
+    <row r="60" spans="1:1" ht="15" customHeight="1">
+      <c r="A60" s="117"/>
+    </row>
+    <row r="61" spans="1:1" ht="15" customHeight="1">
+      <c r="A61" s="117"/>
+    </row>
+    <row r="62" spans="1:1" ht="15" customHeight="1">
+      <c r="A62" s="117"/>
+    </row>
+    <row r="63" spans="1:1" ht="15" customHeight="1">
+      <c r="A63" s="117"/>
+    </row>
+    <row r="64" spans="1:1" ht="15" customHeight="1">
+      <c r="A64" s="116"/>
+    </row>
+    <row r="65" spans="1:1" ht="15" customHeight="1">
+      <c r="A65" s="117"/>
+    </row>
+    <row r="66" spans="1:1" ht="15" customHeight="1">
+      <c r="A66" s="117"/>
+    </row>
+    <row r="67" spans="1:1" ht="15" customHeight="1">
+      <c r="A67" s="117"/>
+    </row>
+    <row r="68" spans="1:1" ht="15" customHeight="1">
+      <c r="A68" s="117"/>
+    </row>
+    <row r="69" spans="1:1" ht="15" customHeight="1">
+      <c r="A69" s="117"/>
+    </row>
+    <row r="70" spans="1:1" ht="15" customHeight="1">
+      <c r="A70" s="117"/>
+    </row>
+    <row r="71" spans="1:1" ht="15" customHeight="1">
+      <c r="A71" s="117"/>
+    </row>
+    <row r="72" spans="1:1" ht="15" customHeight="1">
+      <c r="A72" s="117"/>
+    </row>
+    <row r="73" spans="1:1" ht="15" customHeight="1">
+      <c r="A73" s="117"/>
+    </row>
+    <row r="74" spans="1:1" ht="15" customHeight="1">
+      <c r="A74" s="117"/>
+    </row>
+    <row r="75" spans="1:1" ht="15" customHeight="1">
+      <c r="A75" s="117"/>
+    </row>
+    <row r="76" spans="1:1" ht="15" customHeight="1">
+      <c r="A76" s="117"/>
+    </row>
+    <row r="77" spans="1:1" ht="15" customHeight="1">
+      <c r="A77" s="117"/>
+    </row>
+    <row r="78" spans="1:1" ht="15" customHeight="1">
+      <c r="A78" s="116"/>
+    </row>
+    <row r="79" spans="1:1" ht="15" customHeight="1">
+      <c r="A79" s="117"/>
+    </row>
+    <row r="80" spans="1:1" ht="15" customHeight="1">
+      <c r="A80" s="117"/>
+    </row>
+    <row r="81" spans="1:1" ht="15" customHeight="1">
+      <c r="A81" s="117"/>
+    </row>
+    <row r="82" spans="1:1" ht="15" customHeight="1">
+      <c r="A82" s="117"/>
+    </row>
+    <row r="83" spans="1:1" ht="15" customHeight="1">
+      <c r="A83" s="117"/>
+    </row>
+    <row r="84" spans="1:1" ht="15" customHeight="1">
+      <c r="A84" s="116"/>
+    </row>
+    <row r="85" spans="1:1" ht="15" customHeight="1">
+      <c r="A85" s="117"/>
+    </row>
+    <row r="86" spans="1:1" ht="15" customHeight="1">
+      <c r="A86" s="117"/>
+    </row>
+    <row r="87" spans="1:1" ht="15" customHeight="1">
+      <c r="A87" s="117"/>
+    </row>
+    <row r="88" spans="1:1" ht="15" customHeight="1">
+      <c r="A88" s="117"/>
+    </row>
+    <row r="89" spans="1:1" ht="15" customHeight="1">
+      <c r="A89" s="117"/>
+    </row>
+    <row r="90" spans="1:1" ht="15" customHeight="1">
+      <c r="A90" s="117"/>
+    </row>
+    <row r="91" spans="1:1" ht="15" customHeight="1">
+      <c r="A91" s="116"/>
+    </row>
+    <row r="92" spans="1:1" ht="15" customHeight="1">
+      <c r="A92" s="117"/>
+    </row>
+    <row r="93" spans="1:1" ht="15" customHeight="1">
+      <c r="A93" s="117"/>
+    </row>
+    <row r="94" spans="1:1" ht="15" customHeight="1">
+      <c r="A94" s="117"/>
+    </row>
+    <row r="96" spans="1:1" ht="15" customHeight="1">
+      <c r="A96" s="118"/>
+    </row>
+    <row r="97" spans="1:1" ht="15" customHeight="1">
+      <c r="A97" s="115"/>
+    </row>
+    <row r="98" spans="1:1" ht="15" customHeight="1">
+      <c r="A98" s="106"/>
+    </row>
+    <row r="99" spans="1:1" ht="15" customHeight="1">
+      <c r="A99" s="115"/>
+    </row>
+    <row r="100" spans="1:1" ht="15" customHeight="1">
+      <c r="A100" s="106"/>
+    </row>
+    <row r="101" spans="1:1" ht="15" customHeight="1">
+      <c r="A101" s="115"/>
+    </row>
+    <row r="102" spans="1:1" ht="15" customHeight="1">
+      <c r="A102" s="106"/>
+    </row>
+    <row r="103" spans="1:1" ht="15" customHeight="1">
+      <c r="A103" s="115"/>
+    </row>
+    <row r="104" spans="1:1" ht="15" customHeight="1">
+      <c r="A104" s="106"/>
+    </row>
+    <row r="105" spans="1:1" ht="15" customHeight="1">
+      <c r="A105" s="115"/>
+    </row>
+    <row r="106" spans="1:1" ht="15" customHeight="1">
+      <c r="A106" s="106"/>
+    </row>
+    <row r="110" spans="1:1" ht="15" customHeight="1">
+      <c r="A110" s="114"/>
+    </row>
+    <row r="111" spans="1:1" ht="15" customHeight="1">
+      <c r="A111" s="115"/>
+    </row>
+    <row r="112" spans="1:1" ht="15" customHeight="1">
+      <c r="A112" s="115"/>
+    </row>
+    <row r="114" spans="1:1" ht="15" customHeight="1">
+      <c r="A114" s="117"/>
+    </row>
+    <row r="115" spans="1:1" ht="15" customHeight="1">
+      <c r="A115" s="117"/>
+    </row>
+    <row r="116" spans="1:1" ht="15" customHeight="1">
+      <c r="A116" s="117"/>
+    </row>
+    <row r="117" spans="1:1" ht="15" customHeight="1">
+      <c r="A117" s="117"/>
+    </row>
+    <row r="118" spans="1:1" ht="15" customHeight="1">
+      <c r="A118" s="116"/>
+    </row>
+    <row r="119" spans="1:1" ht="15" customHeight="1">
+      <c r="A119" s="117"/>
+    </row>
+    <row r="120" spans="1:1" ht="15" customHeight="1">
+      <c r="A120" s="117"/>
+    </row>
+    <row r="121" spans="1:1" ht="15" customHeight="1">
+      <c r="A121" s="117"/>
+    </row>
+    <row r="122" spans="1:1" ht="15" customHeight="1">
+      <c r="A122" s="117"/>
+    </row>
+    <row r="123" spans="1:1" ht="15" customHeight="1">
+      <c r="A123" s="117"/>
+    </row>
+    <row r="124" spans="1:1" ht="15" customHeight="1">
+      <c r="A124" s="117"/>
+    </row>
+    <row r="125" spans="1:1" ht="15" customHeight="1">
+      <c r="A125" s="117"/>
+    </row>
+    <row r="126" spans="1:1" ht="15" customHeight="1">
+      <c r="A126" s="117"/>
+    </row>
+    <row r="127" spans="1:1" ht="15" customHeight="1">
+      <c r="A127" s="117"/>
+    </row>
+    <row r="128" spans="1:1" ht="15" customHeight="1">
+      <c r="A128" s="117"/>
+    </row>
+    <row r="129" spans="1:1" ht="15" customHeight="1">
+      <c r="A129" s="117"/>
+    </row>
+    <row r="130" spans="1:1" ht="15" customHeight="1">
+      <c r="A130" s="117"/>
+    </row>
+    <row r="131" spans="1:1" ht="15" customHeight="1">
+      <c r="A131" s="117"/>
+    </row>
+    <row r="132" spans="1:1" ht="15" customHeight="1">
+      <c r="A132" s="117"/>
+    </row>
+    <row r="133" spans="1:1" ht="15" customHeight="1">
+      <c r="A133" s="117"/>
+    </row>
+    <row r="134" spans="1:1" ht="15" customHeight="1">
+      <c r="A134" s="117"/>
+    </row>
+    <row r="135" spans="1:1" ht="15" customHeight="1">
+      <c r="A135" s="116"/>
+    </row>
+    <row r="136" spans="1:1" ht="15" customHeight="1">
+      <c r="A136" s="117"/>
+    </row>
+    <row r="137" spans="1:1" ht="15" customHeight="1">
+      <c r="A137" s="117"/>
+    </row>
+    <row r="138" spans="1:1" ht="15" customHeight="1">
+      <c r="A138" s="117"/>
+    </row>
+    <row r="139" spans="1:1" ht="15" customHeight="1">
+      <c r="A139" s="117"/>
+    </row>
+    <row r="140" spans="1:1" ht="15" customHeight="1">
+      <c r="A140" s="117"/>
+    </row>
+    <row r="141" spans="1:1" ht="15" customHeight="1">
+      <c r="A141" s="117"/>
+    </row>
+    <row r="142" spans="1:1" ht="15" customHeight="1">
+      <c r="A142" s="117"/>
+    </row>
+    <row r="143" spans="1:1" ht="15" customHeight="1">
+      <c r="A143" s="117"/>
+    </row>
+    <row r="144" spans="1:1" ht="15" customHeight="1">
+      <c r="A144" s="117"/>
+    </row>
+    <row r="148" spans="1:1" ht="15" customHeight="1">
+      <c r="A148" s="114"/>
+    </row>
+    <row r="149" spans="1:1" ht="15" customHeight="1">
+      <c r="A149" s="115"/>
+    </row>
+    <row r="150" spans="1:1" ht="15" customHeight="1">
+      <c r="A150" s="115"/>
+    </row>
+    <row r="152" spans="1:1" ht="15" customHeight="1">
+      <c r="A152" s="117"/>
+    </row>
+    <row r="153" spans="1:1" ht="15" customHeight="1">
+      <c r="A153" s="117"/>
+    </row>
+    <row r="154" spans="1:1" ht="15" customHeight="1">
+      <c r="A154" s="116"/>
+    </row>
+    <row r="155" spans="1:1" ht="15" customHeight="1">
+      <c r="A155" s="117"/>
+    </row>
+    <row r="156" spans="1:1" ht="15" customHeight="1">
+      <c r="A156" s="117"/>
+    </row>
+    <row r="157" spans="1:1" ht="15" customHeight="1">
+      <c r="A157" s="116"/>
+    </row>
+    <row r="158" spans="1:1" ht="15" customHeight="1">
+      <c r="A158" s="117"/>
+    </row>
+    <row r="159" spans="1:1" ht="15" customHeight="1">
+      <c r="A159" s="117"/>
+    </row>
+    <row r="160" spans="1:1" ht="15" customHeight="1">
+      <c r="A160" s="117"/>
+    </row>
+    <row r="161" spans="1:1" ht="15" customHeight="1">
+      <c r="A161" s="117"/>
+    </row>
+    <row r="162" spans="1:1" ht="15" customHeight="1">
+      <c r="A162" s="117"/>
+    </row>
+    <row r="163" spans="1:1" ht="15" customHeight="1">
+      <c r="A163" s="116"/>
+    </row>
+    <row r="164" spans="1:1" ht="15" customHeight="1">
+      <c r="A164" s="117"/>
+    </row>
+    <row r="165" spans="1:1" ht="15" customHeight="1">
+      <c r="A165" s="117"/>
+    </row>
+    <row r="166" spans="1:1" ht="15" customHeight="1">
+      <c r="A166" s="117"/>
+    </row>
+    <row r="167" spans="1:1" ht="15" customHeight="1">
+      <c r="A167" s="117"/>
+    </row>
+    <row r="168" spans="1:1" ht="15" customHeight="1">
+      <c r="A168" s="117"/>
+    </row>
+    <row r="169" spans="1:1" ht="15" customHeight="1">
+      <c r="A169" s="117"/>
+    </row>
+    <row r="170" spans="1:1" ht="15" customHeight="1">
+      <c r="A170" s="117"/>
+    </row>
+    <row r="171" spans="1:1" ht="15" customHeight="1">
+      <c r="A171" s="117"/>
+    </row>
+    <row r="172" spans="1:1" ht="15" customHeight="1">
+      <c r="A172" s="117"/>
+    </row>
+    <row r="173" spans="1:1" ht="15" customHeight="1">
+      <c r="A173" s="117"/>
+    </row>
+    <row r="174" spans="1:1" ht="15" customHeight="1">
+      <c r="A174" s="116"/>
+    </row>
+    <row r="175" spans="1:1" ht="15" customHeight="1">
+      <c r="A175" s="117"/>
+    </row>
+    <row r="176" spans="1:1" ht="15" customHeight="1">
+      <c r="A176" s="117"/>
+    </row>
+    <row r="177" spans="1:1" ht="15" customHeight="1">
+      <c r="A177" s="116"/>
+    </row>
+    <row r="178" spans="1:1" ht="15" customHeight="1">
+      <c r="A178" s="117"/>
+    </row>
+    <row r="179" spans="1:1" ht="15" customHeight="1">
+      <c r="A179" s="117"/>
+    </row>
+    <row r="180" spans="1:1" ht="15" customHeight="1">
+      <c r="A180" s="117"/>
+    </row>
+    <row r="181" spans="1:1" ht="15" customHeight="1">
+      <c r="A181" s="116"/>
+    </row>
+    <row r="182" spans="1:1" ht="15" customHeight="1">
+      <c r="A182" s="117"/>
+    </row>
+    <row r="183" spans="1:1" ht="15" customHeight="1">
+      <c r="A183" s="117"/>
+    </row>
+    <row r="184" spans="1:1" ht="15" customHeight="1">
+      <c r="A184" s="117"/>
+    </row>
+    <row r="185" spans="1:1" ht="15" customHeight="1">
+      <c r="A185" s="116"/>
+    </row>
+    <row r="186" spans="1:1" ht="15" customHeight="1">
+      <c r="A186" s="117"/>
+    </row>
+    <row r="187" spans="1:1" ht="15" customHeight="1">
+      <c r="A187" s="117"/>
+    </row>
+    <row r="188" spans="1:1" ht="15" customHeight="1">
+      <c r="A188" s="117"/>
+    </row>
+    <row r="189" spans="1:1" ht="15" customHeight="1">
+      <c r="A189" s="117"/>
+    </row>
+    <row r="190" spans="1:1" ht="15" customHeight="1">
+      <c r="A190" s="117"/>
+    </row>
+    <row r="191" spans="1:1" ht="15" customHeight="1">
+      <c r="A191" s="117"/>
+    </row>
+    <row r="192" spans="1:1" ht="15" customHeight="1">
+      <c r="A192" s="117"/>
+    </row>
+    <row r="193" spans="1:1" ht="15" customHeight="1">
+      <c r="A193" s="116"/>
+    </row>
+    <row r="194" spans="1:1" ht="15" customHeight="1">
+      <c r="A194" s="117"/>
+    </row>
+    <row r="195" spans="1:1" ht="15" customHeight="1">
+      <c r="A195" s="117"/>
+    </row>
+    <row r="196" spans="1:1" ht="15" customHeight="1">
+      <c r="A196" s="117"/>
+    </row>
+    <row r="197" spans="1:1" ht="15" customHeight="1">
+      <c r="A197" s="117"/>
+    </row>
+    <row r="198" spans="1:1" ht="15" customHeight="1">
+      <c r="A198" s="117"/>
+    </row>
+    <row r="199" spans="1:1" ht="15" customHeight="1">
+      <c r="A199" s="117"/>
+    </row>
+    <row r="200" spans="1:1" ht="15" customHeight="1">
+      <c r="A200" s="117"/>
+    </row>
+    <row r="201" spans="1:1" ht="15" customHeight="1">
+      <c r="A201" s="117"/>
+    </row>
+    <row r="202" spans="1:1" ht="15" customHeight="1">
+      <c r="A202" s="116"/>
+    </row>
+    <row r="203" spans="1:1" ht="15" customHeight="1">
+      <c r="A203" s="117"/>
+    </row>
+    <row r="207" spans="1:1" ht="15" customHeight="1">
+      <c r="A207" s="114"/>
+    </row>
+    <row r="211" spans="1:1" ht="15" customHeight="1">
+      <c r="A211" s="117"/>
+    </row>
+    <row r="212" spans="1:1" ht="15" customHeight="1">
+      <c r="A212" s="117"/>
+    </row>
+    <row r="213" spans="1:1" ht="15" customHeight="1">
+      <c r="A213" s="117"/>
+    </row>
+    <row r="217" spans="1:1" ht="15" customHeight="1">
+      <c r="A217" s="117"/>
+    </row>
+    <row r="218" spans="1:1" ht="15" customHeight="1">
+      <c r="A218" s="117"/>
+    </row>
+    <row r="219" spans="1:1" ht="15" customHeight="1">
+      <c r="A219" s="117"/>
+    </row>
+    <row r="220" spans="1:1" ht="15" customHeight="1">
+      <c r="A220" s="117"/>
+    </row>
+    <row r="221" spans="1:1" ht="15" customHeight="1">
+      <c r="A221" s="117"/>
+    </row>
+    <row r="222" spans="1:1" ht="15" customHeight="1">
+      <c r="A222" s="117"/>
+    </row>
+    <row r="223" spans="1:1" ht="15" customHeight="1">
+      <c r="A223" s="117"/>
+    </row>
+    <row r="224" spans="1:1" ht="15" customHeight="1">
+      <c r="A224" s="117"/>
+    </row>
+    <row r="225" spans="1:1" ht="15" customHeight="1">
+      <c r="A225" s="117"/>
+    </row>
+    <row r="226" spans="1:1" ht="15" customHeight="1">
+      <c r="A226" s="117"/>
+    </row>
+    <row r="227" spans="1:1" ht="15" customHeight="1">
+      <c r="A227" s="117"/>
+    </row>
+    <row r="228" spans="1:1" ht="15" customHeight="1">
+      <c r="A228" s="117"/>
+    </row>
+    <row r="229" spans="1:1" ht="15" customHeight="1">
+      <c r="A229" s="117"/>
+    </row>
+    <row r="232" spans="1:1" ht="15" customHeight="1">
+      <c r="A232" s="115"/>
+    </row>
+    <row r="233" spans="1:1" ht="15" customHeight="1">
+      <c r="A233" s="119"/>
+    </row>
+    <row r="234" spans="1:1" ht="15" customHeight="1">
+      <c r="A234" s="115"/>
+    </row>
+    <row r="235" spans="1:1" ht="15" customHeight="1">
+      <c r="A235" s="119"/>
+    </row>
+    <row r="236" spans="1:1" ht="15" customHeight="1">
+      <c r="A236" s="119"/>
+    </row>
+    <row r="237" spans="1:1" ht="15" customHeight="1">
+      <c r="A237" s="115"/>
+    </row>
+    <row r="238" spans="1:1" ht="15" customHeight="1">
+      <c r="A238" s="119"/>
+    </row>
+    <row r="242" spans="1:1" ht="15" customHeight="1">
+      <c r="A242" s="114"/>
+    </row>
+    <row r="246" spans="1:1" ht="15" customHeight="1">
+      <c r="A246" s="117"/>
+    </row>
+    <row r="247" spans="1:1" ht="15" customHeight="1">
+      <c r="A247" s="117"/>
+    </row>
+    <row r="248" spans="1:1" ht="15" customHeight="1">
+      <c r="A248" s="117"/>
+    </row>
+    <row r="249" spans="1:1" ht="15" customHeight="1">
+      <c r="A249" s="117"/>
+    </row>
+    <row r="250" spans="1:1" ht="15" customHeight="1">
+      <c r="A250" s="117"/>
+    </row>
+    <row r="251" spans="1:1" ht="15" customHeight="1">
+      <c r="A251" s="117"/>
+    </row>
+    <row r="252" spans="1:1" ht="15" customHeight="1">
+      <c r="A252" s="116"/>
+    </row>
+    <row r="253" spans="1:1" ht="15" customHeight="1">
+      <c r="A253" s="117"/>
+    </row>
+    <row r="254" spans="1:1" ht="15" customHeight="1">
+      <c r="A254" s="117"/>
+    </row>
+    <row r="255" spans="1:1" ht="15" customHeight="1">
+      <c r="A255" s="117"/>
+    </row>
+    <row r="256" spans="1:1" ht="15" customHeight="1">
+      <c r="A256" s="117"/>
+    </row>
+    <row r="257" spans="1:1" ht="15" customHeight="1">
+      <c r="A257" s="117"/>
+    </row>
+    <row r="258" spans="1:1" ht="15" customHeight="1">
+      <c r="A258" s="117"/>
+    </row>
+    <row r="262" spans="1:1" ht="15" customHeight="1">
+      <c r="A262" s="114"/>
+    </row>
+    <row r="264" spans="1:1" ht="15" customHeight="1">
+      <c r="A264" s="117"/>
+    </row>
+    <row r="265" spans="1:1" ht="15" customHeight="1">
+      <c r="A265" s="117"/>
+    </row>
+    <row r="266" spans="1:1" ht="15" customHeight="1">
+      <c r="A266" s="117"/>
+    </row>
+    <row r="267" spans="1:1" ht="15" customHeight="1">
+      <c r="A267" s="117"/>
+    </row>
+    <row r="268" spans="1:1" ht="15" customHeight="1">
+      <c r="A268" s="117"/>
+    </row>
+    <row r="269" spans="1:1" ht="15" customHeight="1">
+      <c r="A269" s="117"/>
+    </row>
+    <row r="270" spans="1:1" ht="15" customHeight="1">
+      <c r="A270" s="117"/>
+    </row>
+    <row r="271" spans="1:1" ht="15" customHeight="1">
+      <c r="A271" s="117"/>
+    </row>
+    <row r="272" spans="1:1" ht="15" customHeight="1">
+      <c r="A272" s="117"/>
+    </row>
+    <row r="273" spans="1:1" ht="15" customHeight="1">
+      <c r="A273" s="117"/>
+    </row>
+    <row r="274" spans="1:1" ht="15" customHeight="1">
+      <c r="A274" s="117"/>
+    </row>
+    <row r="275" spans="1:1" ht="15" customHeight="1">
+      <c r="A275" s="117"/>
+    </row>
+    <row r="279" spans="1:1" ht="15" customHeight="1">
+      <c r="A279" s="114"/>
+    </row>
+    <row r="281" spans="1:1" ht="15" customHeight="1">
+      <c r="A281" s="117"/>
+    </row>
+    <row r="282" spans="1:1" ht="15" customHeight="1">
+      <c r="A282" s="117"/>
+    </row>
+    <row r="283" spans="1:1" ht="15" customHeight="1">
+      <c r="A283" s="116"/>
+    </row>
+    <row r="284" spans="1:1" ht="15" customHeight="1">
+      <c r="A284" s="117"/>
+    </row>
+    <row r="285" spans="1:1" ht="15" customHeight="1">
+      <c r="A285" s="117"/>
+    </row>
+    <row r="288" spans="1:1" ht="15" customHeight="1">
+      <c r="A288" s="115"/>
+    </row>
+    <row r="289" spans="1:1" ht="15" customHeight="1">
+      <c r="A289" s="119"/>
+    </row>
+    <row r="290" spans="1:1" ht="15" customHeight="1">
+      <c r="A290" s="115"/>
+    </row>
+    <row r="291" spans="1:1" ht="15" customHeight="1">
+      <c r="A291" s="119"/>
+    </row>
+    <row r="292" spans="1:1" ht="15" customHeight="1">
+      <c r="A292" s="115"/>
+    </row>
+    <row r="293" spans="1:1" ht="15" customHeight="1">
+      <c r="A293" s="119"/>
+    </row>
+    <row r="294" spans="1:1" ht="15" customHeight="1">
+      <c r="A294" s="115"/>
+    </row>
+    <row r="295" spans="1:1" ht="15" customHeight="1">
+      <c r="A295" s="120"/>
+    </row>
+    <row r="299" spans="1:1" ht="15" customHeight="1">
+      <c r="A299" s="114"/>
+    </row>
+    <row r="301" spans="1:1" ht="15" customHeight="1">
+      <c r="A301" s="117"/>
+    </row>
+    <row r="302" spans="1:1" ht="15" customHeight="1">
+      <c r="A302" s="117"/>
+    </row>
+    <row r="303" spans="1:1" ht="15" customHeight="1">
+      <c r="A303" s="117"/>
+    </row>
+    <row r="304" spans="1:1" ht="15" customHeight="1">
+      <c r="A304" s="117"/>
+    </row>
+    <row r="308" spans="1:1" ht="15" customHeight="1">
+      <c r="A308" s="121"/>
+    </row>
+    <row r="309" spans="1:1" ht="15" customHeight="1">
+      <c r="A309" s="115"/>
+    </row>
+    <row r="310" spans="1:1" ht="15" customHeight="1">
+      <c r="A310" s="106"/>
+    </row>
+    <row r="311" spans="1:1" ht="15" customHeight="1">
+      <c r="A311" s="115"/>
+    </row>
+    <row r="312" spans="1:1" ht="15" customHeight="1">
+      <c r="A312" s="106"/>
+    </row>
+    <row r="313" spans="1:1" ht="15" customHeight="1">
+      <c r="A313" s="115"/>
+    </row>
+    <row r="314" spans="1:1" ht="15" customHeight="1">
+      <c r="A314" s="106"/>
+    </row>
+    <row r="315" spans="1:1" ht="15" customHeight="1">
+      <c r="A315" s="115"/>
+    </row>
+    <row r="316" spans="1:1" ht="15" customHeight="1">
+      <c r="A316" s="106"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>